--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -7952,9 +7952,7 @@
       <c r="D11" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>103</v>
-      </c>
+      <c r="E11" s="48"/>
       <c r="F11" s="29" t="s">
         <v>103</v>
       </c>

--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -7896,8 +7896,8 @@
       <c r="D8" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="30">
-        <v>20</v>
+      <c s="30" r="E8" t="n">
+        <v>10</v>
       </c>
       <c r="F8" s="30">
         <v>20</v>
@@ -8240,8 +8240,8 @@
       <c r="B8" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="58">
-        <v>-8</v>
+      <c s="58" r="C8" t="n">
+        <v>-4</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -8371,9 +8371,9 @@
       <c r="B14" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="66">
-        <f>Parameters!D24</f>
-        <v>20</v>
+      <c s="66" r="C14" t="n">
+        <f>IF(C6="RA65",Parameters!D27,Parameters!D24)</f>
+        <v>10</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -8975,7 +8975,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="whole" sqref="C8" xr:uid="{00000000-0002-0000-0500-000003000000}">
-      <formula1>-20</formula1>
+      <formula1>-C14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="whole" sqref="C9" xr:uid="{00000000-0002-0000-0500-000004000000}">
@@ -12782,10 +12782,8 @@
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="87" t="inlineStr">
-        <is>
-          <t>Sweep 使用 40 格 R；计算器按型号换算。</t>
-        </is>
+      <c s="87" r="F23" t="str">
+        <v>Sweep 使用 8 系 C、40 格 R。</v>
       </c>
       <c r="G23" s="88"/>
       <c r="H23" s="88"/>
@@ -12799,8 +12797,8 @@
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="59" t="s">
-        <v>86</v>
+      <c s="59" r="B24" t="str">
+        <v>HSC · 8 系</v>
       </c>
       <c r="C24" s="70"/>
       <c r="D24" s="66">
@@ -12864,11 +12862,15 @@
       <c r="N26" s="79"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" ht="12" customHeight="1">
+    <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
+      <c s="59" r="B27" t="str">
+        <v>HSC · 6 系</v>
+      </c>
+      <c s="70" r="C27"/>
+      <c s="66" r="D27" t="n">
+        <v>10</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -13124,7 +13126,8 @@
       <c r="O41" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
     <mergeCell ref="D5:H5"/>
@@ -20203,9 +20206,9 @@
         <f>Calculator!C7</f>
         <v>-12</v>
       </c>
-      <c r="D165" s="114">
+      <c s="114" r="D165" t="n">
         <f>Calculator!C8</f>
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="E165" s="114">
         <f>Calculator!C9</f>
@@ -20259,8 +20262,8 @@
         <f>MIN(4,MAX(1,INT((1+C165/Parameters!$D$23)*4)+1))</f>
         <v>3</v>
       </c>
-      <c r="R165" s="114">
-        <f>MIN(4,MAX(1,INT((1+D165/Parameters!$D$24)*4)+1))</f>
+      <c s="114" r="R165" t="n">
+        <f>MIN(4,MAX(1,INT((1+D165/Calculator!$C$14)*4)+1))</f>
         <v>3</v>
       </c>
       <c r="S165" s="114">
@@ -20271,9 +20274,9 @@
         <f>MAX(0,MIN(1,(1+C165/Parameters!$D$23)*4-(Q165-1)))</f>
         <v>0</v>
       </c>
-      <c r="U165" s="114">
-        <f>MAX(0,MIN(1,(1+D165/Parameters!$D$24)*4-(R165-1)))</f>
-        <v>0.39999999999999991</v>
+      <c s="114" r="U165" t="n">
+        <f>MAX(0,MIN(1,(1+D165/Calculator!$C$14)*4-(R165-1)))</f>
+        <v>0.3999999999999999</v>
       </c>
       <c r="V165" s="114">
         <f>MAX(0,MIN(1,(1+E165/Calculator!$C$15)*4-(S165-1)))</f>

--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\damping-rx-sync-20261026\native\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041BE659-9D6E-4F69-AD06-1DC5797401F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB36D54-73B1-4918-96E7-EB4EFC8A4F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
   <si>
     <t>Valving</t>
   </si>
@@ -333,6 +333,10 @@
   <si>
     <t>Calculator</t>
   </si>
+  <si>
+    <t>Type-A</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -343,7 +347,7 @@
     <numFmt numFmtId="177" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="178" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="81">
+  <fonts count="80">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -437,13 +441,6 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF283C50"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -876,7 +873,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="72">
+  <fills count="71">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,11 +898,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF5F7FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1234,7 +1226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="73">
+  <borders count="72">
     <border>
       <left/>
       <right/>
@@ -1299,13 +1291,6 @@
       <diagonal style="thin">
         <color auto="1"/>
       </diagonal>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1833,11 +1818,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1852,13 +1837,13 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1873,10 +1858,10 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1885,13 +1870,13 @@
     <xf numFmtId="178" fontId="8" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="8" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -1900,74 +1885,77 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="22" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="28" fillId="19" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="27" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="33" fillId="24" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="34" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="35" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="36" fillId="27" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="38" fillId="29" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="39" fillId="30" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="40" fillId="31" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="45" fillId="36" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="46" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="47" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="48" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="49" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="46" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="47" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="48" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="49" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="50" fillId="41" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="58" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="50" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="60" fillId="51" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1979,7 +1967,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="54" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="55" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1991,85 +1979,88 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="58" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="68" fillId="59" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="60" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="69" fillId="60" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="70" fillId="61" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="71" fillId="62" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="71" fillId="62" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="72" fillId="63" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="64" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="73" fillId="64" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="74" fillId="65" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="75" fillId="66" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="76" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="68" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="79" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="71" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="27" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2083,43 +2074,34 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="75" fillId="66" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2288,64 +2270,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>270</c:v>
-                </c:pt>
                 <c:pt idx="4">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>360</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>450</c:v>
-                </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>480.00000000000006</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>540</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>630</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>685.80000000000007</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>741.6</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>797.40000000000009</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>853.2</c:v>
+                  <c:v>660.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>909</c:v>
+                  <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>989.80000000000007</c:v>
+                  <c:v>880.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1070.5999999999999</c:v>
+                  <c:v>1040</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1151.4000000000001</c:v>
+                  <c:v>1200</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1232.2</c:v>
+                  <c:v>1360.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1313</c:v>
+                  <c:v>1520</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1393.8000000000002</c:v>
+                  <c:v>1680</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1474.6</c:v>
+                  <c:v>1840</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1555.4</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2464,64 +2446,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>120</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>240</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>360</c:v>
+                  <c:v>268.64999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>480</c:v>
+                  <c:v>356.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>600</c:v>
+                  <c:v>444.15</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>720</c:v>
+                  <c:v>531.9</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>840</c:v>
+                  <c:v>619.65</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>912</c:v>
+                  <c:v>707.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>984</c:v>
+                  <c:v>795.15</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1056</c:v>
+                  <c:v>882.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1128</c:v>
+                  <c:v>970.65000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1200</c:v>
+                  <c:v>1058.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1297</c:v>
+                  <c:v>1246.1500000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1394</c:v>
+                  <c:v>1433.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1491</c:v>
+                  <c:v>1621.65</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1588</c:v>
+                  <c:v>1809.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1685</c:v>
+                  <c:v>1997.1499999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1782</c:v>
+                  <c:v>2184.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1879</c:v>
+                  <c:v>2372.6499999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1976</c:v>
+                  <c:v>2560.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2640,64 +2622,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1137</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1224</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1311</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1398</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1485</c:v>
+                  <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1597</c:v>
+                  <c:v>1596.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1709</c:v>
+                  <c:v>1810.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1821</c:v>
+                  <c:v>2024.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1933</c:v>
+                  <c:v>2238.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2045</c:v>
+                  <c:v>2452.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2157</c:v>
+                  <c:v>2666.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2269</c:v>
+                  <c:v>2880.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2381</c:v>
+                  <c:v>3094.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2816,64 +2798,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>180</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>360</c:v>
+                  <c:v>300</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>540</c:v>
+                  <c:v>443.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>720</c:v>
+                  <c:v>582</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>900</c:v>
+                  <c:v>720.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1080</c:v>
+                  <c:v>859.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1260</c:v>
+                  <c:v>998.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1360.8000000000002</c:v>
+                  <c:v>1137</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1461.6000000000001</c:v>
+                  <c:v>1275.75</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1562.4</c:v>
+                  <c:v>1414.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1663.2000000000003</c:v>
+                  <c:v>1553.2500000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1764</c:v>
+                  <c:v>1692</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1889.8000000000002</c:v>
+                  <c:v>1930.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2015.6</c:v>
+                  <c:v>2169.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2141.4</c:v>
+                  <c:v>2408.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2267.2000000000003</c:v>
+                  <c:v>2647</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2393</c:v>
+                  <c:v>2885.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2518.8000000000002</c:v>
+                  <c:v>3124.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2644.6000000000004</c:v>
+                  <c:v>3363.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2770.4</c:v>
+                  <c:v>3602</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2992,64 +2974,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>210</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>420</c:v>
+                  <c:v>360</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>630</c:v>
+                  <c:v>529.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>840</c:v>
+                  <c:v>691.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1050</c:v>
+                  <c:v>853.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1260</c:v>
+                  <c:v>1015.1999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1470</c:v>
+                  <c:v>1177.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1583.4</c:v>
+                  <c:v>1339.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1696.8000000000002</c:v>
+                  <c:v>1501.2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1810.2</c:v>
+                  <c:v>1663.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1923.6000000000001</c:v>
+                  <c:v>1825.2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2037</c:v>
+                  <c:v>1987.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2175.4</c:v>
+                  <c:v>2249.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2313.8000000000002</c:v>
+                  <c:v>2511.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2452.1999999999998</c:v>
+                  <c:v>2773.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2590.6000000000004</c:v>
+                  <c:v>3035.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2729</c:v>
+                  <c:v>3297.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2867.4</c:v>
+                  <c:v>3559.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3005.8</c:v>
+                  <c:v>3821.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3144.2</c:v>
+                  <c:v>4083.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4460,52 +4442,52 @@
                   <c:v>220</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>274.12</c:v>
+                  <c:v>275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>326.91999999999996</c:v>
+                  <c:v>327.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>379.71999999999997</c:v>
+                  <c:v>380.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>432.52</c:v>
+                  <c:v>433.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>485.32</c:v>
+                  <c:v>486.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>538.12</c:v>
+                  <c:v>539</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>590.92000000000007</c:v>
+                  <c:v>591.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>643.72</c:v>
+                  <c:v>644.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>696.52</c:v>
+                  <c:v>697.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>749.31999999999994</c:v>
+                  <c:v>750.19999999999993</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>802.12</c:v>
+                  <c:v>803</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>854.92000000000007</c:v>
+                  <c:v>855.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>907.72</c:v>
+                  <c:v>908.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>960.5200000000001</c:v>
+                  <c:v>961.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1013.3199999999999</c:v>
+                  <c:v>1014.1999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1066.1199999999999</c:v>
+                  <c:v>1067</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4639,49 +4621,49 @@
                   <c:v>387.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>459.41999999999996</c:v>
+                  <c:v>461.90000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>530.72</c:v>
+                  <c:v>533.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>602.02</c:v>
+                  <c:v>604.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>673.31999999999994</c:v>
+                  <c:v>675.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>744.62</c:v>
+                  <c:v>747.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>815.92000000000007</c:v>
+                  <c:v>818.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>887.22</c:v>
+                  <c:v>889.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>958.52</c:v>
+                  <c:v>961</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1029.82</c:v>
+                  <c:v>1032.3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1101.1199999999999</c:v>
+                  <c:v>1103.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1172.42</c:v>
+                  <c:v>1174.9000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1243.7199999999998</c:v>
+                  <c:v>1246.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1315.02</c:v>
+                  <c:v>1317.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1386.32</c:v>
+                  <c:v>1388.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1457.62</c:v>
+                  <c:v>1460.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4815,49 +4797,49 @@
                   <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>595.19999999999993</c:v>
+                  <c:v>600</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>683.19999999999993</c:v>
+                  <c:v>688</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>771.2</c:v>
+                  <c:v>776</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>859.2</c:v>
+                  <c:v>864</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>947.19999999999993</c:v>
+                  <c:v>952</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1035.2</c:v>
+                  <c:v>1040</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1123.1999999999998</c:v>
+                  <c:v>1128</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1211.2</c:v>
+                  <c:v>1216</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1299.1999999999998</c:v>
+                  <c:v>1304</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1387.1999999999998</c:v>
+                  <c:v>1392</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1475.2</c:v>
+                  <c:v>1480</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1563.1999999999998</c:v>
+                  <c:v>1568</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1651.2</c:v>
+                  <c:v>1656.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1739.1999999999998</c:v>
+                  <c:v>1743.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1827.2</c:v>
+                  <c:v>1832</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4994,46 +4976,46 @@
                   <c:v>735</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>839.86</c:v>
+                  <c:v>847.69999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>942.76</c:v>
+                  <c:v>950.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1045.6600000000001</c:v>
+                  <c:v>1053.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1148.56</c:v>
+                  <c:v>1156.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1251.46</c:v>
+                  <c:v>1259.3000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1354.3600000000001</c:v>
+                  <c:v>1362.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1457.2600000000002</c:v>
+                  <c:v>1465.1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1560.1599999999999</c:v>
+                  <c:v>1568</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1663.06</c:v>
+                  <c:v>1670.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1765.96</c:v>
+                  <c:v>1773.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1868.8600000000001</c:v>
+                  <c:v>1876.6999999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1971.7600000000002</c:v>
+                  <c:v>1979.6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2074.66</c:v>
+                  <c:v>2082.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2177.56</c:v>
+                  <c:v>2185.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5170,46 +5152,46 @@
                   <c:v>870</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1003.3999999999999</c:v>
+                  <c:v>1014.9999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1119.4000000000001</c:v>
+                  <c:v>1131</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1235.4000000000001</c:v>
+                  <c:v>1247</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1351.4</c:v>
+                  <c:v>1363</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1467.4</c:v>
+                  <c:v>1479</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1583.3999999999999</c:v>
+                  <c:v>1595</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1699.4</c:v>
+                  <c:v>1711</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1815.3999999999999</c:v>
+                  <c:v>1827</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1931.4</c:v>
+                  <c:v>1943</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2047.4</c:v>
+                  <c:v>2059</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2163.4</c:v>
+                  <c:v>2175</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2279.4</c:v>
+                  <c:v>2291</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2395.3999999999996</c:v>
+                  <c:v>2407</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2511.3999999999996</c:v>
+                  <c:v>2523</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6413,52 +6395,52 @@
                   <c:v>-220</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-274.12</c:v>
+                  <c:v>-275</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-326.91999999999996</c:v>
+                  <c:v>-327.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-379.71999999999997</c:v>
+                  <c:v>-380.59999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-432.52</c:v>
+                  <c:v>-433.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-485.32</c:v>
+                  <c:v>-486.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-538.12</c:v>
+                  <c:v>-539</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-590.92000000000007</c:v>
+                  <c:v>-591.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-643.72</c:v>
+                  <c:v>-644.59999999999991</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-696.52</c:v>
+                  <c:v>-697.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-749.31999999999994</c:v>
+                  <c:v>-750.19999999999993</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-802.12</c:v>
+                  <c:v>-803</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-854.92000000000007</c:v>
+                  <c:v>-855.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-907.72</c:v>
+                  <c:v>-908.6</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-960.5200000000001</c:v>
+                  <c:v>-961.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1013.3199999999999</c:v>
+                  <c:v>-1014.1999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1066.1199999999999</c:v>
+                  <c:v>-1067</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6592,49 +6574,49 @@
                   <c:v>-387.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-459.41999999999996</c:v>
+                  <c:v>-461.90000000000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-530.72</c:v>
+                  <c:v>-533.20000000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-602.02</c:v>
+                  <c:v>-604.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-673.31999999999994</c:v>
+                  <c:v>-675.80000000000007</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-744.62</c:v>
+                  <c:v>-747.1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-815.92000000000007</c:v>
+                  <c:v>-818.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-887.22</c:v>
+                  <c:v>-889.7</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-958.52</c:v>
+                  <c:v>-961</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1029.82</c:v>
+                  <c:v>-1032.3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1101.1199999999999</c:v>
+                  <c:v>-1103.6000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1172.42</c:v>
+                  <c:v>-1174.9000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1243.7199999999998</c:v>
+                  <c:v>-1246.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1315.02</c:v>
+                  <c:v>-1317.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1386.32</c:v>
+                  <c:v>-1388.8</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1457.62</c:v>
+                  <c:v>-1460.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6768,49 +6750,49 @@
                   <c:v>-500</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-595.19999999999993</c:v>
+                  <c:v>-600</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-683.19999999999993</c:v>
+                  <c:v>-688</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-771.2</c:v>
+                  <c:v>-776</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-859.2</c:v>
+                  <c:v>-864</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-947.19999999999993</c:v>
+                  <c:v>-952</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1035.2</c:v>
+                  <c:v>-1040</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1123.1999999999998</c:v>
+                  <c:v>-1128</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1211.2</c:v>
+                  <c:v>-1216</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1299.1999999999998</c:v>
+                  <c:v>-1304</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1387.1999999999998</c:v>
+                  <c:v>-1392</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1475.2</c:v>
+                  <c:v>-1480</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1563.1999999999998</c:v>
+                  <c:v>-1568</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1651.2</c:v>
+                  <c:v>-1656.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1739.1999999999998</c:v>
+                  <c:v>-1743.9999999999998</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-1827.2</c:v>
+                  <c:v>-1832</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6947,46 +6929,46 @@
                   <c:v>-735</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-839.86</c:v>
+                  <c:v>-847.69999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-942.76</c:v>
+                  <c:v>-950.6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1045.6600000000001</c:v>
+                  <c:v>-1053.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1148.56</c:v>
+                  <c:v>-1156.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1251.46</c:v>
+                  <c:v>-1259.3000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1354.3600000000001</c:v>
+                  <c:v>-1362.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1457.2600000000002</c:v>
+                  <c:v>-1465.1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1560.1599999999999</c:v>
+                  <c:v>-1568</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1663.06</c:v>
+                  <c:v>-1670.9</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-1765.96</c:v>
+                  <c:v>-1773.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-1868.8600000000001</c:v>
+                  <c:v>-1876.6999999999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-1971.7600000000002</c:v>
+                  <c:v>-1979.6</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2074.66</c:v>
+                  <c:v>-2082.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2177.56</c:v>
+                  <c:v>-2185.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7123,46 +7105,46 @@
                   <c:v>-870</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1003.3999999999999</c:v>
+                  <c:v>-1014.9999999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-1119.4000000000001</c:v>
+                  <c:v>-1131</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1235.4000000000001</c:v>
+                  <c:v>-1247</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1351.4</c:v>
+                  <c:v>-1363</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-1467.4</c:v>
+                  <c:v>-1479</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-1583.3999999999999</c:v>
+                  <c:v>-1595</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-1699.4</c:v>
+                  <c:v>-1711</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-1815.3999999999999</c:v>
+                  <c:v>-1827</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-1931.4</c:v>
+                  <c:v>-1943</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-2047.4</c:v>
+                  <c:v>-2059</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-2163.4</c:v>
+                  <c:v>-2175</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-2279.4</c:v>
+                  <c:v>-2291</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-2395.3999999999996</c:v>
+                  <c:v>-2407</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-2511.3999999999996</c:v>
+                  <c:v>-2523</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7343,19 +7325,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -7378,25 +7355,20 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -7419,25 +7391,20 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -7460,25 +7427,20 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="10287000" cy="5143500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart">
@@ -7501,7 +7463,7 @@
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7726,14 +7688,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7784,7 +7746,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="82" t="s">
+      <c r="B6" s="84" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="6"/>
@@ -7804,7 +7766,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="82"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="6"/>
       <c r="D7" s="12" t="s">
         <v>79</v>
@@ -7938,30 +7900,30 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -8052,20 +8014,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -8092,18 +8054,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8134,13 +8096,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -8178,16 +8140,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="69"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70">
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="86">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>3181.44</v>
       </c>
-      <c r="J8" s="71"/>
+      <c r="J8" s="87"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -8225,16 +8187,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="69"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="70">
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="86">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
-        <v>1827.2</v>
-      </c>
-      <c r="J10" s="71"/>
+        <v>1832</v>
+      </c>
+      <c r="J10" s="87"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -8286,13 +8248,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="66" t="s">
+      <c r="F13" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -8310,11 +8272,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
       <c r="I14" s="32">
         <f>Samples!F165</f>
         <v>2400</v>
@@ -8339,11 +8301,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="69" t="s">
+      <c r="F15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
       <c r="I15" s="33">
         <f>Samples!I165</f>
         <v>2280</v>
@@ -8363,11 +8325,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="75" t="s">
+      <c r="F16" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
       <c r="I16" s="32">
         <f>Samples!J165</f>
         <v>2240</v>
@@ -8387,11 +8349,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="65"/>
       <c r="I17" s="33">
         <f>Samples!L165</f>
         <v>4520</v>
@@ -8433,11 +8395,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
+      <c r="G19" s="72"/>
+      <c r="H19" s="72"/>
       <c r="I19" s="32">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -8457,11 +8419,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="69" t="s">
+      <c r="F20" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
       <c r="I20" s="33">
         <f>Samples!P165</f>
         <v>1760</v>
@@ -8498,11 +8460,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="75" t="s">
+      <c r="F22" s="71" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
       <c r="I22" s="35">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -8522,11 +8484,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="68" t="s">
+      <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
       <c r="I23" s="36">
         <f>Samples!K165</f>
         <v>0.60399999999999998</v>
@@ -8546,14 +8508,14 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="72" t="s">
+      <c r="F24" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
       <c r="I24" s="35">
         <f>Samples!N165</f>
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="J24" s="23" t="s">
         <v>12</v>
@@ -8600,20 +8562,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="76" t="s">
+      <c r="B27" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="77"/>
-      <c r="L27" s="77"/>
-      <c r="M27" s="77"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="90"/>
+      <c r="F27" s="90"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -8948,20 +8910,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -8988,18 +8950,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9029,15 +8991,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9621,18 +9583,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
+      <c r="B41" s="91"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9706,20 +9668,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -9749,15 +9711,15 @@
         <v>4</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9787,15 +9749,15 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10379,18 +10341,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
+      <c r="B41" s="91"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10464,20 +10426,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -10507,15 +10469,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10538,18 +10500,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="78"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -11133,18 +11095,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
+      <c r="B41" s="91"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11214,20 +11176,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -11257,15 +11219,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="85"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11288,18 +11250,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="78"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="78"/>
-      <c r="J6" s="78"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="78"/>
-      <c r="M6" s="78"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -11883,18 +11845,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
+      <c r="B41" s="91"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11968,40 +11930,40 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="85"/>
-      <c r="J3" s="85"/>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
-      <c r="N3" s="85"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -12025,21 +11987,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="67" t="s">
+      <c r="J5" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -12554,21 +12516,21 @@
         <v>12</v>
       </c>
       <c r="D18" s="40">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="E18" s="36">
         <f>(D18+F18)/2</f>
-        <v>0.255</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="F18" s="40">
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="G18" s="36">
         <f>(F18+H18)/2</f>
-        <v>0.30500000000000005</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="H18" s="40">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="40">
@@ -12671,73 +12633,73 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="67"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="69"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="73"/>
+      <c r="C23" s="72"/>
       <c r="D23" s="29">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="86" t="s">
+      <c r="F23" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="87"/>
-      <c r="H23" s="87"/>
-      <c r="I23" s="87"/>
-      <c r="J23" s="87"/>
-      <c r="K23" s="87"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="87"/>
-      <c r="N23" s="87"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="75"/>
+      <c r="K23" s="75"/>
+      <c r="L23" s="75"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="75"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="74"/>
+      <c r="C24" s="65"/>
       <c r="D24" s="31">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="87"/>
-      <c r="N24" s="87"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="75"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="75"/>
+      <c r="L24" s="75"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="73"/>
+      <c r="C25" s="72"/>
       <c r="D25" s="29">
         <v>40</v>
       </c>
@@ -12755,33 +12717,33 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="74"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="31">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="88" t="s">
+      <c r="F26" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="74"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="31">
         <v>10</v>
       </c>
@@ -12799,140 +12761,140 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="90" t="s">
+      <c r="B28" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="91"/>
-      <c r="L28" s="91"/>
-      <c r="M28" s="91"/>
-      <c r="N28" s="91"/>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="89"/>
-      <c r="C29" s="89"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="89"/>
-      <c r="F29" s="89"/>
-      <c r="G29" s="89"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="89"/>
-      <c r="K29" s="89"/>
-      <c r="L29" s="89"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="89"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77"/>
+      <c r="M29" s="77"/>
+      <c r="N29" s="77"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="92"/>
-      <c r="C30" s="92"/>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="92"/>
-      <c r="G30" s="92"/>
-      <c r="H30" s="92"/>
-      <c r="I30" s="92"/>
-      <c r="J30" s="92"/>
-      <c r="K30" s="92"/>
-      <c r="L30" s="92"/>
-      <c r="M30" s="92"/>
-      <c r="N30" s="92"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="89"/>
-      <c r="C31" s="89"/>
-      <c r="D31" s="89"/>
-      <c r="E31" s="89"/>
-      <c r="F31" s="89"/>
-      <c r="G31" s="89"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="89"/>
-      <c r="K31" s="89"/>
-      <c r="L31" s="89"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="89"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="77"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="77"/>
+      <c r="M31" s="77"/>
+      <c r="N31" s="77"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="89"/>
-      <c r="C32" s="89"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="89"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="89"/>
-      <c r="K32" s="89"/>
-      <c r="L32" s="89"/>
-      <c r="M32" s="89"/>
-      <c r="N32" s="89"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77"/>
+      <c r="M32" s="77"/>
+      <c r="N32" s="77"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="89"/>
-      <c r="C33" s="89"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="89"/>
-      <c r="K33" s="89"/>
-      <c r="L33" s="89"/>
-      <c r="M33" s="89"/>
-      <c r="N33" s="89"/>
+      <c r="B33" s="77"/>
+      <c r="C33" s="77"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="77"/>
+      <c r="K33" s="77"/>
+      <c r="L33" s="77"/>
+      <c r="M33" s="77"/>
+      <c r="N33" s="77"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="89"/>
-      <c r="C34" s="89"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="89"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="89"/>
-      <c r="M34" s="89"/>
-      <c r="N34" s="89"/>
+      <c r="B34" s="77"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
+      <c r="N34" s="77"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="89"/>
-      <c r="J35" s="89"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="89"/>
-      <c r="M35" s="89"/>
-      <c r="N35" s="89"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+      <c r="I35" s="77"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="77"/>
+      <c r="M35" s="77"/>
+      <c r="N35" s="77"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -13080,29 +13042,29 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="93"/>
-      <c r="K1" s="93"/>
-      <c r="L1" s="93"/>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
+      <c r="U1" s="93"/>
+      <c r="V1" s="93"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -13238,23 +13200,23 @@
       </c>
       <c r="F5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q5)+(INDEX(Parameters!$J$10:$N$10,1,Q5+1)-INDEX(Parameters!$J$10:$N$10,1,Q5))*T5,INDEX(Parameters!$D$10:$H$10,1,Q5)+(INDEX(Parameters!$D$10:$H$10,1,Q5+1)-INDEX(Parameters!$D$10:$H$10,1,Q5))*T5)</f>
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="G5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R5)+(INDEX(Parameters!$J$11:$N$11,1,R5+1)-INDEX(Parameters!$J$11:$N$11,1,R5))*U5,INDEX(Parameters!$D$11:$H$11,1,Q5)+(INDEX(Parameters!$D$11:$H$11,1,Q5+1)-INDEX(Parameters!$D$11:$H$11,1,Q5))*T5)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q5)+(INDEX(Parameters!$J$12:$N$12,1,Q5+1)-INDEX(Parameters!$J$12:$N$12,1,Q5))*T5,INDEX(Parameters!$D$12:$H$12,1,Q5)+(INDEX(Parameters!$D$12:$H$12,1,Q5+1)-INDEX(Parameters!$D$12:$H$12,1,Q5))*T5)</f>
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="I5" s="49">
         <f>F5*H5</f>
-        <v>1116</v>
+        <v>1200</v>
       </c>
       <c r="J5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -13262,19 +13224,19 @@
       </c>
       <c r="L5" s="49">
         <f>I5+J5</f>
-        <v>1616</v>
+        <v>3200</v>
       </c>
       <c r="M5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="N5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S5)+(INDEX(Parameters!$J$18:$N$18,1,S5+1)-INDEX(Parameters!$J$18:$N$18,1,S5))*V5,INDEX(Parameters!$D$18:$H$18,1,S5)+(INDEX(Parameters!$D$18:$H$18,1,S5+1)-INDEX(Parameters!$D$18:$H$18,1,S5))*V5)</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S5)+(INDEX(Parameters!$J$19:$N$19,1,S5+1)-INDEX(Parameters!$J$19:$N$19,1,S5))*V5,INDEX(Parameters!$D$19:$H$19,1,S5)+(INDEX(Parameters!$D$19:$H$19,1,S5+1)-INDEX(Parameters!$D$19:$H$19,1,S5))*V5)</f>
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="P5" s="50">
         <f>M5*O5</f>
@@ -13325,23 +13287,23 @@
       </c>
       <c r="F6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q6)+(INDEX(Parameters!$J$10:$N$10,1,Q6+1)-INDEX(Parameters!$J$10:$N$10,1,Q6))*T6,INDEX(Parameters!$D$10:$H$10,1,Q6)+(INDEX(Parameters!$D$10:$H$10,1,Q6+1)-INDEX(Parameters!$D$10:$H$10,1,Q6))*T6)</f>
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="G6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R6)+(INDEX(Parameters!$J$11:$N$11,1,R6+1)-INDEX(Parameters!$J$11:$N$11,1,R6))*U6,INDEX(Parameters!$D$11:$H$11,1,Q6)+(INDEX(Parameters!$D$11:$H$11,1,Q6+1)-INDEX(Parameters!$D$11:$H$11,1,Q6))*T6)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q6)+(INDEX(Parameters!$J$12:$N$12,1,Q6+1)-INDEX(Parameters!$J$12:$N$12,1,Q6))*T6,INDEX(Parameters!$D$12:$H$12,1,Q6)+(INDEX(Parameters!$D$12:$H$12,1,Q6+1)-INDEX(Parameters!$D$12:$H$12,1,Q6))*T6)</f>
-        <v>0.6</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="I6" s="51">
         <f>F6*H6</f>
-        <v>1440</v>
+        <v>1755</v>
       </c>
       <c r="J6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -13349,23 +13311,23 @@
       </c>
       <c r="L6" s="51">
         <f>I6+J6</f>
-        <v>1940</v>
+        <v>3755</v>
       </c>
       <c r="M6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
-        <v>2050</v>
+        <v>1550</v>
       </c>
       <c r="N6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S6)+(INDEX(Parameters!$J$18:$N$18,1,S6+1)-INDEX(Parameters!$J$18:$N$18,1,S6))*V6,INDEX(Parameters!$D$18:$H$18,1,S6)+(INDEX(Parameters!$D$18:$H$18,1,S6+1)-INDEX(Parameters!$D$18:$H$18,1,S6))*V6)</f>
-        <v>0.22500000000000001</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S6)+(INDEX(Parameters!$J$19:$N$19,1,S6+1)-INDEX(Parameters!$J$19:$N$19,1,S6))*V6,INDEX(Parameters!$D$19:$H$19,1,S6)+(INDEX(Parameters!$D$19:$H$19,1,S6+1)-INDEX(Parameters!$D$19:$H$19,1,S6))*V6)</f>
-        <v>0.62</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="P6" s="52">
         <f>M6*O6</f>
-        <v>1271</v>
+        <v>1426</v>
       </c>
       <c r="Q6" s="52">
         <f>MIN(4,MAX(1,INT((1+C6/Parameters!$D$23)*4)+1))</f>
@@ -13412,23 +13374,23 @@
       </c>
       <c r="F7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q7)+(INDEX(Parameters!$J$10:$N$10,1,Q7+1)-INDEX(Parameters!$J$10:$N$10,1,Q7))*T7,INDEX(Parameters!$D$10:$H$10,1,Q7)+(INDEX(Parameters!$D$10:$H$10,1,Q7+1)-INDEX(Parameters!$D$10:$H$10,1,Q7))*T7)</f>
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R7)+(INDEX(Parameters!$J$11:$N$11,1,R7+1)-INDEX(Parameters!$J$11:$N$11,1,R7))*U7,INDEX(Parameters!$D$11:$H$11,1,Q7)+(INDEX(Parameters!$D$11:$H$11,1,Q7+1)-INDEX(Parameters!$D$11:$H$11,1,Q7))*T7)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q7)+(INDEX(Parameters!$J$12:$N$12,1,Q7+1)-INDEX(Parameters!$J$12:$N$12,1,Q7))*T7,INDEX(Parameters!$D$12:$H$12,1,Q7)+(INDEX(Parameters!$D$12:$H$12,1,Q7+1)-INDEX(Parameters!$D$12:$H$12,1,Q7))*T7)</f>
-        <v>0.57999999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="I7" s="49">
         <f>F7*H7</f>
-        <v>1739.9999999999998</v>
+        <v>2280</v>
       </c>
       <c r="J7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -13436,23 +13398,23 @@
       </c>
       <c r="L7" s="49">
         <f>I7+J7</f>
-        <v>2240</v>
+        <v>4280</v>
       </c>
       <c r="M7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S7)+(INDEX(Parameters!$J$18:$N$18,1,S7+1)-INDEX(Parameters!$J$18:$N$18,1,S7))*V7,INDEX(Parameters!$D$18:$H$18,1,S7)+(INDEX(Parameters!$D$18:$H$18,1,S7+1)-INDEX(Parameters!$D$18:$H$18,1,S7))*V7)</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="O7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S7)+(INDEX(Parameters!$J$19:$N$19,1,S7+1)-INDEX(Parameters!$J$19:$N$19,1,S7))*V7,INDEX(Parameters!$D$19:$H$19,1,S7)+(INDEX(Parameters!$D$19:$H$19,1,S7+1)-INDEX(Parameters!$D$19:$H$19,1,S7))*V7)</f>
-        <v>0.57999999999999996</v>
+        <v>0.88</v>
       </c>
       <c r="P7" s="50">
         <f>M7*O7</f>
-        <v>1450</v>
+        <v>1760</v>
       </c>
       <c r="Q7" s="50">
         <f>MIN(4,MAX(1,INT((1+C7/Parameters!$D$23)*4)+1))</f>
@@ -13499,23 +13461,23 @@
       </c>
       <c r="F8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q8)+(INDEX(Parameters!$J$10:$N$10,1,Q8+1)-INDEX(Parameters!$J$10:$N$10,1,Q8))*T8,INDEX(Parameters!$D$10:$H$10,1,Q8)+(INDEX(Parameters!$D$10:$H$10,1,Q8+1)-INDEX(Parameters!$D$10:$H$10,1,Q8))*T8)</f>
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="G8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R8)+(INDEX(Parameters!$J$11:$N$11,1,R8+1)-INDEX(Parameters!$J$11:$N$11,1,R8))*U8,INDEX(Parameters!$D$11:$H$11,1,Q8)+(INDEX(Parameters!$D$11:$H$11,1,Q8+1)-INDEX(Parameters!$D$11:$H$11,1,Q8))*T8)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q8)+(INDEX(Parameters!$J$12:$N$12,1,Q8+1)-INDEX(Parameters!$J$12:$N$12,1,Q8))*T8,INDEX(Parameters!$D$12:$H$12,1,Q8)+(INDEX(Parameters!$D$12:$H$12,1,Q8+1)-INDEX(Parameters!$D$12:$H$12,1,Q8))*T8)</f>
-        <v>0.56000000000000005</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="I8" s="51">
         <f>F8*H8</f>
-        <v>2016.0000000000002</v>
+        <v>2775</v>
       </c>
       <c r="J8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -13523,23 +13485,23 @@
       </c>
       <c r="L8" s="51">
         <f>I8+J8</f>
-        <v>2516</v>
+        <v>4775</v>
       </c>
       <c r="M8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
-        <v>2950</v>
+        <v>2450</v>
       </c>
       <c r="N8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S8)+(INDEX(Parameters!$J$18:$N$18,1,S8+1)-INDEX(Parameters!$J$18:$N$18,1,S8))*V8,INDEX(Parameters!$D$18:$H$18,1,S8)+(INDEX(Parameters!$D$18:$H$18,1,S8+1)-INDEX(Parameters!$D$18:$H$18,1,S8))*V8)</f>
-        <v>0.27500000000000002</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="O8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S8)+(INDEX(Parameters!$J$19:$N$19,1,S8+1)-INDEX(Parameters!$J$19:$N$19,1,S8))*V8,INDEX(Parameters!$D$19:$H$19,1,S8)+(INDEX(Parameters!$D$19:$H$19,1,S8+1)-INDEX(Parameters!$D$19:$H$19,1,S8))*V8)</f>
-        <v>0.54</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P8" s="52">
         <f>M8*O8</f>
-        <v>1593</v>
+        <v>2058</v>
       </c>
       <c r="Q8" s="52">
         <f>MIN(4,MAX(1,INT((1+C8/Parameters!$D$23)*4)+1))</f>
@@ -13586,23 +13548,23 @@
       </c>
       <c r="F9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q9)+(INDEX(Parameters!$J$10:$N$10,1,Q9+1)-INDEX(Parameters!$J$10:$N$10,1,Q9))*T9,INDEX(Parameters!$D$10:$H$10,1,Q9)+(INDEX(Parameters!$D$10:$H$10,1,Q9+1)-INDEX(Parameters!$D$10:$H$10,1,Q9))*T9)</f>
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="G9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R9)+(INDEX(Parameters!$J$11:$N$11,1,R9+1)-INDEX(Parameters!$J$11:$N$11,1,R9))*U9,INDEX(Parameters!$D$11:$H$11,1,Q9)+(INDEX(Parameters!$D$11:$H$11,1,Q9+1)-INDEX(Parameters!$D$11:$H$11,1,Q9))*T9)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q9)+(INDEX(Parameters!$J$12:$N$12,1,Q9+1)-INDEX(Parameters!$J$12:$N$12,1,Q9))*T9,INDEX(Parameters!$D$12:$H$12,1,Q9)+(INDEX(Parameters!$D$12:$H$12,1,Q9+1)-INDEX(Parameters!$D$12:$H$12,1,Q9))*T9)</f>
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="I9" s="49">
         <f>F9*H9</f>
-        <v>2268</v>
+        <v>3240</v>
       </c>
       <c r="J9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -13610,23 +13572,23 @@
       </c>
       <c r="L9" s="49">
         <f>I9+J9</f>
-        <v>2768</v>
+        <v>5240</v>
       </c>
       <c r="M9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="N9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S9)+(INDEX(Parameters!$J$18:$N$18,1,S9+1)-INDEX(Parameters!$J$18:$N$18,1,S9))*V9,INDEX(Parameters!$D$18:$H$18,1,S9)+(INDEX(Parameters!$D$18:$H$18,1,S9+1)-INDEX(Parameters!$D$18:$H$18,1,S9))*V9)</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S9)+(INDEX(Parameters!$J$19:$N$19,1,S9+1)-INDEX(Parameters!$J$19:$N$19,1,S9))*V9,INDEX(Parameters!$D$19:$H$19,1,S9)+(INDEX(Parameters!$D$19:$H$19,1,S9+1)-INDEX(Parameters!$D$19:$H$19,1,S9))*V9)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P9" s="50">
         <f>M9*O9</f>
-        <v>1700</v>
+        <v>2320</v>
       </c>
       <c r="Q9" s="50">
         <f>MIN(4,MAX(1,INT((1+C9/Parameters!$D$23)*4)+1))</f>
@@ -13814,23 +13776,23 @@
       </c>
       <c r="C15" s="56">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D15" s="56">
         <f t="shared" si="1"/>
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E15" s="56">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F15" s="56">
         <f t="shared" si="3"/>
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G15" s="56">
         <f t="shared" si="4"/>
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -13855,23 +13817,23 @@
       </c>
       <c r="C16" s="55">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="D16" s="55">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="E16" s="55">
         <f t="shared" si="2"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="F16" s="55">
         <f t="shared" si="3"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="G16" s="55">
         <f t="shared" si="4"/>
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -13896,23 +13858,23 @@
       </c>
       <c r="C17" s="56">
         <f t="shared" si="0"/>
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="D17" s="56">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>268.64999999999998</v>
       </c>
       <c r="E17" s="56">
         <f t="shared" si="2"/>
-        <v>450</v>
+        <v>356.4</v>
       </c>
       <c r="F17" s="56">
         <f t="shared" si="3"/>
-        <v>540</v>
+        <v>443.25</v>
       </c>
       <c r="G17" s="56">
         <f t="shared" si="4"/>
-        <v>630</v>
+        <v>529.20000000000005</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -13937,23 +13899,23 @@
       </c>
       <c r="C18" s="55">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="D18" s="55">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>356.40000000000003</v>
       </c>
       <c r="E18" s="55">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="F18" s="55">
         <f t="shared" si="3"/>
-        <v>720</v>
+        <v>582</v>
       </c>
       <c r="G18" s="55">
         <f t="shared" si="4"/>
-        <v>840</v>
+        <v>691.2</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -13978,23 +13940,23 @@
       </c>
       <c r="C19" s="56">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="D19" s="56">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>444.15</v>
       </c>
       <c r="E19" s="56">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="F19" s="56">
         <f t="shared" si="3"/>
-        <v>900</v>
+        <v>720.75</v>
       </c>
       <c r="G19" s="56">
         <f t="shared" si="4"/>
-        <v>1050</v>
+        <v>853.2</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -14019,23 +13981,23 @@
       </c>
       <c r="C20" s="55">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="D20" s="55">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>531.9</v>
       </c>
       <c r="E20" s="55">
         <f t="shared" si="2"/>
-        <v>900</v>
+        <v>698.4</v>
       </c>
       <c r="F20" s="55">
         <f t="shared" si="3"/>
-        <v>1080</v>
+        <v>859.5</v>
       </c>
       <c r="G20" s="55">
         <f t="shared" si="4"/>
-        <v>1260</v>
+        <v>1015.1999999999999</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -14060,23 +14022,23 @@
       </c>
       <c r="C21" s="56">
         <f t="shared" si="0"/>
-        <v>630</v>
+        <v>420</v>
       </c>
       <c r="D21" s="56">
         <f t="shared" si="1"/>
-        <v>840</v>
+        <v>619.65</v>
       </c>
       <c r="E21" s="56">
         <f t="shared" si="2"/>
-        <v>1050</v>
+        <v>812.4</v>
       </c>
       <c r="F21" s="56">
         <f t="shared" si="3"/>
-        <v>1260</v>
+        <v>998.25</v>
       </c>
       <c r="G21" s="56">
         <f t="shared" si="4"/>
-        <v>1470</v>
+        <v>1177.1999999999998</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -14101,23 +14063,23 @@
       </c>
       <c r="C22" s="55">
         <f t="shared" si="0"/>
-        <v>685.80000000000007</v>
+        <v>480.00000000000006</v>
       </c>
       <c r="D22" s="55">
         <f t="shared" si="1"/>
-        <v>912</v>
+        <v>707.40000000000009</v>
       </c>
       <c r="E22" s="55">
         <f t="shared" si="2"/>
-        <v>1137</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="F22" s="55">
         <f t="shared" si="3"/>
-        <v>1360.8000000000002</v>
+        <v>1137</v>
       </c>
       <c r="G22" s="55">
         <f t="shared" si="4"/>
-        <v>1583.4</v>
+        <v>1339.2</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -14142,23 +14104,23 @@
       </c>
       <c r="C23" s="56">
         <f t="shared" si="0"/>
-        <v>741.6</v>
+        <v>540</v>
       </c>
       <c r="D23" s="56">
         <f t="shared" si="1"/>
-        <v>984</v>
+        <v>795.15</v>
       </c>
       <c r="E23" s="56">
         <f t="shared" si="2"/>
-        <v>1224</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="F23" s="56">
         <f t="shared" si="3"/>
-        <v>1461.6000000000001</v>
+        <v>1275.75</v>
       </c>
       <c r="G23" s="56">
         <f t="shared" si="4"/>
-        <v>1696.8000000000002</v>
+        <v>1501.2</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -14183,23 +14145,23 @@
       </c>
       <c r="C24" s="55">
         <f t="shared" si="0"/>
-        <v>797.40000000000009</v>
+        <v>600</v>
       </c>
       <c r="D24" s="55">
         <f t="shared" si="1"/>
-        <v>1056</v>
+        <v>882.9</v>
       </c>
       <c r="E24" s="55">
         <f t="shared" si="2"/>
-        <v>1311</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="F24" s="55">
         <f t="shared" si="3"/>
-        <v>1562.4</v>
+        <v>1414.5</v>
       </c>
       <c r="G24" s="55">
         <f t="shared" si="4"/>
-        <v>1810.2</v>
+        <v>1663.2</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -14224,23 +14186,23 @@
       </c>
       <c r="C25" s="56">
         <f t="shared" si="0"/>
-        <v>853.2</v>
+        <v>660.00000000000011</v>
       </c>
       <c r="D25" s="56">
         <f t="shared" si="1"/>
-        <v>1128</v>
+        <v>970.65000000000009</v>
       </c>
       <c r="E25" s="56">
         <f t="shared" si="2"/>
-        <v>1398</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="F25" s="56">
         <f t="shared" si="3"/>
-        <v>1663.2000000000003</v>
+        <v>1553.2500000000002</v>
       </c>
       <c r="G25" s="56">
         <f t="shared" si="4"/>
-        <v>1923.6000000000001</v>
+        <v>1825.2</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -14265,23 +14227,23 @@
       </c>
       <c r="C26" s="55">
         <f t="shared" si="0"/>
-        <v>909</v>
+        <v>720</v>
       </c>
       <c r="D26" s="55">
         <f t="shared" si="1"/>
-        <v>1200</v>
+        <v>1058.4000000000001</v>
       </c>
       <c r="E26" s="55">
         <f t="shared" si="2"/>
-        <v>1485</v>
+        <v>1382.3999999999999</v>
       </c>
       <c r="F26" s="55">
         <f t="shared" si="3"/>
-        <v>1764</v>
+        <v>1692</v>
       </c>
       <c r="G26" s="55">
         <f t="shared" si="4"/>
-        <v>2037</v>
+        <v>1987.2</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -14306,23 +14268,23 @@
       </c>
       <c r="C27" s="56">
         <f t="shared" si="0"/>
-        <v>989.80000000000007</v>
+        <v>880.00000000000011</v>
       </c>
       <c r="D27" s="56">
         <f t="shared" si="1"/>
-        <v>1297</v>
+        <v>1246.1500000000001</v>
       </c>
       <c r="E27" s="56">
         <f t="shared" si="2"/>
-        <v>1597</v>
+        <v>1596.4</v>
       </c>
       <c r="F27" s="56">
         <f t="shared" si="3"/>
-        <v>1889.8000000000002</v>
+        <v>1930.75</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="4"/>
-        <v>2175.4</v>
+        <v>2249.1999999999998</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -14347,23 +14309,23 @@
       </c>
       <c r="C28" s="55">
         <f t="shared" si="0"/>
-        <v>1070.5999999999999</v>
+        <v>1040</v>
       </c>
       <c r="D28" s="55">
         <f t="shared" si="1"/>
-        <v>1394</v>
+        <v>1433.9</v>
       </c>
       <c r="E28" s="55">
         <f t="shared" si="2"/>
-        <v>1709</v>
+        <v>1810.3999999999999</v>
       </c>
       <c r="F28" s="55">
         <f t="shared" si="3"/>
-        <v>2015.6</v>
+        <v>2169.5</v>
       </c>
       <c r="G28" s="55">
         <f t="shared" si="4"/>
-        <v>2313.8000000000002</v>
+        <v>2511.1999999999998</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -14388,23 +14350,23 @@
       </c>
       <c r="C29" s="56">
         <f t="shared" si="0"/>
-        <v>1151.4000000000001</v>
+        <v>1200</v>
       </c>
       <c r="D29" s="56">
         <f t="shared" si="1"/>
-        <v>1491</v>
+        <v>1621.65</v>
       </c>
       <c r="E29" s="56">
         <f t="shared" si="2"/>
-        <v>1821</v>
+        <v>2024.4</v>
       </c>
       <c r="F29" s="56">
         <f t="shared" si="3"/>
-        <v>2141.4</v>
+        <v>2408.25</v>
       </c>
       <c r="G29" s="56">
         <f t="shared" si="4"/>
-        <v>2452.1999999999998</v>
+        <v>2773.2</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -14429,23 +14391,23 @@
       </c>
       <c r="C30" s="55">
         <f t="shared" si="0"/>
-        <v>1232.2</v>
+        <v>1360.0000000000002</v>
       </c>
       <c r="D30" s="55">
         <f t="shared" si="1"/>
-        <v>1588</v>
+        <v>1809.4</v>
       </c>
       <c r="E30" s="55">
         <f t="shared" si="2"/>
-        <v>1933</v>
+        <v>2238.4</v>
       </c>
       <c r="F30" s="55">
         <f t="shared" si="3"/>
-        <v>2267.2000000000003</v>
+        <v>2647</v>
       </c>
       <c r="G30" s="55">
         <f t="shared" si="4"/>
-        <v>2590.6000000000004</v>
+        <v>3035.2000000000003</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -14470,23 +14432,23 @@
       </c>
       <c r="C31" s="56">
         <f t="shared" si="0"/>
-        <v>1313</v>
+        <v>1520</v>
       </c>
       <c r="D31" s="56">
         <f t="shared" si="1"/>
-        <v>1685</v>
+        <v>1997.1499999999999</v>
       </c>
       <c r="E31" s="56">
         <f t="shared" si="2"/>
-        <v>2045</v>
+        <v>2452.3999999999996</v>
       </c>
       <c r="F31" s="56">
         <f t="shared" si="3"/>
-        <v>2393</v>
+        <v>2885.75</v>
       </c>
       <c r="G31" s="56">
         <f t="shared" si="4"/>
-        <v>2729</v>
+        <v>3297.2</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -14511,23 +14473,23 @@
       </c>
       <c r="C32" s="55">
         <f t="shared" si="0"/>
-        <v>1393.8000000000002</v>
+        <v>1680</v>
       </c>
       <c r="D32" s="55">
         <f t="shared" si="1"/>
-        <v>1782</v>
+        <v>2184.9</v>
       </c>
       <c r="E32" s="55">
         <f t="shared" si="2"/>
-        <v>2157</v>
+        <v>2666.4</v>
       </c>
       <c r="F32" s="55">
         <f t="shared" si="3"/>
-        <v>2518.8000000000002</v>
+        <v>3124.5</v>
       </c>
       <c r="G32" s="55">
         <f t="shared" si="4"/>
-        <v>2867.4</v>
+        <v>3559.2000000000003</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -14552,23 +14514,23 @@
       </c>
       <c r="C33" s="56">
         <f t="shared" si="0"/>
-        <v>1474.6</v>
+        <v>1840</v>
       </c>
       <c r="D33" s="56">
         <f t="shared" si="1"/>
-        <v>1879</v>
+        <v>2372.6499999999996</v>
       </c>
       <c r="E33" s="56">
         <f t="shared" si="2"/>
-        <v>2269</v>
+        <v>2880.3999999999996</v>
       </c>
       <c r="F33" s="56">
         <f t="shared" si="3"/>
-        <v>2644.6000000000004</v>
+        <v>3363.25</v>
       </c>
       <c r="G33" s="56">
         <f t="shared" si="4"/>
-        <v>3005.8</v>
+        <v>3821.2</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -14593,23 +14555,23 @@
       </c>
       <c r="C34" s="55">
         <f t="shared" si="0"/>
-        <v>1555.4</v>
+        <v>2000</v>
       </c>
       <c r="D34" s="55">
         <f t="shared" si="1"/>
-        <v>1976</v>
+        <v>2560.4</v>
       </c>
       <c r="E34" s="55">
         <f t="shared" si="2"/>
-        <v>2381</v>
+        <v>3094.4</v>
       </c>
       <c r="F34" s="55">
         <f t="shared" si="3"/>
-        <v>2770.4</v>
+        <v>3602</v>
       </c>
       <c r="G34" s="55">
         <f t="shared" si="4"/>
-        <v>3144.2</v>
+        <v>4083.2</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -14773,29 +14735,29 @@
     </row>
     <row r="41" spans="1:22" ht="32" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="93"/>
-      <c r="D41" s="93"/>
-      <c r="E41" s="93"/>
-      <c r="F41" s="93"/>
-      <c r="G41" s="93"/>
-      <c r="H41" s="93"/>
-      <c r="I41" s="93"/>
-      <c r="J41" s="93"/>
-      <c r="K41" s="93"/>
-      <c r="L41" s="93"/>
-      <c r="M41" s="93"/>
-      <c r="N41" s="93"/>
-      <c r="O41" s="93"/>
-      <c r="P41" s="94"/>
-      <c r="Q41" s="94"/>
-      <c r="R41" s="94"/>
-      <c r="S41" s="94"/>
-      <c r="T41" s="94"/>
-      <c r="U41" s="94"/>
-      <c r="V41" s="94"/>
+      <c r="C41" s="92"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+      <c r="M41" s="92"/>
+      <c r="N41" s="92"/>
+      <c r="O41" s="92"/>
+      <c r="P41" s="93"/>
+      <c r="Q41" s="93"/>
+      <c r="R41" s="93"/>
+      <c r="S41" s="93"/>
+      <c r="T41" s="93"/>
+      <c r="U41" s="93"/>
+      <c r="V41" s="93"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -16427,29 +16389,29 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="94" t="s">
+      <c r="B81" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="C81" s="94"/>
-      <c r="D81" s="94"/>
-      <c r="E81" s="94"/>
-      <c r="F81" s="94"/>
-      <c r="G81" s="94"/>
-      <c r="H81" s="94"/>
-      <c r="I81" s="94"/>
-      <c r="J81" s="94"/>
-      <c r="K81" s="94"/>
-      <c r="L81" s="94"/>
-      <c r="M81" s="94"/>
-      <c r="N81" s="94"/>
-      <c r="O81" s="94"/>
-      <c r="P81" s="94"/>
-      <c r="Q81" s="94"/>
-      <c r="R81" s="94"/>
-      <c r="S81" s="94"/>
-      <c r="T81" s="94"/>
-      <c r="U81" s="94"/>
-      <c r="V81" s="94"/>
+      <c r="C81" s="93"/>
+      <c r="D81" s="93"/>
+      <c r="E81" s="93"/>
+      <c r="F81" s="93"/>
+      <c r="G81" s="93"/>
+      <c r="H81" s="93"/>
+      <c r="I81" s="93"/>
+      <c r="J81" s="93"/>
+      <c r="K81" s="93"/>
+      <c r="L81" s="93"/>
+      <c r="M81" s="93"/>
+      <c r="N81" s="93"/>
+      <c r="O81" s="93"/>
+      <c r="P81" s="93"/>
+      <c r="Q81" s="93"/>
+      <c r="R81" s="93"/>
+      <c r="S81" s="93"/>
+      <c r="T81" s="93"/>
+      <c r="U81" s="93"/>
+      <c r="V81" s="93"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -16613,7 +16575,7 @@
       </c>
       <c r="N85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S85)+(INDEX(Parameters!$J$18:$N$18,1,S85+1)-INDEX(Parameters!$J$18:$N$18,1,S85))*V85,INDEX(Parameters!$D$18:$H$18,1,S85)+(INDEX(Parameters!$D$18:$H$18,1,S85+1)-INDEX(Parameters!$D$18:$H$18,1,S85))*V85)</f>
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="O85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S85)+(INDEX(Parameters!$J$19:$N$19,1,S85+1)-INDEX(Parameters!$J$19:$N$19,1,S85))*V85,INDEX(Parameters!$D$19:$H$19,1,S85)+(INDEX(Parameters!$D$19:$H$19,1,S85+1)-INDEX(Parameters!$D$19:$H$19,1,S85))*V85)</f>
@@ -16699,7 +16661,7 @@
       </c>
       <c r="N86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S86)+(INDEX(Parameters!$J$18:$N$18,1,S86+1)-INDEX(Parameters!$J$18:$N$18,1,S86))*V86,INDEX(Parameters!$D$18:$H$18,1,S86)+(INDEX(Parameters!$D$18:$H$18,1,S86+1)-INDEX(Parameters!$D$18:$H$18,1,S86))*V86)</f>
-        <v>0.255</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S86)+(INDEX(Parameters!$J$19:$N$19,1,S86+1)-INDEX(Parameters!$J$19:$N$19,1,S86))*V86,INDEX(Parameters!$D$19:$H$19,1,S86)+(INDEX(Parameters!$D$19:$H$19,1,S86+1)-INDEX(Parameters!$D$19:$H$19,1,S86))*V86)</f>
@@ -16785,7 +16747,7 @@
       </c>
       <c r="N87" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S87)+(INDEX(Parameters!$J$18:$N$18,1,S87+1)-INDEX(Parameters!$J$18:$N$18,1,S87))*V87,INDEX(Parameters!$D$18:$H$18,1,S87)+(INDEX(Parameters!$D$18:$H$18,1,S87+1)-INDEX(Parameters!$D$18:$H$18,1,S87))*V87)</f>
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="O87" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S87)+(INDEX(Parameters!$J$19:$N$19,1,S87+1)-INDEX(Parameters!$J$19:$N$19,1,S87))*V87,INDEX(Parameters!$D$19:$H$19,1,S87)+(INDEX(Parameters!$D$19:$H$19,1,S87+1)-INDEX(Parameters!$D$19:$H$19,1,S87))*V87)</f>
@@ -16871,7 +16833,7 @@
       </c>
       <c r="N88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S88)+(INDEX(Parameters!$J$18:$N$18,1,S88+1)-INDEX(Parameters!$J$18:$N$18,1,S88))*V88,INDEX(Parameters!$D$18:$H$18,1,S88)+(INDEX(Parameters!$D$18:$H$18,1,S88+1)-INDEX(Parameters!$D$18:$H$18,1,S88))*V88)</f>
-        <v>0.30500000000000005</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="O88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S88)+(INDEX(Parameters!$J$19:$N$19,1,S88+1)-INDEX(Parameters!$J$19:$N$19,1,S88))*V88,INDEX(Parameters!$D$19:$H$19,1,S88)+(INDEX(Parameters!$D$19:$H$19,1,S88+1)-INDEX(Parameters!$D$19:$H$19,1,S88))*V88)</f>
@@ -16957,7 +16919,7 @@
       </c>
       <c r="N89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S89)+(INDEX(Parameters!$J$18:$N$18,1,S89+1)-INDEX(Parameters!$J$18:$N$18,1,S89))*V89,INDEX(Parameters!$D$18:$H$18,1,S89)+(INDEX(Parameters!$D$18:$H$18,1,S89+1)-INDEX(Parameters!$D$18:$H$18,1,S89))*V89)</f>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S89)+(INDEX(Parameters!$J$19:$N$19,1,S89+1)-INDEX(Parameters!$J$19:$N$19,1,S89))*V89,INDEX(Parameters!$D$19:$H$19,1,S89)+(INDEX(Parameters!$D$19:$H$19,1,S89+1)-INDEX(Parameters!$D$19:$H$19,1,S89))*V89)</f>
@@ -17307,7 +17269,7 @@
       </c>
       <c r="C99" s="60">
         <f t="shared" si="10"/>
-        <v>274.12</v>
+        <v>275</v>
       </c>
       <c r="D99" s="60">
         <f t="shared" si="11"/>
@@ -17347,15 +17309,15 @@
       </c>
       <c r="C100" s="59">
         <f t="shared" si="10"/>
-        <v>326.91999999999996</v>
+        <v>327.8</v>
       </c>
       <c r="D100" s="59">
         <f t="shared" si="11"/>
-        <v>459.41999999999996</v>
+        <v>461.90000000000003</v>
       </c>
       <c r="E100" s="59">
         <f t="shared" si="12"/>
-        <v>595.19999999999993</v>
+        <v>600</v>
       </c>
       <c r="F100" s="59">
         <f t="shared" si="13"/>
@@ -17387,23 +17349,23 @@
       </c>
       <c r="C101" s="60">
         <f t="shared" si="10"/>
-        <v>379.71999999999997</v>
+        <v>380.59999999999997</v>
       </c>
       <c r="D101" s="60">
         <f t="shared" si="11"/>
-        <v>530.72</v>
+        <v>533.20000000000005</v>
       </c>
       <c r="E101" s="60">
         <f t="shared" si="12"/>
-        <v>683.19999999999993</v>
+        <v>688</v>
       </c>
       <c r="F101" s="60">
         <f t="shared" si="13"/>
-        <v>839.86</v>
+        <v>847.69999999999993</v>
       </c>
       <c r="G101" s="60">
         <f t="shared" si="14"/>
-        <v>1003.3999999999999</v>
+        <v>1014.9999999999999</v>
       </c>
       <c r="H101" s="4"/>
       <c r="I101" s="4"/>
@@ -17427,23 +17389,23 @@
       </c>
       <c r="C102" s="59">
         <f t="shared" si="10"/>
-        <v>432.52</v>
+        <v>433.40000000000003</v>
       </c>
       <c r="D102" s="59">
         <f t="shared" si="11"/>
-        <v>602.02</v>
+        <v>604.5</v>
       </c>
       <c r="E102" s="59">
         <f t="shared" si="12"/>
-        <v>771.2</v>
+        <v>776</v>
       </c>
       <c r="F102" s="59">
         <f t="shared" si="13"/>
-        <v>942.76</v>
+        <v>950.6</v>
       </c>
       <c r="G102" s="59">
         <f t="shared" si="14"/>
-        <v>1119.4000000000001</v>
+        <v>1131</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
@@ -17467,23 +17429,23 @@
       </c>
       <c r="C103" s="60">
         <f t="shared" si="10"/>
-        <v>485.32</v>
+        <v>486.20000000000005</v>
       </c>
       <c r="D103" s="60">
         <f t="shared" si="11"/>
-        <v>673.31999999999994</v>
+        <v>675.80000000000007</v>
       </c>
       <c r="E103" s="60">
         <f t="shared" si="12"/>
-        <v>859.2</v>
+        <v>864</v>
       </c>
       <c r="F103" s="60">
         <f t="shared" si="13"/>
-        <v>1045.6600000000001</v>
+        <v>1053.5</v>
       </c>
       <c r="G103" s="60">
         <f t="shared" si="14"/>
-        <v>1235.4000000000001</v>
+        <v>1247</v>
       </c>
       <c r="H103" s="4"/>
       <c r="I103" s="4"/>
@@ -17507,23 +17469,23 @@
       </c>
       <c r="C104" s="59">
         <f t="shared" si="10"/>
-        <v>538.12</v>
+        <v>539</v>
       </c>
       <c r="D104" s="59">
         <f t="shared" si="11"/>
-        <v>744.62</v>
+        <v>747.1</v>
       </c>
       <c r="E104" s="59">
         <f t="shared" si="12"/>
-        <v>947.19999999999993</v>
+        <v>952</v>
       </c>
       <c r="F104" s="59">
         <f t="shared" si="13"/>
-        <v>1148.56</v>
+        <v>1156.4000000000001</v>
       </c>
       <c r="G104" s="59">
         <f t="shared" si="14"/>
-        <v>1351.4</v>
+        <v>1363</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -17547,23 +17509,23 @@
       </c>
       <c r="C105" s="60">
         <f t="shared" si="10"/>
-        <v>590.92000000000007</v>
+        <v>591.80000000000007</v>
       </c>
       <c r="D105" s="60">
         <f t="shared" si="11"/>
-        <v>815.92000000000007</v>
+        <v>818.40000000000009</v>
       </c>
       <c r="E105" s="60">
         <f t="shared" si="12"/>
-        <v>1035.2</v>
+        <v>1040</v>
       </c>
       <c r="F105" s="60">
         <f t="shared" si="13"/>
-        <v>1251.46</v>
+        <v>1259.3000000000002</v>
       </c>
       <c r="G105" s="60">
         <f t="shared" si="14"/>
-        <v>1467.4</v>
+        <v>1479</v>
       </c>
       <c r="H105" s="4"/>
       <c r="I105" s="4"/>
@@ -17587,23 +17549,23 @@
       </c>
       <c r="C106" s="59">
         <f t="shared" si="10"/>
-        <v>643.72</v>
+        <v>644.59999999999991</v>
       </c>
       <c r="D106" s="59">
         <f t="shared" si="11"/>
-        <v>887.22</v>
+        <v>889.7</v>
       </c>
       <c r="E106" s="59">
         <f t="shared" si="12"/>
-        <v>1123.1999999999998</v>
+        <v>1128</v>
       </c>
       <c r="F106" s="59">
         <f t="shared" si="13"/>
-        <v>1354.3600000000001</v>
+        <v>1362.1999999999998</v>
       </c>
       <c r="G106" s="59">
         <f t="shared" si="14"/>
-        <v>1583.3999999999999</v>
+        <v>1595</v>
       </c>
       <c r="H106" s="4"/>
       <c r="I106" s="4"/>
@@ -17627,23 +17589,23 @@
       </c>
       <c r="C107" s="60">
         <f t="shared" si="10"/>
-        <v>696.52</v>
+        <v>697.40000000000009</v>
       </c>
       <c r="D107" s="60">
         <f t="shared" si="11"/>
-        <v>958.52</v>
+        <v>961</v>
       </c>
       <c r="E107" s="60">
         <f t="shared" si="12"/>
-        <v>1211.2</v>
+        <v>1216</v>
       </c>
       <c r="F107" s="60">
         <f t="shared" si="13"/>
-        <v>1457.2600000000002</v>
+        <v>1465.1</v>
       </c>
       <c r="G107" s="60">
         <f t="shared" si="14"/>
-        <v>1699.4</v>
+        <v>1711</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -17667,23 +17629,23 @@
       </c>
       <c r="C108" s="59">
         <f t="shared" si="10"/>
-        <v>749.31999999999994</v>
+        <v>750.19999999999993</v>
       </c>
       <c r="D108" s="59">
         <f t="shared" si="11"/>
-        <v>1029.82</v>
+        <v>1032.3</v>
       </c>
       <c r="E108" s="59">
         <f t="shared" si="12"/>
-        <v>1299.1999999999998</v>
+        <v>1304</v>
       </c>
       <c r="F108" s="59">
         <f t="shared" si="13"/>
-        <v>1560.1599999999999</v>
+        <v>1568</v>
       </c>
       <c r="G108" s="59">
         <f t="shared" si="14"/>
-        <v>1815.3999999999999</v>
+        <v>1827</v>
       </c>
       <c r="H108" s="4"/>
       <c r="I108" s="4"/>
@@ -17707,23 +17669,23 @@
       </c>
       <c r="C109" s="60">
         <f t="shared" si="10"/>
-        <v>802.12</v>
+        <v>803</v>
       </c>
       <c r="D109" s="60">
         <f t="shared" si="11"/>
-        <v>1101.1199999999999</v>
+        <v>1103.6000000000001</v>
       </c>
       <c r="E109" s="60">
         <f t="shared" si="12"/>
-        <v>1387.1999999999998</v>
+        <v>1392</v>
       </c>
       <c r="F109" s="60">
         <f t="shared" si="13"/>
-        <v>1663.06</v>
+        <v>1670.9</v>
       </c>
       <c r="G109" s="60">
         <f t="shared" si="14"/>
-        <v>1931.4</v>
+        <v>1943</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -17747,23 +17709,23 @@
       </c>
       <c r="C110" s="59">
         <f t="shared" si="10"/>
-        <v>854.92000000000007</v>
+        <v>855.80000000000007</v>
       </c>
       <c r="D110" s="59">
         <f t="shared" si="11"/>
-        <v>1172.42</v>
+        <v>1174.9000000000001</v>
       </c>
       <c r="E110" s="59">
         <f t="shared" si="12"/>
-        <v>1475.2</v>
+        <v>1480</v>
       </c>
       <c r="F110" s="59">
         <f t="shared" si="13"/>
-        <v>1765.96</v>
+        <v>1773.8000000000002</v>
       </c>
       <c r="G110" s="59">
         <f t="shared" si="14"/>
-        <v>2047.4</v>
+        <v>2059</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
@@ -17787,23 +17749,23 @@
       </c>
       <c r="C111" s="60">
         <f t="shared" si="10"/>
-        <v>907.72</v>
+        <v>908.6</v>
       </c>
       <c r="D111" s="60">
         <f t="shared" si="11"/>
-        <v>1243.7199999999998</v>
+        <v>1246.2</v>
       </c>
       <c r="E111" s="60">
         <f t="shared" si="12"/>
-        <v>1563.1999999999998</v>
+        <v>1568</v>
       </c>
       <c r="F111" s="60">
         <f t="shared" si="13"/>
-        <v>1868.8600000000001</v>
+        <v>1876.6999999999998</v>
       </c>
       <c r="G111" s="60">
         <f t="shared" si="14"/>
-        <v>2163.4</v>
+        <v>2175</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -17827,23 +17789,23 @@
       </c>
       <c r="C112" s="59">
         <f t="shared" si="10"/>
-        <v>960.5200000000001</v>
+        <v>961.4</v>
       </c>
       <c r="D112" s="59">
         <f t="shared" si="11"/>
-        <v>1315.02</v>
+        <v>1317.5</v>
       </c>
       <c r="E112" s="59">
         <f t="shared" si="12"/>
-        <v>1651.2</v>
+        <v>1656.0000000000002</v>
       </c>
       <c r="F112" s="59">
         <f t="shared" si="13"/>
-        <v>1971.7600000000002</v>
+        <v>1979.6</v>
       </c>
       <c r="G112" s="59">
         <f t="shared" si="14"/>
-        <v>2279.4</v>
+        <v>2291</v>
       </c>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
@@ -17867,23 +17829,23 @@
       </c>
       <c r="C113" s="60">
         <f t="shared" si="10"/>
-        <v>1013.3199999999999</v>
+        <v>1014.1999999999999</v>
       </c>
       <c r="D113" s="60">
         <f t="shared" si="11"/>
-        <v>1386.32</v>
+        <v>1388.8</v>
       </c>
       <c r="E113" s="60">
         <f t="shared" si="12"/>
-        <v>1739.1999999999998</v>
+        <v>1743.9999999999998</v>
       </c>
       <c r="F113" s="60">
         <f t="shared" si="13"/>
-        <v>2074.66</v>
+        <v>2082.5</v>
       </c>
       <c r="G113" s="60">
         <f t="shared" si="14"/>
-        <v>2395.3999999999996</v>
+        <v>2407</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -17907,23 +17869,23 @@
       </c>
       <c r="C114" s="59">
         <f t="shared" si="10"/>
-        <v>1066.1199999999999</v>
+        <v>1067</v>
       </c>
       <c r="D114" s="59">
         <f t="shared" si="11"/>
-        <v>1457.62</v>
+        <v>1460.1</v>
       </c>
       <c r="E114" s="59">
         <f t="shared" si="12"/>
-        <v>1827.2</v>
+        <v>1832</v>
       </c>
       <c r="F114" s="59">
         <f t="shared" si="13"/>
-        <v>2177.56</v>
+        <v>2185.4</v>
       </c>
       <c r="G114" s="59">
         <f t="shared" si="14"/>
-        <v>2511.3999999999996</v>
+        <v>2523</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -18080,29 +18042,29 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="94" t="s">
+      <c r="B121" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="C121" s="94"/>
-      <c r="D121" s="94"/>
-      <c r="E121" s="94"/>
-      <c r="F121" s="94"/>
-      <c r="G121" s="94"/>
-      <c r="H121" s="94"/>
-      <c r="I121" s="94"/>
-      <c r="J121" s="94"/>
-      <c r="K121" s="94"/>
-      <c r="L121" s="94"/>
-      <c r="M121" s="94"/>
-      <c r="N121" s="94"/>
-      <c r="O121" s="94"/>
-      <c r="P121" s="94"/>
-      <c r="Q121" s="94"/>
-      <c r="R121" s="94"/>
-      <c r="S121" s="94"/>
-      <c r="T121" s="94"/>
-      <c r="U121" s="94"/>
-      <c r="V121" s="94"/>
+      <c r="C121" s="93"/>
+      <c r="D121" s="93"/>
+      <c r="E121" s="93"/>
+      <c r="F121" s="93"/>
+      <c r="G121" s="93"/>
+      <c r="H121" s="93"/>
+      <c r="I121" s="93"/>
+      <c r="J121" s="93"/>
+      <c r="K121" s="93"/>
+      <c r="L121" s="93"/>
+      <c r="M121" s="93"/>
+      <c r="N121" s="93"/>
+      <c r="O121" s="93"/>
+      <c r="P121" s="93"/>
+      <c r="Q121" s="93"/>
+      <c r="R121" s="93"/>
+      <c r="S121" s="93"/>
+      <c r="T121" s="93"/>
+      <c r="U121" s="93"/>
+      <c r="V121" s="93"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -18266,7 +18228,7 @@
       </c>
       <c r="N125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S125)+(INDEX(Parameters!$J$18:$N$18,1,S125+1)-INDEX(Parameters!$J$18:$N$18,1,S125))*V125,INDEX(Parameters!$D$18:$H$18,1,S125)+(INDEX(Parameters!$D$18:$H$18,1,S125+1)-INDEX(Parameters!$D$18:$H$18,1,S125))*V125)</f>
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="O125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S125)+(INDEX(Parameters!$J$19:$N$19,1,S125+1)-INDEX(Parameters!$J$19:$N$19,1,S125))*V125,INDEX(Parameters!$D$19:$H$19,1,S125)+(INDEX(Parameters!$D$19:$H$19,1,S125+1)-INDEX(Parameters!$D$19:$H$19,1,S125))*V125)</f>
@@ -18352,7 +18314,7 @@
       </c>
       <c r="N126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S126)+(INDEX(Parameters!$J$18:$N$18,1,S126+1)-INDEX(Parameters!$J$18:$N$18,1,S126))*V126,INDEX(Parameters!$D$18:$H$18,1,S126)+(INDEX(Parameters!$D$18:$H$18,1,S126+1)-INDEX(Parameters!$D$18:$H$18,1,S126))*V126)</f>
-        <v>0.255</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S126)+(INDEX(Parameters!$J$19:$N$19,1,S126+1)-INDEX(Parameters!$J$19:$N$19,1,S126))*V126,INDEX(Parameters!$D$19:$H$19,1,S126)+(INDEX(Parameters!$D$19:$H$19,1,S126+1)-INDEX(Parameters!$D$19:$H$19,1,S126))*V126)</f>
@@ -18438,7 +18400,7 @@
       </c>
       <c r="N127" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S127)+(INDEX(Parameters!$J$18:$N$18,1,S127+1)-INDEX(Parameters!$J$18:$N$18,1,S127))*V127,INDEX(Parameters!$D$18:$H$18,1,S127)+(INDEX(Parameters!$D$18:$H$18,1,S127+1)-INDEX(Parameters!$D$18:$H$18,1,S127))*V127)</f>
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="O127" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S127)+(INDEX(Parameters!$J$19:$N$19,1,S127+1)-INDEX(Parameters!$J$19:$N$19,1,S127))*V127,INDEX(Parameters!$D$19:$H$19,1,S127)+(INDEX(Parameters!$D$19:$H$19,1,S127+1)-INDEX(Parameters!$D$19:$H$19,1,S127))*V127)</f>
@@ -18524,7 +18486,7 @@
       </c>
       <c r="N128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S128)+(INDEX(Parameters!$J$18:$N$18,1,S128+1)-INDEX(Parameters!$J$18:$N$18,1,S128))*V128,INDEX(Parameters!$D$18:$H$18,1,S128)+(INDEX(Parameters!$D$18:$H$18,1,S128+1)-INDEX(Parameters!$D$18:$H$18,1,S128))*V128)</f>
-        <v>0.30500000000000005</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="O128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S128)+(INDEX(Parameters!$J$19:$N$19,1,S128+1)-INDEX(Parameters!$J$19:$N$19,1,S128))*V128,INDEX(Parameters!$D$19:$H$19,1,S128)+(INDEX(Parameters!$D$19:$H$19,1,S128+1)-INDEX(Parameters!$D$19:$H$19,1,S128))*V128)</f>
@@ -18610,7 +18572,7 @@
       </c>
       <c r="N129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S129)+(INDEX(Parameters!$J$18:$N$18,1,S129+1)-INDEX(Parameters!$J$18:$N$18,1,S129))*V129,INDEX(Parameters!$D$18:$H$18,1,S129)+(INDEX(Parameters!$D$18:$H$18,1,S129+1)-INDEX(Parameters!$D$18:$H$18,1,S129))*V129)</f>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S129)+(INDEX(Parameters!$J$19:$N$19,1,S129+1)-INDEX(Parameters!$J$19:$N$19,1,S129))*V129,INDEX(Parameters!$D$19:$H$19,1,S129)+(INDEX(Parameters!$D$19:$H$19,1,S129+1)-INDEX(Parameters!$D$19:$H$19,1,S129))*V129)</f>
@@ -19070,7 +19032,7 @@
       </c>
       <c r="H139" s="60">
         <f t="shared" si="20"/>
-        <v>-274.12</v>
+        <v>-275</v>
       </c>
       <c r="I139" s="60">
         <f t="shared" si="21"/>
@@ -19125,15 +19087,15 @@
       </c>
       <c r="H140" s="59">
         <f t="shared" si="20"/>
-        <v>-326.91999999999996</v>
+        <v>-327.8</v>
       </c>
       <c r="I140" s="59">
         <f t="shared" si="21"/>
-        <v>-459.41999999999996</v>
+        <v>-461.90000000000003</v>
       </c>
       <c r="J140" s="59">
         <f t="shared" si="22"/>
-        <v>-595.19999999999993</v>
+        <v>-600</v>
       </c>
       <c r="K140" s="59">
         <f t="shared" si="23"/>
@@ -19180,23 +19142,23 @@
       </c>
       <c r="H141" s="60">
         <f t="shared" si="20"/>
-        <v>-379.71999999999997</v>
+        <v>-380.59999999999997</v>
       </c>
       <c r="I141" s="60">
         <f t="shared" si="21"/>
-        <v>-530.72</v>
+        <v>-533.20000000000005</v>
       </c>
       <c r="J141" s="60">
         <f t="shared" si="22"/>
-        <v>-683.19999999999993</v>
+        <v>-688</v>
       </c>
       <c r="K141" s="60">
         <f t="shared" si="23"/>
-        <v>-839.86</v>
+        <v>-847.69999999999993</v>
       </c>
       <c r="L141" s="60">
         <f t="shared" si="24"/>
-        <v>-1003.3999999999999</v>
+        <v>-1014.9999999999999</v>
       </c>
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
@@ -19235,23 +19197,23 @@
       </c>
       <c r="H142" s="59">
         <f t="shared" si="20"/>
-        <v>-432.52</v>
+        <v>-433.40000000000003</v>
       </c>
       <c r="I142" s="59">
         <f t="shared" si="21"/>
-        <v>-602.02</v>
+        <v>-604.5</v>
       </c>
       <c r="J142" s="59">
         <f t="shared" si="22"/>
-        <v>-771.2</v>
+        <v>-776</v>
       </c>
       <c r="K142" s="59">
         <f t="shared" si="23"/>
-        <v>-942.76</v>
+        <v>-950.6</v>
       </c>
       <c r="L142" s="59">
         <f t="shared" si="24"/>
-        <v>-1119.4000000000001</v>
+        <v>-1131</v>
       </c>
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
@@ -19290,23 +19252,23 @@
       </c>
       <c r="H143" s="60">
         <f t="shared" si="20"/>
-        <v>-485.32</v>
+        <v>-486.20000000000005</v>
       </c>
       <c r="I143" s="60">
         <f t="shared" si="21"/>
-        <v>-673.31999999999994</v>
+        <v>-675.80000000000007</v>
       </c>
       <c r="J143" s="60">
         <f t="shared" si="22"/>
-        <v>-859.2</v>
+        <v>-864</v>
       </c>
       <c r="K143" s="60">
         <f t="shared" si="23"/>
-        <v>-1045.6600000000001</v>
+        <v>-1053.5</v>
       </c>
       <c r="L143" s="60">
         <f t="shared" si="24"/>
-        <v>-1235.4000000000001</v>
+        <v>-1247</v>
       </c>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
@@ -19345,23 +19307,23 @@
       </c>
       <c r="H144" s="59">
         <f t="shared" si="20"/>
-        <v>-538.12</v>
+        <v>-539</v>
       </c>
       <c r="I144" s="59">
         <f t="shared" si="21"/>
-        <v>-744.62</v>
+        <v>-747.1</v>
       </c>
       <c r="J144" s="59">
         <f t="shared" si="22"/>
-        <v>-947.19999999999993</v>
+        <v>-952</v>
       </c>
       <c r="K144" s="59">
         <f t="shared" si="23"/>
-        <v>-1148.56</v>
+        <v>-1156.4000000000001</v>
       </c>
       <c r="L144" s="59">
         <f t="shared" si="24"/>
-        <v>-1351.4</v>
+        <v>-1363</v>
       </c>
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
@@ -19400,23 +19362,23 @@
       </c>
       <c r="H145" s="60">
         <f t="shared" si="20"/>
-        <v>-590.92000000000007</v>
+        <v>-591.80000000000007</v>
       </c>
       <c r="I145" s="60">
         <f t="shared" si="21"/>
-        <v>-815.92000000000007</v>
+        <v>-818.40000000000009</v>
       </c>
       <c r="J145" s="60">
         <f t="shared" si="22"/>
-        <v>-1035.2</v>
+        <v>-1040</v>
       </c>
       <c r="K145" s="60">
         <f t="shared" si="23"/>
-        <v>-1251.46</v>
+        <v>-1259.3000000000002</v>
       </c>
       <c r="L145" s="60">
         <f t="shared" si="24"/>
-        <v>-1467.4</v>
+        <v>-1479</v>
       </c>
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
@@ -19455,23 +19417,23 @@
       </c>
       <c r="H146" s="59">
         <f t="shared" si="20"/>
-        <v>-643.72</v>
+        <v>-644.59999999999991</v>
       </c>
       <c r="I146" s="59">
         <f t="shared" si="21"/>
-        <v>-887.22</v>
+        <v>-889.7</v>
       </c>
       <c r="J146" s="59">
         <f t="shared" si="22"/>
-        <v>-1123.1999999999998</v>
+        <v>-1128</v>
       </c>
       <c r="K146" s="59">
         <f t="shared" si="23"/>
-        <v>-1354.3600000000001</v>
+        <v>-1362.1999999999998</v>
       </c>
       <c r="L146" s="59">
         <f t="shared" si="24"/>
-        <v>-1583.3999999999999</v>
+        <v>-1595</v>
       </c>
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
@@ -19510,23 +19472,23 @@
       </c>
       <c r="H147" s="60">
         <f t="shared" si="20"/>
-        <v>-696.52</v>
+        <v>-697.40000000000009</v>
       </c>
       <c r="I147" s="60">
         <f t="shared" si="21"/>
-        <v>-958.52</v>
+        <v>-961</v>
       </c>
       <c r="J147" s="60">
         <f t="shared" si="22"/>
-        <v>-1211.2</v>
+        <v>-1216</v>
       </c>
       <c r="K147" s="60">
         <f t="shared" si="23"/>
-        <v>-1457.2600000000002</v>
+        <v>-1465.1</v>
       </c>
       <c r="L147" s="60">
         <f t="shared" si="24"/>
-        <v>-1699.4</v>
+        <v>-1711</v>
       </c>
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
@@ -19565,23 +19527,23 @@
       </c>
       <c r="H148" s="59">
         <f t="shared" si="20"/>
-        <v>-749.31999999999994</v>
+        <v>-750.19999999999993</v>
       </c>
       <c r="I148" s="59">
         <f t="shared" si="21"/>
-        <v>-1029.82</v>
+        <v>-1032.3</v>
       </c>
       <c r="J148" s="59">
         <f t="shared" si="22"/>
-        <v>-1299.1999999999998</v>
+        <v>-1304</v>
       </c>
       <c r="K148" s="59">
         <f t="shared" si="23"/>
-        <v>-1560.1599999999999</v>
+        <v>-1568</v>
       </c>
       <c r="L148" s="59">
         <f t="shared" si="24"/>
-        <v>-1815.3999999999999</v>
+        <v>-1827</v>
       </c>
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
@@ -19620,23 +19582,23 @@
       </c>
       <c r="H149" s="60">
         <f t="shared" si="20"/>
-        <v>-802.12</v>
+        <v>-803</v>
       </c>
       <c r="I149" s="60">
         <f t="shared" si="21"/>
-        <v>-1101.1199999999999</v>
+        <v>-1103.6000000000001</v>
       </c>
       <c r="J149" s="60">
         <f t="shared" si="22"/>
-        <v>-1387.1999999999998</v>
+        <v>-1392</v>
       </c>
       <c r="K149" s="60">
         <f t="shared" si="23"/>
-        <v>-1663.06</v>
+        <v>-1670.9</v>
       </c>
       <c r="L149" s="60">
         <f t="shared" si="24"/>
-        <v>-1931.4</v>
+        <v>-1943</v>
       </c>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
@@ -19675,23 +19637,23 @@
       </c>
       <c r="H150" s="59">
         <f t="shared" si="20"/>
-        <v>-854.92000000000007</v>
+        <v>-855.80000000000007</v>
       </c>
       <c r="I150" s="59">
         <f t="shared" si="21"/>
-        <v>-1172.42</v>
+        <v>-1174.9000000000001</v>
       </c>
       <c r="J150" s="59">
         <f t="shared" si="22"/>
-        <v>-1475.2</v>
+        <v>-1480</v>
       </c>
       <c r="K150" s="59">
         <f t="shared" si="23"/>
-        <v>-1765.96</v>
+        <v>-1773.8000000000002</v>
       </c>
       <c r="L150" s="59">
         <f t="shared" si="24"/>
-        <v>-2047.4</v>
+        <v>-2059</v>
       </c>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
@@ -19730,23 +19692,23 @@
       </c>
       <c r="H151" s="60">
         <f t="shared" si="20"/>
-        <v>-907.72</v>
+        <v>-908.6</v>
       </c>
       <c r="I151" s="60">
         <f t="shared" si="21"/>
-        <v>-1243.7199999999998</v>
+        <v>-1246.2</v>
       </c>
       <c r="J151" s="60">
         <f t="shared" si="22"/>
-        <v>-1563.1999999999998</v>
+        <v>-1568</v>
       </c>
       <c r="K151" s="60">
         <f t="shared" si="23"/>
-        <v>-1868.8600000000001</v>
+        <v>-1876.6999999999998</v>
       </c>
       <c r="L151" s="60">
         <f t="shared" si="24"/>
-        <v>-2163.4</v>
+        <v>-2175</v>
       </c>
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
@@ -19785,23 +19747,23 @@
       </c>
       <c r="H152" s="59">
         <f t="shared" si="20"/>
-        <v>-960.5200000000001</v>
+        <v>-961.4</v>
       </c>
       <c r="I152" s="59">
         <f t="shared" si="21"/>
-        <v>-1315.02</v>
+        <v>-1317.5</v>
       </c>
       <c r="J152" s="59">
         <f t="shared" si="22"/>
-        <v>-1651.2</v>
+        <v>-1656.0000000000002</v>
       </c>
       <c r="K152" s="59">
         <f t="shared" si="23"/>
-        <v>-1971.7600000000002</v>
+        <v>-1979.6</v>
       </c>
       <c r="L152" s="59">
         <f t="shared" si="24"/>
-        <v>-2279.4</v>
+        <v>-2291</v>
       </c>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
@@ -19840,23 +19802,23 @@
       </c>
       <c r="H153" s="60">
         <f t="shared" si="20"/>
-        <v>-1013.3199999999999</v>
+        <v>-1014.1999999999999</v>
       </c>
       <c r="I153" s="60">
         <f t="shared" si="21"/>
-        <v>-1386.32</v>
+        <v>-1388.8</v>
       </c>
       <c r="J153" s="60">
         <f t="shared" si="22"/>
-        <v>-1739.1999999999998</v>
+        <v>-1743.9999999999998</v>
       </c>
       <c r="K153" s="60">
         <f t="shared" si="23"/>
-        <v>-2074.66</v>
+        <v>-2082.5</v>
       </c>
       <c r="L153" s="60">
         <f t="shared" si="24"/>
-        <v>-2395.3999999999996</v>
+        <v>-2407</v>
       </c>
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
@@ -19895,23 +19857,23 @@
       </c>
       <c r="H154" s="59">
         <f t="shared" si="20"/>
-        <v>-1066.1199999999999</v>
+        <v>-1067</v>
       </c>
       <c r="I154" s="59">
         <f t="shared" si="21"/>
-        <v>-1457.62</v>
+        <v>-1460.1</v>
       </c>
       <c r="J154" s="59">
         <f t="shared" si="22"/>
-        <v>-1827.2</v>
+        <v>-1832</v>
       </c>
       <c r="K154" s="59">
         <f t="shared" si="23"/>
-        <v>-2177.56</v>
+        <v>-2185.4</v>
       </c>
       <c r="L154" s="59">
         <f t="shared" si="24"/>
-        <v>-2511.3999999999996</v>
+        <v>-2523</v>
       </c>
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
@@ -19994,29 +19956,29 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="95" t="s">
+      <c r="B161" s="94" t="s">
         <v>94</v>
       </c>
-      <c r="C161" s="95"/>
-      <c r="D161" s="95"/>
-      <c r="E161" s="95"/>
-      <c r="F161" s="95"/>
-      <c r="G161" s="95"/>
-      <c r="H161" s="95"/>
-      <c r="I161" s="95"/>
-      <c r="J161" s="95"/>
-      <c r="K161" s="95"/>
-      <c r="L161" s="95"/>
-      <c r="M161" s="95"/>
-      <c r="N161" s="95"/>
-      <c r="O161" s="95"/>
-      <c r="P161" s="95"/>
-      <c r="Q161" s="95"/>
-      <c r="R161" s="95"/>
-      <c r="S161" s="95"/>
-      <c r="T161" s="95"/>
-      <c r="U161" s="95"/>
-      <c r="V161" s="95"/>
+      <c r="C161" s="94"/>
+      <c r="D161" s="94"/>
+      <c r="E161" s="94"/>
+      <c r="F161" s="94"/>
+      <c r="G161" s="94"/>
+      <c r="H161" s="94"/>
+      <c r="I161" s="94"/>
+      <c r="J161" s="94"/>
+      <c r="K161" s="94"/>
+      <c r="L161" s="94"/>
+      <c r="M161" s="94"/>
+      <c r="N161" s="94"/>
+      <c r="O161" s="94"/>
+      <c r="P161" s="94"/>
+      <c r="Q161" s="94"/>
+      <c r="R161" s="94"/>
+      <c r="S161" s="94"/>
+      <c r="T161" s="94"/>
+      <c r="U161" s="94"/>
+      <c r="V161" s="94"/>
     </row>
     <row r="164" spans="2:22" ht="44" customHeight="1">
       <c r="B164" s="61" t="s">
@@ -20131,7 +20093,7 @@
       </c>
       <c r="N165" s="63">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S165)+(INDEX(Parameters!$J$18:$N$18,1,S165+1)-INDEX(Parameters!$J$18:$N$18,1,S165))*V165,INDEX(Parameters!$D$18:$H$18,1,S165)+(INDEX(Parameters!$D$18:$H$18,1,S165+1)-INDEX(Parameters!$D$18:$H$18,1,S165))*V165)</f>
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="O165" s="63">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S165)+(INDEX(Parameters!$J$19:$N$19,1,S165+1)-INDEX(Parameters!$J$19:$N$19,1,S165))*V165,INDEX(Parameters!$D$19:$H$19,1,S165)+(INDEX(Parameters!$D$19:$H$19,1,S165+1)-INDEX(Parameters!$D$19:$H$19,1,S165))*V165)</f>

--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\damping-rx-sync-20261026\native\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB36D54-73B1-4918-96E7-EB4EFC8A4F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D45ABE-D6F8-4F9D-BC3B-4F991366B8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -347,7 +347,7 @@
     <numFmt numFmtId="177" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="178" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="80">
+  <fonts count="79">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -494,13 +494,6 @@
       <color rgb="FF195DB1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF667B91"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -873,7 +866,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="71">
+  <fills count="70">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -938,11 +931,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1226,7 +1214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="72">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1338,15 +1326,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFDCE4EB"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1818,11 +1797,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1837,7 +1816,7 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1855,10 +1834,10 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1876,10 +1855,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1903,56 +1882,59 @@
     <xf numFmtId="1" fontId="22" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="27" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="26" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="32" fillId="23" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="33" fillId="24" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="34" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="35" fillId="26" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="37" fillId="28" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="38" fillId="29" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="39" fillId="30" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="44" fillId="35" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="45" fillId="36" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="46" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="47" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="48" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="40" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="45" fillId="36" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="46" fillId="37" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="47" fillId="38" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="48" fillId="39" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="49" fillId="40" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="57" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="49" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="50" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1964,7 +1946,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="53" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="54" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1976,54 +1958,60 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="57" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="67" fillId="58" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="59" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="68" fillId="59" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="69" fillId="60" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="70" fillId="61" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="70" fillId="61" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="62" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="72" fillId="63" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="72" fillId="63" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="73" fillId="64" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="74" fillId="65" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="75" fillId="66" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="76" fillId="67" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="77" fillId="68" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="78" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2032,13 +2020,16 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2046,21 +2037,6 @@
     </xf>
     <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2074,34 +2050,34 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="17" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="56" fillId="47" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="75" fillId="66" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="65" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3350,64 +3326,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>837</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>924</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1011</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1098</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1185</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1272</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1359</c:v>
+                  <c:v>1398.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1471</c:v>
+                  <c:v>1552.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1582.9999999999998</c:v>
+                  <c:v>1706.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1695</c:v>
+                  <c:v>1860.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1807</c:v>
+                  <c:v>2014.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1918.9999999999998</c:v>
+                  <c:v>2168.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2031</c:v>
+                  <c:v>2322.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2143</c:v>
+                  <c:v>2476.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2255</c:v>
+                  <c:v>2630.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3526,64 +3502,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>987</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1074</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1161</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1248</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1335</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1422</c:v>
+                  <c:v>1396.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1534</c:v>
+                  <c:v>1580.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1646</c:v>
+                  <c:v>1764.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1758</c:v>
+                  <c:v>1948.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1870</c:v>
+                  <c:v>2132.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1982</c:v>
+                  <c:v>2316.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2094</c:v>
+                  <c:v>2500.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2206</c:v>
+                  <c:v>2684.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2318</c:v>
+                  <c:v>2868.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3702,64 +3678,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1137</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1224</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1311</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1398</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1485</c:v>
+                  <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1597</c:v>
+                  <c:v>1596.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1709</c:v>
+                  <c:v>1810.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1821</c:v>
+                  <c:v>2024.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1933</c:v>
+                  <c:v>2238.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2045</c:v>
+                  <c:v>2452.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2157</c:v>
+                  <c:v>2666.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2269</c:v>
+                  <c:v>2880.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2381</c:v>
+                  <c:v>3094.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3878,64 +3854,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1200</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1287</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1374</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1461</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1548</c:v>
+                  <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1660</c:v>
+                  <c:v>1600.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1771.9999999999998</c:v>
+                  <c:v>1844.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1884</c:v>
+                  <c:v>2088.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1996</c:v>
+                  <c:v>2332.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2108</c:v>
+                  <c:v>2576.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2220</c:v>
+                  <c:v>2820.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2332</c:v>
+                  <c:v>3064.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2444</c:v>
+                  <c:v>3308.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4054,64 +4030,64 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>300</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>450</c:v>
+                  <c:v>356.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600</c:v>
+                  <c:v>470.40000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>750</c:v>
+                  <c:v>584.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>900</c:v>
+                  <c:v>698.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1050</c:v>
+                  <c:v>812.4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1200</c:v>
+                  <c:v>926.40000000000009</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1350</c:v>
+                  <c:v>1040.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1437</c:v>
+                  <c:v>1154.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1524</c:v>
+                  <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1611</c:v>
+                  <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1723</c:v>
+                  <c:v>1592.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1834.9999999999998</c:v>
+                  <c:v>1866.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1947</c:v>
+                  <c:v>2140.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2059</c:v>
+                  <c:v>2414.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2171</c:v>
+                  <c:v>2688.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2283</c:v>
+                  <c:v>2962.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2395</c:v>
+                  <c:v>3236.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2507</c:v>
+                  <c:v>3510.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7688,14 +7664,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7746,7 +7722,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="83" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="6"/>
@@ -7766,7 +7742,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="84"/>
+      <c r="B7" s="83"/>
       <c r="C7" s="6"/>
       <c r="D7" s="12" t="s">
         <v>79</v>
@@ -7900,30 +7876,30 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="81"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="81"/>
-      <c r="G16" s="81"/>
+      <c r="D16" s="80"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -8014,20 +7990,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -8057,15 +8033,15 @@
         <v>95</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8096,13 +8072,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -8140,16 +8116,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="86">
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="88">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
         <v>3181.44</v>
       </c>
-      <c r="J8" s="87"/>
+      <c r="J8" s="89"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -8187,16 +8163,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="86">
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="88">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1832</v>
       </c>
-      <c r="J10" s="87"/>
+      <c r="J10" s="89"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -8248,13 +8224,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="70" t="s">
+      <c r="F13" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="69"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="72"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -8272,11 +8248,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="88" t="s">
+      <c r="F14" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="75"/>
       <c r="I14" s="32">
         <f>Samples!F165</f>
         <v>2400</v>
@@ -8301,11 +8277,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
       <c r="I15" s="33">
         <f>Samples!I165</f>
         <v>2280</v>
@@ -8325,11 +8301,11 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="71" t="s">
+      <c r="F16" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
+      <c r="G16" s="75"/>
+      <c r="H16" s="75"/>
       <c r="I16" s="32">
         <f>Samples!J165</f>
         <v>2240</v>
@@ -8349,11 +8325,11 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
       <c r="I17" s="33">
         <f>Samples!L165</f>
         <v>4520</v>
@@ -8395,11 +8371,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="88" t="s">
+      <c r="F19" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
+      <c r="G19" s="75"/>
+      <c r="H19" s="75"/>
       <c r="I19" s="32">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -8419,11 +8395,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="76" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
       <c r="I20" s="33">
         <f>Samples!P165</f>
         <v>1760</v>
@@ -8460,11 +8436,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="71" t="s">
+      <c r="F22" s="74" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
+      <c r="G22" s="75"/>
+      <c r="H22" s="75"/>
       <c r="I22" s="35">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -8484,11 +8460,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
       <c r="I23" s="36">
         <f>Samples!K165</f>
         <v>0.60399999999999998</v>
@@ -8508,11 +8484,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="88" t="s">
+      <c r="F24" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
       <c r="I24" s="35">
         <f>Samples!N165</f>
         <v>0.3</v>
@@ -8562,20 +8538,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="89" t="s">
+      <c r="B27" s="84" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="90"/>
-      <c r="K27" s="90"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="90"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
+      <c r="G27" s="85"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="85"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -8836,17 +8812,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8854,6 +8819,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -8910,20 +8886,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -8953,15 +8929,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8991,15 +8967,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9583,18 +9559,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="91"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9668,20 +9644,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -9708,18 +9684,18 @@
         <v>0</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9749,15 +9725,15 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10341,18 +10317,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="91"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10426,20 +10402,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -10469,15 +10445,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10500,18 +10476,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -11095,18 +11071,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="91"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11176,20 +11152,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -11219,15 +11195,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="85"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11250,18 +11226,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="68"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -11845,18 +11821,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="91"/>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
+      <c r="B41" s="90"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11930,40 +11906,40 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="68"/>
+      <c r="N2" s="68"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -11987,21 +11963,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="69" t="s">
+      <c r="J5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="69"/>
-      <c r="L5" s="69"/>
-      <c r="M5" s="69"/>
-      <c r="N5" s="69"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -12633,73 +12609,73 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="69"/>
-      <c r="M22" s="69"/>
-      <c r="N22" s="69"/>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="71" t="s">
+      <c r="B23" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="72"/>
+      <c r="C23" s="75"/>
       <c r="D23" s="29">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="74" t="s">
+      <c r="F23" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="75"/>
-      <c r="K23" s="75"/>
-      <c r="L23" s="75"/>
-      <c r="M23" s="75"/>
-      <c r="N23" s="75"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
+      <c r="J23" s="78"/>
+      <c r="K23" s="78"/>
+      <c r="L23" s="78"/>
+      <c r="M23" s="78"/>
+      <c r="N23" s="78"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="68" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="69"/>
       <c r="D24" s="31">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
-      <c r="J24" s="75"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="75"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="75"/>
+      <c r="F24" s="78"/>
+      <c r="G24" s="78"/>
+      <c r="H24" s="78"/>
+      <c r="I24" s="78"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="78"/>
+      <c r="M24" s="78"/>
+      <c r="N24" s="78"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="71" t="s">
+      <c r="B25" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="72"/>
+      <c r="C25" s="75"/>
       <c r="D25" s="29">
         <v>40</v>
       </c>
@@ -12717,33 +12693,33 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="65"/>
+      <c r="C26" s="69"/>
       <c r="D26" s="31">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="68"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="69"/>
       <c r="D27" s="31">
         <v>10</v>
       </c>
@@ -12761,140 +12737,140 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="77"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="80"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="80"/>
-      <c r="I30" s="80"/>
-      <c r="J30" s="80"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="80"/>
-      <c r="M30" s="80"/>
-      <c r="N30" s="80"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="77"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="77"/>
-      <c r="K31" s="77"/>
-      <c r="L31" s="77"/>
-      <c r="M31" s="77"/>
-      <c r="N31" s="77"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" ht="23.15" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="77"/>
-      <c r="M32" s="77"/>
-      <c r="N32" s="77"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
     <row r="33" spans="1:15" ht="23.15" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="77"/>
-      <c r="K33" s="77"/>
-      <c r="L33" s="77"/>
-      <c r="M33" s="77"/>
-      <c r="N33" s="77"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
     <row r="34" spans="1:15" ht="23.15" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="77"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="77"/>
-      <c r="K34" s="77"/>
-      <c r="L34" s="77"/>
-      <c r="M34" s="77"/>
-      <c r="N34" s="77"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
     <row r="35" spans="1:15" ht="23.15" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="77"/>
-      <c r="K35" s="77"/>
-      <c r="L35" s="77"/>
-      <c r="M35" s="77"/>
-      <c r="N35" s="77"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
     <row r="36" spans="1:15" ht="23.15" customHeight="1">
@@ -13001,14 +12977,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -13021,6 +12989,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13042,29 +13018,29 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="93"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -14735,29 +14711,29 @@
     </row>
     <row r="41" spans="1:22" ht="32" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="92" t="s">
+      <c r="B41" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="92"/>
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-      <c r="M41" s="92"/>
-      <c r="N41" s="92"/>
-      <c r="O41" s="92"/>
-      <c r="P41" s="93"/>
-      <c r="Q41" s="93"/>
-      <c r="R41" s="93"/>
-      <c r="S41" s="93"/>
-      <c r="T41" s="93"/>
-      <c r="U41" s="93"/>
-      <c r="V41" s="93"/>
+      <c r="C41" s="91"/>
+      <c r="D41" s="91"/>
+      <c r="E41" s="91"/>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="91"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="91"/>
+      <c r="P41" s="92"/>
+      <c r="Q41" s="92"/>
+      <c r="R41" s="92"/>
+      <c r="S41" s="92"/>
+      <c r="T41" s="92"/>
+      <c r="U41" s="92"/>
+      <c r="V41" s="92"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -14890,43 +14866,43 @@
       </c>
       <c r="F45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q45)+(INDEX(Parameters!$J$10:$N$10,1,Q45+1)-INDEX(Parameters!$J$10:$N$10,1,Q45))*T45,INDEX(Parameters!$D$10:$H$10,1,Q45)+(INDEX(Parameters!$D$10:$H$10,1,Q45+1)-INDEX(Parameters!$D$10:$H$10,1,Q45))*T45)</f>
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R45)+(INDEX(Parameters!$J$11:$N$11,1,R45+1)-INDEX(Parameters!$J$11:$N$11,1,R45))*U45,INDEX(Parameters!$D$11:$H$11,1,Q45)+(INDEX(Parameters!$D$11:$H$11,1,Q45+1)-INDEX(Parameters!$D$11:$H$11,1,Q45))*T45)</f>
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q45)+(INDEX(Parameters!$J$12:$N$12,1,Q45+1)-INDEX(Parameters!$J$12:$N$12,1,Q45))*T45,INDEX(Parameters!$D$12:$H$12,1,Q45)+(INDEX(Parameters!$D$12:$H$12,1,Q45+1)-INDEX(Parameters!$D$12:$H$12,1,Q45))*T45)</f>
-        <v>0.57999999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="I45" s="50">
         <f>F45*H45</f>
-        <v>1739.9999999999998</v>
+        <v>2280</v>
       </c>
       <c r="J45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="K45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
-        <v>0.6</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="L45" s="50">
         <f>I45+J45</f>
-        <v>2240</v>
+        <v>3080</v>
       </c>
       <c r="M45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="N45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S45)+(INDEX(Parameters!$J$18:$N$18,1,S45+1)-INDEX(Parameters!$J$18:$N$18,1,S45))*V45,INDEX(Parameters!$D$18:$H$18,1,S45)+(INDEX(Parameters!$D$18:$H$18,1,S45+1)-INDEX(Parameters!$D$18:$H$18,1,S45))*V45)</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="O45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S45)+(INDEX(Parameters!$J$19:$N$19,1,S45+1)-INDEX(Parameters!$J$19:$N$19,1,S45))*V45,INDEX(Parameters!$D$19:$H$19,1,S45)+(INDEX(Parameters!$D$19:$H$19,1,S45+1)-INDEX(Parameters!$D$19:$H$19,1,S45))*V45)</f>
-        <v>0.66</v>
+        <v>0.96</v>
       </c>
       <c r="P45" s="50">
         <f>M45*O45</f>
@@ -14976,47 +14952,47 @@
       </c>
       <c r="F46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q46)+(INDEX(Parameters!$J$10:$N$10,1,Q46+1)-INDEX(Parameters!$J$10:$N$10,1,Q46))*T46,INDEX(Parameters!$D$10:$H$10,1,Q46)+(INDEX(Parameters!$D$10:$H$10,1,Q46+1)-INDEX(Parameters!$D$10:$H$10,1,Q46))*T46)</f>
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R46)+(INDEX(Parameters!$J$11:$N$11,1,R46+1)-INDEX(Parameters!$J$11:$N$11,1,R46))*U46,INDEX(Parameters!$D$11:$H$11,1,Q46)+(INDEX(Parameters!$D$11:$H$11,1,Q46+1)-INDEX(Parameters!$D$11:$H$11,1,Q46))*T46)</f>
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="H46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q46)+(INDEX(Parameters!$J$12:$N$12,1,Q46+1)-INDEX(Parameters!$J$12:$N$12,1,Q46))*T46,INDEX(Parameters!$D$12:$H$12,1,Q46)+(INDEX(Parameters!$D$12:$H$12,1,Q46+1)-INDEX(Parameters!$D$12:$H$12,1,Q46))*T46)</f>
-        <v>0.57999999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="I46" s="52">
         <f>F46*H46</f>
-        <v>1739.9999999999998</v>
+        <v>2280</v>
       </c>
       <c r="J46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>500</v>
+        <v>1400</v>
       </c>
       <c r="K46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="L46" s="52">
         <f>I46+J46</f>
-        <v>2240</v>
+        <v>3680</v>
       </c>
       <c r="M46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
-        <v>2050</v>
+        <v>1550</v>
       </c>
       <c r="N46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S46)+(INDEX(Parameters!$J$18:$N$18,1,S46+1)-INDEX(Parameters!$J$18:$N$18,1,S46))*V46,INDEX(Parameters!$D$18:$H$18,1,S46)+(INDEX(Parameters!$D$18:$H$18,1,S46+1)-INDEX(Parameters!$D$18:$H$18,1,S46))*V46)</f>
-        <v>0.22500000000000001</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="O46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S46)+(INDEX(Parameters!$J$19:$N$19,1,S46+1)-INDEX(Parameters!$J$19:$N$19,1,S46))*V46,INDEX(Parameters!$D$19:$H$19,1,S46)+(INDEX(Parameters!$D$19:$H$19,1,S46+1)-INDEX(Parameters!$D$19:$H$19,1,S46))*V46)</f>
-        <v>0.62</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="P46" s="52">
         <f>M46*O46</f>
-        <v>1271</v>
+        <v>1426</v>
       </c>
       <c r="Q46" s="52">
         <f>MIN(4,MAX(1,INT((1+C46/Parameters!$D$23)*4)+1))</f>
@@ -15062,23 +15038,23 @@
       </c>
       <c r="F47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q47)+(INDEX(Parameters!$J$10:$N$10,1,Q47+1)-INDEX(Parameters!$J$10:$N$10,1,Q47))*T47,INDEX(Parameters!$D$10:$H$10,1,Q47)+(INDEX(Parameters!$D$10:$H$10,1,Q47+1)-INDEX(Parameters!$D$10:$H$10,1,Q47))*T47)</f>
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R47)+(INDEX(Parameters!$J$11:$N$11,1,R47+1)-INDEX(Parameters!$J$11:$N$11,1,R47))*U47,INDEX(Parameters!$D$11:$H$11,1,Q47)+(INDEX(Parameters!$D$11:$H$11,1,Q47+1)-INDEX(Parameters!$D$11:$H$11,1,Q47))*T47)</f>
-        <v>0.35</v>
+        <v>0.12</v>
       </c>
       <c r="H47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q47)+(INDEX(Parameters!$J$12:$N$12,1,Q47+1)-INDEX(Parameters!$J$12:$N$12,1,Q47))*T47,INDEX(Parameters!$D$12:$H$12,1,Q47)+(INDEX(Parameters!$D$12:$H$12,1,Q47+1)-INDEX(Parameters!$D$12:$H$12,1,Q47))*T47)</f>
-        <v>0.57999999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="I47" s="50">
         <f>F47*H47</f>
-        <v>1739.9999999999998</v>
+        <v>2280</v>
       </c>
       <c r="J47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="K47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -15086,23 +15062,23 @@
       </c>
       <c r="L47" s="50">
         <f>I47+J47</f>
-        <v>2240</v>
+        <v>4280</v>
       </c>
       <c r="M47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="N47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S47)+(INDEX(Parameters!$J$18:$N$18,1,S47+1)-INDEX(Parameters!$J$18:$N$18,1,S47))*V47,INDEX(Parameters!$D$18:$H$18,1,S47)+(INDEX(Parameters!$D$18:$H$18,1,S47+1)-INDEX(Parameters!$D$18:$H$18,1,S47))*V47)</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="O47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S47)+(INDEX(Parameters!$J$19:$N$19,1,S47+1)-INDEX(Parameters!$J$19:$N$19,1,S47))*V47,INDEX(Parameters!$D$19:$H$19,1,S47)+(INDEX(Parameters!$D$19:$H$19,1,S47+1)-INDEX(Parameters!$D$19:$H$19,1,S47))*V47)</f>
-        <v>0.57999999999999996</v>
+        <v>0.88</v>
       </c>
       <c r="P47" s="50">
         <f>M47*O47</f>
-        <v>1450</v>
+        <v>1760</v>
       </c>
       <c r="Q47" s="50">
         <f>MIN(4,MAX(1,INT((1+C47/Parameters!$D$23)*4)+1))</f>
@@ -15148,47 +15124,47 @@
       </c>
       <c r="F48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q48)+(INDEX(Parameters!$J$10:$N$10,1,Q48+1)-INDEX(Parameters!$J$10:$N$10,1,Q48))*T48,INDEX(Parameters!$D$10:$H$10,1,Q48)+(INDEX(Parameters!$D$10:$H$10,1,Q48+1)-INDEX(Parameters!$D$10:$H$10,1,Q48))*T48)</f>
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R48)+(INDEX(Parameters!$J$11:$N$11,1,R48+1)-INDEX(Parameters!$J$11:$N$11,1,R48))*U48,INDEX(Parameters!$D$11:$H$11,1,Q48)+(INDEX(Parameters!$D$11:$H$11,1,Q48+1)-INDEX(Parameters!$D$11:$H$11,1,Q48))*T48)</f>
-        <v>0.4</v>
+        <v>0.12</v>
       </c>
       <c r="H48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q48)+(INDEX(Parameters!$J$12:$N$12,1,Q48+1)-INDEX(Parameters!$J$12:$N$12,1,Q48))*T48,INDEX(Parameters!$D$12:$H$12,1,Q48)+(INDEX(Parameters!$D$12:$H$12,1,Q48+1)-INDEX(Parameters!$D$12:$H$12,1,Q48))*T48)</f>
-        <v>0.57999999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="I48" s="52">
         <f>F48*H48</f>
-        <v>1739.9999999999998</v>
+        <v>2280</v>
       </c>
       <c r="J48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="K48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="L48" s="52">
         <f>I48+J48</f>
-        <v>2240</v>
+        <v>4880</v>
       </c>
       <c r="M48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
-        <v>2950</v>
+        <v>2450</v>
       </c>
       <c r="N48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S48)+(INDEX(Parameters!$J$18:$N$18,1,S48+1)-INDEX(Parameters!$J$18:$N$18,1,S48))*V48,INDEX(Parameters!$D$18:$H$18,1,S48)+(INDEX(Parameters!$D$18:$H$18,1,S48+1)-INDEX(Parameters!$D$18:$H$18,1,S48))*V48)</f>
-        <v>0.27500000000000002</v>
+        <v>0.32499999999999996</v>
       </c>
       <c r="O48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S48)+(INDEX(Parameters!$J$19:$N$19,1,S48+1)-INDEX(Parameters!$J$19:$N$19,1,S48))*V48,INDEX(Parameters!$D$19:$H$19,1,S48)+(INDEX(Parameters!$D$19:$H$19,1,S48+1)-INDEX(Parameters!$D$19:$H$19,1,S48))*V48)</f>
-        <v>0.54</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="P48" s="52">
         <f>M48*O48</f>
-        <v>1593</v>
+        <v>2058</v>
       </c>
       <c r="Q48" s="52">
         <f>MIN(4,MAX(1,INT((1+C48/Parameters!$D$23)*4)+1))</f>
@@ -15234,47 +15210,47 @@
       </c>
       <c r="F49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$10:$N$10,1,Q49)+(INDEX(Parameters!$J$10:$N$10,1,Q49+1)-INDEX(Parameters!$J$10:$N$10,1,Q49))*T49,INDEX(Parameters!$D$10:$H$10,1,Q49)+(INDEX(Parameters!$D$10:$H$10,1,Q49+1)-INDEX(Parameters!$D$10:$H$10,1,Q49))*T49)</f>
-        <v>3000</v>
+        <v>2400</v>
       </c>
       <c r="G49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$11:$N$11,1,R49)+(INDEX(Parameters!$J$11:$N$11,1,R49+1)-INDEX(Parameters!$J$11:$N$11,1,R49))*U49,INDEX(Parameters!$D$11:$H$11,1,Q49)+(INDEX(Parameters!$D$11:$H$11,1,Q49+1)-INDEX(Parameters!$D$11:$H$11,1,Q49))*T49)</f>
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
       <c r="H49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$12:$N$12,1,Q49)+(INDEX(Parameters!$J$12:$N$12,1,Q49+1)-INDEX(Parameters!$J$12:$N$12,1,Q49))*T49,INDEX(Parameters!$D$12:$H$12,1,Q49)+(INDEX(Parameters!$D$12:$H$12,1,Q49+1)-INDEX(Parameters!$D$12:$H$12,1,Q49))*T49)</f>
-        <v>0.57999999999999996</v>
+        <v>0.95</v>
       </c>
       <c r="I49" s="50">
         <f>F49*H49</f>
-        <v>1739.9999999999998</v>
+        <v>2280</v>
       </c>
       <c r="J49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>500</v>
+        <v>3200</v>
       </c>
       <c r="K49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L49" s="50">
         <f>I49+J49</f>
-        <v>2240</v>
+        <v>5480</v>
       </c>
       <c r="M49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="N49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$18:$N$18,1,S49)+(INDEX(Parameters!$J$18:$N$18,1,S49+1)-INDEX(Parameters!$J$18:$N$18,1,S49))*V49,INDEX(Parameters!$D$18:$H$18,1,S49)+(INDEX(Parameters!$D$18:$H$18,1,S49+1)-INDEX(Parameters!$D$18:$H$18,1,S49))*V49)</f>
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$19:$N$19,1,S49)+(INDEX(Parameters!$J$19:$N$19,1,S49+1)-INDEX(Parameters!$J$19:$N$19,1,S49))*V49,INDEX(Parameters!$D$19:$H$19,1,S49)+(INDEX(Parameters!$D$19:$H$19,1,S49+1)-INDEX(Parameters!$D$19:$H$19,1,S49))*V49)</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="P49" s="50">
         <f>M49*O49</f>
-        <v>1700</v>
+        <v>2320</v>
       </c>
       <c r="Q49" s="50">
         <f>MIN(4,MAX(1,INT((1+C49/Parameters!$D$23)*4)+1))</f>
@@ -15456,23 +15432,23 @@
       </c>
       <c r="C55" s="60">
         <f t="shared" si="5"/>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D55" s="60">
         <f t="shared" si="6"/>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="E55" s="60">
         <f t="shared" si="7"/>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F55" s="60">
         <f t="shared" si="8"/>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G55" s="60">
         <f t="shared" si="9"/>
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -15496,23 +15472,23 @@
       </c>
       <c r="C56" s="59">
         <f t="shared" si="5"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="D56" s="59">
         <f t="shared" si="6"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="E56" s="59">
         <f t="shared" si="7"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="F56" s="59">
         <f t="shared" si="8"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="G56" s="59">
         <f t="shared" si="9"/>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="H56" s="4"/>
       <c r="I56" s="4"/>
@@ -15536,23 +15512,23 @@
       </c>
       <c r="C57" s="60">
         <f t="shared" si="5"/>
-        <v>450</v>
+        <v>356.4</v>
       </c>
       <c r="D57" s="60">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>356.4</v>
       </c>
       <c r="E57" s="60">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>356.4</v>
       </c>
       <c r="F57" s="60">
         <f t="shared" si="8"/>
-        <v>450</v>
+        <v>356.4</v>
       </c>
       <c r="G57" s="60">
         <f t="shared" si="9"/>
-        <v>450</v>
+        <v>356.4</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -15576,23 +15552,23 @@
       </c>
       <c r="C58" s="59">
         <f t="shared" si="5"/>
-        <v>600</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="D58" s="59">
         <f t="shared" si="6"/>
-        <v>600</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="E58" s="59">
         <f t="shared" si="7"/>
-        <v>600</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="F58" s="59">
         <f t="shared" si="8"/>
-        <v>600</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="G58" s="59">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>470.40000000000003</v>
       </c>
       <c r="H58" s="4"/>
       <c r="I58" s="4"/>
@@ -15616,23 +15592,23 @@
       </c>
       <c r="C59" s="60">
         <f t="shared" si="5"/>
-        <v>750</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="D59" s="60">
         <f t="shared" si="6"/>
-        <v>750</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="E59" s="60">
         <f t="shared" si="7"/>
-        <v>750</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="F59" s="60">
         <f t="shared" si="8"/>
-        <v>750</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="G59" s="60">
         <f t="shared" si="9"/>
-        <v>750</v>
+        <v>584.40000000000009</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -15656,23 +15632,23 @@
       </c>
       <c r="C60" s="59">
         <f t="shared" si="5"/>
-        <v>837</v>
+        <v>698.4</v>
       </c>
       <c r="D60" s="59">
         <f t="shared" si="6"/>
-        <v>900</v>
+        <v>698.4</v>
       </c>
       <c r="E60" s="59">
         <f t="shared" si="7"/>
-        <v>900</v>
+        <v>698.4</v>
       </c>
       <c r="F60" s="59">
         <f t="shared" si="8"/>
-        <v>900</v>
+        <v>698.4</v>
       </c>
       <c r="G60" s="59">
         <f t="shared" si="9"/>
-        <v>900</v>
+        <v>698.4</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -15696,23 +15672,23 @@
       </c>
       <c r="C61" s="60">
         <f t="shared" si="5"/>
-        <v>924</v>
+        <v>812.4</v>
       </c>
       <c r="D61" s="60">
         <f t="shared" si="6"/>
-        <v>987</v>
+        <v>812.4</v>
       </c>
       <c r="E61" s="60">
         <f t="shared" si="7"/>
-        <v>1050</v>
+        <v>812.4</v>
       </c>
       <c r="F61" s="60">
         <f t="shared" si="8"/>
-        <v>1050</v>
+        <v>812.4</v>
       </c>
       <c r="G61" s="60">
         <f t="shared" si="9"/>
-        <v>1050</v>
+        <v>812.4</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -15736,23 +15712,23 @@
       </c>
       <c r="C62" s="59">
         <f t="shared" si="5"/>
-        <v>1011</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="D62" s="59">
         <f t="shared" si="6"/>
-        <v>1074</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="E62" s="59">
         <f t="shared" si="7"/>
-        <v>1137</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="F62" s="59">
         <f t="shared" si="8"/>
-        <v>1200</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="G62" s="59">
         <f t="shared" si="9"/>
-        <v>1200</v>
+        <v>926.40000000000009</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -15776,23 +15752,23 @@
       </c>
       <c r="C63" s="60">
         <f t="shared" si="5"/>
-        <v>1098</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="D63" s="60">
         <f t="shared" si="6"/>
-        <v>1161</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="E63" s="60">
         <f t="shared" si="7"/>
-        <v>1224</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="F63" s="60">
         <f t="shared" si="8"/>
-        <v>1287</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="G63" s="60">
         <f t="shared" si="9"/>
-        <v>1350</v>
+        <v>1040.4000000000001</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -15816,23 +15792,23 @@
       </c>
       <c r="C64" s="59">
         <f t="shared" si="5"/>
-        <v>1185</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="D64" s="59">
         <f t="shared" si="6"/>
-        <v>1248</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="E64" s="59">
         <f t="shared" si="7"/>
-        <v>1311</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="F64" s="59">
         <f t="shared" si="8"/>
-        <v>1374</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="G64" s="59">
         <f t="shared" si="9"/>
-        <v>1437</v>
+        <v>1154.4000000000001</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -15856,23 +15832,23 @@
       </c>
       <c r="C65" s="60">
         <f t="shared" si="5"/>
-        <v>1272</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="D65" s="60">
         <f t="shared" si="6"/>
-        <v>1335</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="E65" s="60">
         <f t="shared" si="7"/>
-        <v>1398</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="F65" s="60">
         <f t="shared" si="8"/>
-        <v>1461</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="G65" s="60">
         <f t="shared" si="9"/>
-        <v>1524</v>
+        <v>1268.4000000000001</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -15896,23 +15872,23 @@
       </c>
       <c r="C66" s="59">
         <f t="shared" si="5"/>
-        <v>1359</v>
+        <v>1398.3999999999999</v>
       </c>
       <c r="D66" s="59">
         <f t="shared" si="6"/>
-        <v>1422</v>
+        <v>1396.3999999999999</v>
       </c>
       <c r="E66" s="59">
         <f t="shared" si="7"/>
-        <v>1485</v>
+        <v>1382.3999999999999</v>
       </c>
       <c r="F66" s="59">
         <f t="shared" si="8"/>
-        <v>1548</v>
+        <v>1382.3999999999999</v>
       </c>
       <c r="G66" s="59">
         <f t="shared" si="9"/>
-        <v>1611</v>
+        <v>1382.3999999999999</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -15936,23 +15912,23 @@
       </c>
       <c r="C67" s="60">
         <f t="shared" si="5"/>
-        <v>1471</v>
+        <v>1552.4</v>
       </c>
       <c r="D67" s="60">
         <f t="shared" si="6"/>
-        <v>1534</v>
+        <v>1580.4</v>
       </c>
       <c r="E67" s="60">
         <f t="shared" si="7"/>
-        <v>1597</v>
+        <v>1596.4</v>
       </c>
       <c r="F67" s="60">
         <f t="shared" si="8"/>
-        <v>1660</v>
+        <v>1600.4</v>
       </c>
       <c r="G67" s="60">
         <f t="shared" si="9"/>
-        <v>1723</v>
+        <v>1592.4</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -15976,23 +15952,23 @@
       </c>
       <c r="C68" s="59">
         <f t="shared" si="5"/>
-        <v>1582.9999999999998</v>
+        <v>1706.3999999999999</v>
       </c>
       <c r="D68" s="59">
         <f t="shared" si="6"/>
-        <v>1646</v>
+        <v>1764.3999999999999</v>
       </c>
       <c r="E68" s="59">
         <f t="shared" si="7"/>
-        <v>1709</v>
+        <v>1810.3999999999999</v>
       </c>
       <c r="F68" s="59">
         <f t="shared" si="8"/>
-        <v>1771.9999999999998</v>
+        <v>1844.3999999999999</v>
       </c>
       <c r="G68" s="59">
         <f t="shared" si="9"/>
-        <v>1834.9999999999998</v>
+        <v>1866.3999999999996</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -16016,23 +15992,23 @@
       </c>
       <c r="C69" s="60">
         <f t="shared" si="5"/>
-        <v>1695</v>
+        <v>1860.4</v>
       </c>
       <c r="D69" s="60">
         <f t="shared" si="6"/>
-        <v>1758</v>
+        <v>1948.4</v>
       </c>
       <c r="E69" s="60">
         <f t="shared" si="7"/>
-        <v>1821</v>
+        <v>2024.4</v>
       </c>
       <c r="F69" s="60">
         <f t="shared" si="8"/>
-        <v>1884</v>
+        <v>2088.4</v>
       </c>
       <c r="G69" s="60">
         <f t="shared" si="9"/>
-        <v>1947</v>
+        <v>2140.4</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -16056,23 +16032,23 @@
       </c>
       <c r="C70" s="59">
         <f t="shared" si="5"/>
-        <v>1807</v>
+        <v>2014.4</v>
       </c>
       <c r="D70" s="59">
         <f t="shared" si="6"/>
-        <v>1870</v>
+        <v>2132.4</v>
       </c>
       <c r="E70" s="59">
         <f t="shared" si="7"/>
-        <v>1933</v>
+        <v>2238.4</v>
       </c>
       <c r="F70" s="59">
         <f t="shared" si="8"/>
-        <v>1996</v>
+        <v>2332.4</v>
       </c>
       <c r="G70" s="59">
         <f t="shared" si="9"/>
-        <v>2059</v>
+        <v>2414.4</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -16096,23 +16072,23 @@
       </c>
       <c r="C71" s="60">
         <f t="shared" si="5"/>
-        <v>1918.9999999999998</v>
+        <v>2168.3999999999996</v>
       </c>
       <c r="D71" s="60">
         <f t="shared" si="6"/>
-        <v>1982</v>
+        <v>2316.3999999999996</v>
       </c>
       <c r="E71" s="60">
         <f t="shared" si="7"/>
-        <v>2045</v>
+        <v>2452.3999999999996</v>
       </c>
       <c r="F71" s="60">
         <f t="shared" si="8"/>
-        <v>2108</v>
+        <v>2576.3999999999996</v>
       </c>
       <c r="G71" s="60">
         <f t="shared" si="9"/>
-        <v>2171</v>
+        <v>2688.3999999999996</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -16136,23 +16112,23 @@
       </c>
       <c r="C72" s="59">
         <f t="shared" si="5"/>
-        <v>2031</v>
+        <v>2322.4</v>
       </c>
       <c r="D72" s="59">
         <f t="shared" si="6"/>
-        <v>2094</v>
+        <v>2500.4</v>
       </c>
       <c r="E72" s="59">
         <f t="shared" si="7"/>
-        <v>2157</v>
+        <v>2666.4</v>
       </c>
       <c r="F72" s="59">
         <f t="shared" si="8"/>
-        <v>2220</v>
+        <v>2820.4</v>
       </c>
       <c r="G72" s="59">
         <f t="shared" si="9"/>
-        <v>2283</v>
+        <v>2962.4</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -16176,23 +16152,23 @@
       </c>
       <c r="C73" s="60">
         <f t="shared" si="5"/>
-        <v>2143</v>
+        <v>2476.3999999999996</v>
       </c>
       <c r="D73" s="60">
         <f t="shared" si="6"/>
-        <v>2206</v>
+        <v>2684.3999999999996</v>
       </c>
       <c r="E73" s="60">
         <f t="shared" si="7"/>
-        <v>2269</v>
+        <v>2880.3999999999996</v>
       </c>
       <c r="F73" s="60">
         <f t="shared" si="8"/>
-        <v>2332</v>
+        <v>3064.3999999999996</v>
       </c>
       <c r="G73" s="60">
         <f t="shared" si="9"/>
-        <v>2395</v>
+        <v>3236.3999999999996</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -16216,23 +16192,23 @@
       </c>
       <c r="C74" s="59">
         <f t="shared" si="5"/>
-        <v>2255</v>
+        <v>2630.4</v>
       </c>
       <c r="D74" s="59">
         <f t="shared" si="6"/>
-        <v>2318</v>
+        <v>2868.4</v>
       </c>
       <c r="E74" s="59">
         <f t="shared" si="7"/>
-        <v>2381</v>
+        <v>3094.4</v>
       </c>
       <c r="F74" s="59">
         <f t="shared" si="8"/>
-        <v>2444</v>
+        <v>3308.4</v>
       </c>
       <c r="G74" s="59">
         <f t="shared" si="9"/>
-        <v>2507</v>
+        <v>3510.4</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -16389,29 +16365,29 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="93" t="s">
+      <c r="B81" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="C81" s="93"/>
-      <c r="D81" s="93"/>
-      <c r="E81" s="93"/>
-      <c r="F81" s="93"/>
-      <c r="G81" s="93"/>
-      <c r="H81" s="93"/>
-      <c r="I81" s="93"/>
-      <c r="J81" s="93"/>
-      <c r="K81" s="93"/>
-      <c r="L81" s="93"/>
-      <c r="M81" s="93"/>
-      <c r="N81" s="93"/>
-      <c r="O81" s="93"/>
-      <c r="P81" s="93"/>
-      <c r="Q81" s="93"/>
-      <c r="R81" s="93"/>
-      <c r="S81" s="93"/>
-      <c r="T81" s="93"/>
-      <c r="U81" s="93"/>
-      <c r="V81" s="93"/>
+      <c r="C81" s="92"/>
+      <c r="D81" s="92"/>
+      <c r="E81" s="92"/>
+      <c r="F81" s="92"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
+      <c r="I81" s="92"/>
+      <c r="J81" s="92"/>
+      <c r="K81" s="92"/>
+      <c r="L81" s="92"/>
+      <c r="M81" s="92"/>
+      <c r="N81" s="92"/>
+      <c r="O81" s="92"/>
+      <c r="P81" s="92"/>
+      <c r="Q81" s="92"/>
+      <c r="R81" s="92"/>
+      <c r="S81" s="92"/>
+      <c r="T81" s="92"/>
+      <c r="U81" s="92"/>
+      <c r="V81" s="92"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -18042,29 +18018,29 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="93" t="s">
+      <c r="B121" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="C121" s="93"/>
-      <c r="D121" s="93"/>
-      <c r="E121" s="93"/>
-      <c r="F121" s="93"/>
-      <c r="G121" s="93"/>
-      <c r="H121" s="93"/>
-      <c r="I121" s="93"/>
-      <c r="J121" s="93"/>
-      <c r="K121" s="93"/>
-      <c r="L121" s="93"/>
-      <c r="M121" s="93"/>
-      <c r="N121" s="93"/>
-      <c r="O121" s="93"/>
-      <c r="P121" s="93"/>
-      <c r="Q121" s="93"/>
-      <c r="R121" s="93"/>
-      <c r="S121" s="93"/>
-      <c r="T121" s="93"/>
-      <c r="U121" s="93"/>
-      <c r="V121" s="93"/>
+      <c r="C121" s="92"/>
+      <c r="D121" s="92"/>
+      <c r="E121" s="92"/>
+      <c r="F121" s="92"/>
+      <c r="G121" s="92"/>
+      <c r="H121" s="92"/>
+      <c r="I121" s="92"/>
+      <c r="J121" s="92"/>
+      <c r="K121" s="92"/>
+      <c r="L121" s="92"/>
+      <c r="M121" s="92"/>
+      <c r="N121" s="92"/>
+      <c r="O121" s="92"/>
+      <c r="P121" s="92"/>
+      <c r="Q121" s="92"/>
+      <c r="R121" s="92"/>
+      <c r="S121" s="92"/>
+      <c r="T121" s="92"/>
+      <c r="U121" s="92"/>
+      <c r="V121" s="92"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -19956,29 +19932,29 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="94" t="s">
+      <c r="B161" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="C161" s="94"/>
-      <c r="D161" s="94"/>
-      <c r="E161" s="94"/>
-      <c r="F161" s="94"/>
-      <c r="G161" s="94"/>
-      <c r="H161" s="94"/>
-      <c r="I161" s="94"/>
-      <c r="J161" s="94"/>
-      <c r="K161" s="94"/>
-      <c r="L161" s="94"/>
-      <c r="M161" s="94"/>
-      <c r="N161" s="94"/>
-      <c r="O161" s="94"/>
-      <c r="P161" s="94"/>
-      <c r="Q161" s="94"/>
-      <c r="R161" s="94"/>
-      <c r="S161" s="94"/>
-      <c r="T161" s="94"/>
-      <c r="U161" s="94"/>
-      <c r="V161" s="94"/>
+      <c r="C161" s="93"/>
+      <c r="D161" s="93"/>
+      <c r="E161" s="93"/>
+      <c r="F161" s="93"/>
+      <c r="G161" s="93"/>
+      <c r="H161" s="93"/>
+      <c r="I161" s="93"/>
+      <c r="J161" s="93"/>
+      <c r="K161" s="93"/>
+      <c r="L161" s="93"/>
+      <c r="M161" s="93"/>
+      <c r="N161" s="93"/>
+      <c r="O161" s="93"/>
+      <c r="P161" s="93"/>
+      <c r="Q161" s="93"/>
+      <c r="R161" s="93"/>
+      <c r="S161" s="93"/>
+      <c r="T161" s="93"/>
+      <c r="U161" s="93"/>
+      <c r="V161" s="93"/>
     </row>
     <row r="164" spans="2:22" ht="44" customHeight="1">
       <c r="B164" s="61" t="s">

--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D45ABE-D6F8-4F9D-BC3B-4F991366B8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8BB36E-8F5B-4273-83D4-C74ED369B666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -1797,11 +1797,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1816,7 +1816,7 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1834,10 +1834,10 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1855,10 +1855,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1993,40 +1993,61 @@
     <xf numFmtId="0" fontId="78" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="24" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2038,38 +2059,14 @@
     <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3359,31 +3356,31 @@
                   <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1398.3999999999999</c:v>
+                  <c:v>1390.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1552.4</c:v>
+                  <c:v>1524.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1706.3999999999999</c:v>
+                  <c:v>1658.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1860.4</c:v>
+                  <c:v>1792.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2014.4</c:v>
+                  <c:v>1926.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2168.3999999999996</c:v>
+                  <c:v>2060.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2322.4</c:v>
+                  <c:v>2194.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2476.3999999999996</c:v>
+                  <c:v>2328.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2630.4</c:v>
+                  <c:v>2462.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3535,31 +3532,31 @@
                   <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1396.3999999999999</c:v>
+                  <c:v>1394.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1580.4</c:v>
+                  <c:v>1568.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1764.3999999999999</c:v>
+                  <c:v>1742.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1948.4</c:v>
+                  <c:v>1916.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2132.4</c:v>
+                  <c:v>2090.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2316.3999999999996</c:v>
+                  <c:v>2264.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2500.4</c:v>
+                  <c:v>2438.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2684.3999999999996</c:v>
+                  <c:v>2612.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2868.4</c:v>
+                  <c:v>2786.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3890,28 +3887,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1600.4</c:v>
+                  <c:v>1608.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1844.3999999999999</c:v>
+                  <c:v>1862.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2088.4</c:v>
+                  <c:v>2116.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2332.4</c:v>
+                  <c:v>2370.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2576.3999999999996</c:v>
+                  <c:v>2624.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2820.4</c:v>
+                  <c:v>2878.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3064.3999999999996</c:v>
+                  <c:v>3132.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3308.4</c:v>
+                  <c:v>3386.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4066,28 +4063,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1592.4</c:v>
+                  <c:v>1604.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1866.3999999999996</c:v>
+                  <c:v>1898.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2140.4</c:v>
+                  <c:v>2192.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2414.4</c:v>
+                  <c:v>2486.4000000000005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2688.3999999999996</c:v>
+                  <c:v>2780.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2962.4</c:v>
+                  <c:v>3074.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3236.3999999999996</c:v>
+                  <c:v>3368.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3510.4</c:v>
+                  <c:v>3662.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5512,31 +5509,31 @@
                   <c:v>660.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>736</c:v>
+                  <c:v>728</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>836</c:v>
+                  <c:v>808</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>936</c:v>
+                  <c:v>888</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1036</c:v>
+                  <c:v>968</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1136.0000000000002</c:v>
+                  <c:v>1048.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1236</c:v>
+                  <c:v>1128</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1336</c:v>
+                  <c:v>1208</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1436</c:v>
+                  <c:v>1288</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1536</c:v>
+                  <c:v>1368</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5688,31 +5685,31 @@
                   <c:v>970.65000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1072.4000000000001</c:v>
+                  <c:v>1070.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1230.1500000000001</c:v>
+                  <c:v>1218.1500000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1387.9</c:v>
+                  <c:v>1365.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1545.65</c:v>
+                  <c:v>1513.65</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1703.4</c:v>
+                  <c:v>1661.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1861.1499999999999</c:v>
+                  <c:v>1809.1499999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2018.9</c:v>
+                  <c:v>1956.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2176.6499999999996</c:v>
+                  <c:v>2104.6499999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2334.4</c:v>
+                  <c:v>2252.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6043,28 +6040,28 @@
                   <c:v>1692</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1934.75</c:v>
+                  <c:v>1942.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2203.5</c:v>
+                  <c:v>2221.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2472.25</c:v>
+                  <c:v>2500.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2741</c:v>
+                  <c:v>2779</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3009.75</c:v>
+                  <c:v>3057.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3278.5</c:v>
+                  <c:v>3336.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3547.25</c:v>
+                  <c:v>3615.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3816</c:v>
+                  <c:v>3894</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6219,28 +6216,28 @@
                   <c:v>1987.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2245.1999999999998</c:v>
+                  <c:v>2257.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2567.1999999999998</c:v>
+                  <c:v>2599.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2889.2</c:v>
+                  <c:v>2941.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3211.2000000000003</c:v>
+                  <c:v>3283.2000000000007</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3533.2</c:v>
+                  <c:v>3625.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3855.2000000000003</c:v>
+                  <c:v>3967.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4177.2</c:v>
+                  <c:v>4309.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4499.2</c:v>
+                  <c:v>4651.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7664,14 +7661,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7722,7 +7719,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="70" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="6"/>
@@ -7742,7 +7739,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="83"/>
+      <c r="B7" s="70"/>
       <c r="C7" s="6"/>
       <c r="D7" s="12" t="s">
         <v>79</v>
@@ -7876,30 +7873,30 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -7990,20 +7987,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -8033,15 +8030,15 @@
         <v>95</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8072,7 +8069,7 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="73" t="s">
+      <c r="F6" s="71" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="72"/>
@@ -8116,16 +8113,16 @@
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="68" t="s">
+      <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="88">
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="74">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>3181.44</v>
-      </c>
-      <c r="J8" s="89"/>
+        <v>3213.12</v>
+      </c>
+      <c r="J8" s="75"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -8163,16 +8160,16 @@
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="68" t="s">
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="76"/>
-      <c r="H10" s="76"/>
-      <c r="I10" s="88">
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="74">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1832</v>
       </c>
-      <c r="J10" s="89"/>
+      <c r="J10" s="75"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -8224,7 +8221,7 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="71" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="72"/>
@@ -8248,11 +8245,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="86" t="s">
+      <c r="F14" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
+      <c r="G14" s="77"/>
+      <c r="H14" s="77"/>
       <c r="I14" s="32">
         <f>Samples!F165</f>
         <v>2400</v>
@@ -8277,11 +8274,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="76" t="s">
+      <c r="F15" s="73" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="69"/>
-      <c r="H15" s="69"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
       <c r="I15" s="33">
         <f>Samples!I165</f>
         <v>2280</v>
@@ -8301,14 +8298,14 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="74" t="s">
+      <c r="F16" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
       <c r="I16" s="32">
         <f>Samples!J165</f>
-        <v>2240</v>
+        <v>2320</v>
       </c>
       <c r="J16" s="23" t="s">
         <v>11</v>
@@ -8325,14 +8322,14 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="68" t="s">
+      <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="69"/>
-      <c r="H17" s="69"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
       <c r="I17" s="33">
         <f>Samples!L165</f>
-        <v>4520</v>
+        <v>4600</v>
       </c>
       <c r="J17" s="26" t="s">
         <v>11</v>
@@ -8371,11 +8368,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="86" t="s">
+      <c r="F19" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
       <c r="I19" s="32">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -8395,11 +8392,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="69"/>
-      <c r="H20" s="69"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
       <c r="I20" s="33">
         <f>Samples!P165</f>
         <v>1760</v>
@@ -8436,11 +8433,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="74" t="s">
+      <c r="F22" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
       <c r="I22" s="35">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -8460,11 +8457,11 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="68" t="s">
+      <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
+      <c r="G23" s="78"/>
+      <c r="H23" s="78"/>
       <c r="I23" s="36">
         <f>Samples!K165</f>
         <v>0.60399999999999998</v>
@@ -8484,11 +8481,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="86" t="s">
+      <c r="F24" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
       <c r="I24" s="35">
         <f>Samples!N165</f>
         <v>0.3</v>
@@ -8538,20 +8535,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="85"/>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="85"/>
-      <c r="J27" s="85"/>
-      <c r="K27" s="85"/>
-      <c r="L27" s="85"/>
-      <c r="M27" s="85"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="81"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -8812,6 +8809,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8819,17 +8827,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -8886,20 +8883,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -8929,15 +8926,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8967,15 +8964,15 @@
         <v>-10</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -9559,18 +9556,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9644,20 +9641,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -9687,15 +9684,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9725,15 +9722,15 @@
         <v>-12</v>
       </c>
       <c r="D6" s="1"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -10317,18 +10314,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10402,20 +10399,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -10445,15 +10442,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10476,18 +10473,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -11071,18 +11068,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11152,20 +11149,20 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
       <c r="N2" s="22"/>
       <c r="O2" s="1"/>
     </row>
@@ -11195,15 +11192,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="87"/>
-      <c r="I4" s="87"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="87"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="87"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11226,18 +11223,18 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
     </row>
@@ -11821,18 +11818,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="90"/>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="66"/>
+      <c r="M41" s="66"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11906,40 +11903,40 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="82" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71"/>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -12289,21 +12286,21 @@
         <v>11</v>
       </c>
       <c r="D13" s="27">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E13" s="41">
         <f>(D13+F13)/2</f>
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="F13" s="27">
         <v>2000</v>
       </c>
       <c r="G13" s="41">
         <f>(F13+H13)/2</f>
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="H13" s="27">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="27">
@@ -12609,7 +12606,7 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="73" t="s">
+      <c r="B22" s="71" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="72"/>
@@ -12628,54 +12625,54 @@
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="79" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="77"/>
       <c r="D23" s="29">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="77" t="s">
+      <c r="F23" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="78"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+      <c r="M23" s="85"/>
+      <c r="N23" s="85"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="68" t="s">
+      <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="69"/>
+      <c r="C24" s="78"/>
       <c r="D24" s="31">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="78"/>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="78"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="78"/>
-      <c r="M24" s="78"/>
-      <c r="N24" s="78"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="85"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="85"/>
+      <c r="J24" s="85"/>
+      <c r="K24" s="85"/>
+      <c r="L24" s="85"/>
+      <c r="M24" s="85"/>
+      <c r="N24" s="85"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="75"/>
+      <c r="C25" s="77"/>
       <c r="D25" s="29">
         <v>40</v>
       </c>
@@ -12693,33 +12690,33 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="69"/>
+      <c r="C26" s="78"/>
       <c r="D26" s="31">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="79" t="s">
+      <c r="F26" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
+      <c r="G26" s="83"/>
+      <c r="H26" s="83"/>
+      <c r="I26" s="83"/>
+      <c r="J26" s="83"/>
+      <c r="K26" s="83"/>
+      <c r="L26" s="83"/>
+      <c r="M26" s="83"/>
+      <c r="N26" s="83"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="69"/>
+      <c r="C27" s="78"/>
       <c r="D27" s="31">
         <v>10</v>
       </c>
@@ -12737,21 +12734,21 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="65" t="s">
+      <c r="B28" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
+      <c r="C28" s="88"/>
+      <c r="D28" s="88"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="88"/>
+      <c r="I28" s="88"/>
+      <c r="J28" s="88"/>
+      <c r="K28" s="88"/>
+      <c r="L28" s="88"/>
+      <c r="M28" s="88"/>
+      <c r="N28" s="88"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
@@ -12773,19 +12770,19 @@
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
+      <c r="L30" s="89"/>
+      <c r="M30" s="89"/>
+      <c r="N30" s="89"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
@@ -12977,6 +12974,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12989,14 +12994,6 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13018,29 +13015,29 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="90" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
+      <c r="E1" s="90"/>
+      <c r="F1" s="90"/>
+      <c r="G1" s="90"/>
+      <c r="H1" s="90"/>
+      <c r="I1" s="90"/>
+      <c r="J1" s="90"/>
+      <c r="K1" s="90"/>
+      <c r="L1" s="90"/>
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -14711,29 +14708,29 @@
     </row>
     <row r="41" spans="1:22" ht="32" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="91" t="s">
+      <c r="B41" s="90" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="91"/>
-      <c r="L41" s="91"/>
-      <c r="M41" s="91"/>
-      <c r="N41" s="91"/>
-      <c r="O41" s="91"/>
-      <c r="P41" s="92"/>
-      <c r="Q41" s="92"/>
-      <c r="R41" s="92"/>
-      <c r="S41" s="92"/>
-      <c r="T41" s="92"/>
-      <c r="U41" s="92"/>
-      <c r="V41" s="92"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="90"/>
+      <c r="I41" s="90"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="90"/>
+      <c r="M41" s="90"/>
+      <c r="N41" s="90"/>
+      <c r="O41" s="90"/>
+      <c r="P41" s="91"/>
+      <c r="Q41" s="91"/>
+      <c r="R41" s="91"/>
+      <c r="S41" s="91"/>
+      <c r="T41" s="91"/>
+      <c r="U41" s="91"/>
+      <c r="V41" s="91"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -14882,7 +14879,7 @@
       </c>
       <c r="J45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
@@ -14890,7 +14887,7 @@
       </c>
       <c r="L45" s="50">
         <f>I45+J45</f>
-        <v>3080</v>
+        <v>2680</v>
       </c>
       <c r="M45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
@@ -14968,7 +14965,7 @@
       </c>
       <c r="J46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="K46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
@@ -14976,7 +14973,7 @@
       </c>
       <c r="L46" s="52">
         <f>I46+J46</f>
-        <v>3680</v>
+        <v>3480</v>
       </c>
       <c r="M46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
@@ -15140,7 +15137,7 @@
       </c>
       <c r="J48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="K48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
@@ -15148,7 +15145,7 @@
       </c>
       <c r="L48" s="52">
         <f>I48+J48</f>
-        <v>4880</v>
+        <v>5080</v>
       </c>
       <c r="M48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
@@ -15226,7 +15223,7 @@
       </c>
       <c r="J49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="K49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
@@ -15234,7 +15231,7 @@
       </c>
       <c r="L49" s="50">
         <f>I49+J49</f>
-        <v>5480</v>
+        <v>5880</v>
       </c>
       <c r="M49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
@@ -15872,11 +15869,11 @@
       </c>
       <c r="C66" s="59">
         <f t="shared" si="5"/>
-        <v>1398.3999999999999</v>
+        <v>1390.3999999999999</v>
       </c>
       <c r="D66" s="59">
         <f t="shared" si="6"/>
-        <v>1396.3999999999999</v>
+        <v>1394.3999999999999</v>
       </c>
       <c r="E66" s="59">
         <f t="shared" si="7"/>
@@ -15912,11 +15909,11 @@
       </c>
       <c r="C67" s="60">
         <f t="shared" si="5"/>
-        <v>1552.4</v>
+        <v>1524.4</v>
       </c>
       <c r="D67" s="60">
         <f t="shared" si="6"/>
-        <v>1580.4</v>
+        <v>1568.4</v>
       </c>
       <c r="E67" s="60">
         <f t="shared" si="7"/>
@@ -15924,11 +15921,11 @@
       </c>
       <c r="F67" s="60">
         <f t="shared" si="8"/>
-        <v>1600.4</v>
+        <v>1608.4</v>
       </c>
       <c r="G67" s="60">
         <f t="shared" si="9"/>
-        <v>1592.4</v>
+        <v>1604.4</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -15952,11 +15949,11 @@
       </c>
       <c r="C68" s="59">
         <f t="shared" si="5"/>
-        <v>1706.3999999999999</v>
+        <v>1658.3999999999999</v>
       </c>
       <c r="D68" s="59">
         <f t="shared" si="6"/>
-        <v>1764.3999999999999</v>
+        <v>1742.3999999999999</v>
       </c>
       <c r="E68" s="59">
         <f t="shared" si="7"/>
@@ -15964,11 +15961,11 @@
       </c>
       <c r="F68" s="59">
         <f t="shared" si="8"/>
-        <v>1844.3999999999999</v>
+        <v>1862.3999999999999</v>
       </c>
       <c r="G68" s="59">
         <f t="shared" si="9"/>
-        <v>1866.3999999999996</v>
+        <v>1898.3999999999996</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -15992,11 +15989,11 @@
       </c>
       <c r="C69" s="60">
         <f t="shared" si="5"/>
-        <v>1860.4</v>
+        <v>1792.4</v>
       </c>
       <c r="D69" s="60">
         <f t="shared" si="6"/>
-        <v>1948.4</v>
+        <v>1916.4</v>
       </c>
       <c r="E69" s="60">
         <f t="shared" si="7"/>
@@ -16004,11 +16001,11 @@
       </c>
       <c r="F69" s="60">
         <f t="shared" si="8"/>
-        <v>2088.4</v>
+        <v>2116.4</v>
       </c>
       <c r="G69" s="60">
         <f t="shared" si="9"/>
-        <v>2140.4</v>
+        <v>2192.4</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -16032,11 +16029,11 @@
       </c>
       <c r="C70" s="59">
         <f t="shared" si="5"/>
-        <v>2014.4</v>
+        <v>1926.4</v>
       </c>
       <c r="D70" s="59">
         <f t="shared" si="6"/>
-        <v>2132.4</v>
+        <v>2090.4</v>
       </c>
       <c r="E70" s="59">
         <f t="shared" si="7"/>
@@ -16044,11 +16041,11 @@
       </c>
       <c r="F70" s="59">
         <f t="shared" si="8"/>
-        <v>2332.4</v>
+        <v>2370.4</v>
       </c>
       <c r="G70" s="59">
         <f t="shared" si="9"/>
-        <v>2414.4</v>
+        <v>2486.4000000000005</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -16072,11 +16069,11 @@
       </c>
       <c r="C71" s="60">
         <f t="shared" si="5"/>
-        <v>2168.3999999999996</v>
+        <v>2060.3999999999996</v>
       </c>
       <c r="D71" s="60">
         <f t="shared" si="6"/>
-        <v>2316.3999999999996</v>
+        <v>2264.3999999999996</v>
       </c>
       <c r="E71" s="60">
         <f t="shared" si="7"/>
@@ -16084,11 +16081,11 @@
       </c>
       <c r="F71" s="60">
         <f t="shared" si="8"/>
-        <v>2576.3999999999996</v>
+        <v>2624.3999999999996</v>
       </c>
       <c r="G71" s="60">
         <f t="shared" si="9"/>
-        <v>2688.3999999999996</v>
+        <v>2780.3999999999996</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -16112,11 +16109,11 @@
       </c>
       <c r="C72" s="59">
         <f t="shared" si="5"/>
-        <v>2322.4</v>
+        <v>2194.4</v>
       </c>
       <c r="D72" s="59">
         <f t="shared" si="6"/>
-        <v>2500.4</v>
+        <v>2438.4</v>
       </c>
       <c r="E72" s="59">
         <f t="shared" si="7"/>
@@ -16124,11 +16121,11 @@
       </c>
       <c r="F72" s="59">
         <f t="shared" si="8"/>
-        <v>2820.4</v>
+        <v>2878.4</v>
       </c>
       <c r="G72" s="59">
         <f t="shared" si="9"/>
-        <v>2962.4</v>
+        <v>3074.4</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -16152,11 +16149,11 @@
       </c>
       <c r="C73" s="60">
         <f t="shared" si="5"/>
-        <v>2476.3999999999996</v>
+        <v>2328.3999999999996</v>
       </c>
       <c r="D73" s="60">
         <f t="shared" si="6"/>
-        <v>2684.3999999999996</v>
+        <v>2612.3999999999996</v>
       </c>
       <c r="E73" s="60">
         <f t="shared" si="7"/>
@@ -16164,11 +16161,11 @@
       </c>
       <c r="F73" s="60">
         <f t="shared" si="8"/>
-        <v>3064.3999999999996</v>
+        <v>3132.3999999999996</v>
       </c>
       <c r="G73" s="60">
         <f t="shared" si="9"/>
-        <v>3236.3999999999996</v>
+        <v>3368.3999999999996</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -16192,11 +16189,11 @@
       </c>
       <c r="C74" s="59">
         <f t="shared" si="5"/>
-        <v>2630.4</v>
+        <v>2462.4</v>
       </c>
       <c r="D74" s="59">
         <f t="shared" si="6"/>
-        <v>2868.4</v>
+        <v>2786.4</v>
       </c>
       <c r="E74" s="59">
         <f t="shared" si="7"/>
@@ -16204,11 +16201,11 @@
       </c>
       <c r="F74" s="59">
         <f t="shared" si="8"/>
-        <v>3308.4</v>
+        <v>3386.4</v>
       </c>
       <c r="G74" s="59">
         <f t="shared" si="9"/>
-        <v>3510.4</v>
+        <v>3662.4</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -16365,29 +16362,29 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="92" t="s">
+      <c r="B81" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="C81" s="92"/>
-      <c r="D81" s="92"/>
-      <c r="E81" s="92"/>
-      <c r="F81" s="92"/>
-      <c r="G81" s="92"/>
-      <c r="H81" s="92"/>
-      <c r="I81" s="92"/>
-      <c r="J81" s="92"/>
-      <c r="K81" s="92"/>
-      <c r="L81" s="92"/>
-      <c r="M81" s="92"/>
-      <c r="N81" s="92"/>
-      <c r="O81" s="92"/>
-      <c r="P81" s="92"/>
-      <c r="Q81" s="92"/>
-      <c r="R81" s="92"/>
-      <c r="S81" s="92"/>
-      <c r="T81" s="92"/>
-      <c r="U81" s="92"/>
-      <c r="V81" s="92"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="91"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="91"/>
+      <c r="G81" s="91"/>
+      <c r="H81" s="91"/>
+      <c r="I81" s="91"/>
+      <c r="J81" s="91"/>
+      <c r="K81" s="91"/>
+      <c r="L81" s="91"/>
+      <c r="M81" s="91"/>
+      <c r="N81" s="91"/>
+      <c r="O81" s="91"/>
+      <c r="P81" s="91"/>
+      <c r="Q81" s="91"/>
+      <c r="R81" s="91"/>
+      <c r="S81" s="91"/>
+      <c r="T81" s="91"/>
+      <c r="U81" s="91"/>
+      <c r="V81" s="91"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -16535,7 +16532,7 @@
       </c>
       <c r="J85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
@@ -16543,7 +16540,7 @@
       </c>
       <c r="L85" s="50">
         <f>I85+J85</f>
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="M85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
@@ -16621,7 +16618,7 @@
       </c>
       <c r="J86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="K86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
@@ -16629,7 +16626,7 @@
       </c>
       <c r="L86" s="52">
         <f>I86+J86</f>
-        <v>3155</v>
+        <v>2955</v>
       </c>
       <c r="M86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
@@ -16793,7 +16790,7 @@
       </c>
       <c r="J88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="K88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
@@ -16801,7 +16798,7 @@
       </c>
       <c r="L88" s="52">
         <f>I88+J88</f>
-        <v>5375</v>
+        <v>5575</v>
       </c>
       <c r="M88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
@@ -16879,7 +16876,7 @@
       </c>
       <c r="J89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="K89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
@@ -16887,7 +16884,7 @@
       </c>
       <c r="L89" s="50">
         <f>I89+J89</f>
-        <v>6440</v>
+        <v>6840</v>
       </c>
       <c r="M89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
@@ -18018,29 +18015,29 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="92" t="s">
+      <c r="B121" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="C121" s="92"/>
-      <c r="D121" s="92"/>
-      <c r="E121" s="92"/>
-      <c r="F121" s="92"/>
-      <c r="G121" s="92"/>
-      <c r="H121" s="92"/>
-      <c r="I121" s="92"/>
-      <c r="J121" s="92"/>
-      <c r="K121" s="92"/>
-      <c r="L121" s="92"/>
-      <c r="M121" s="92"/>
-      <c r="N121" s="92"/>
-      <c r="O121" s="92"/>
-      <c r="P121" s="92"/>
-      <c r="Q121" s="92"/>
-      <c r="R121" s="92"/>
-      <c r="S121" s="92"/>
-      <c r="T121" s="92"/>
-      <c r="U121" s="92"/>
-      <c r="V121" s="92"/>
+      <c r="C121" s="91"/>
+      <c r="D121" s="91"/>
+      <c r="E121" s="91"/>
+      <c r="F121" s="91"/>
+      <c r="G121" s="91"/>
+      <c r="H121" s="91"/>
+      <c r="I121" s="91"/>
+      <c r="J121" s="91"/>
+      <c r="K121" s="91"/>
+      <c r="L121" s="91"/>
+      <c r="M121" s="91"/>
+      <c r="N121" s="91"/>
+      <c r="O121" s="91"/>
+      <c r="P121" s="91"/>
+      <c r="Q121" s="91"/>
+      <c r="R121" s="91"/>
+      <c r="S121" s="91"/>
+      <c r="T121" s="91"/>
+      <c r="U121" s="91"/>
+      <c r="V121" s="91"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -18188,7 +18185,7 @@
       </c>
       <c r="J125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="K125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
@@ -18196,7 +18193,7 @@
       </c>
       <c r="L125" s="50">
         <f>I125+J125</f>
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="M125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
@@ -18274,7 +18271,7 @@
       </c>
       <c r="J126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="K126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
@@ -18282,7 +18279,7 @@
       </c>
       <c r="L126" s="52">
         <f>I126+J126</f>
-        <v>3155</v>
+        <v>2955</v>
       </c>
       <c r="M126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
@@ -18446,7 +18443,7 @@
       </c>
       <c r="J128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>2600</v>
+        <v>2800</v>
       </c>
       <c r="K128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
@@ -18454,7 +18451,7 @@
       </c>
       <c r="L128" s="52">
         <f>I128+J128</f>
-        <v>5375</v>
+        <v>5575</v>
       </c>
       <c r="M128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
@@ -18532,7 +18529,7 @@
       </c>
       <c r="J129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="K129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
@@ -18540,7 +18537,7 @@
       </c>
       <c r="L129" s="50">
         <f>I129+J129</f>
-        <v>6440</v>
+        <v>6840</v>
       </c>
       <c r="M129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
@@ -19373,11 +19370,11 @@
       </c>
       <c r="C146" s="59">
         <f t="shared" si="15"/>
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D146" s="59">
         <f t="shared" si="16"/>
-        <v>1072.4000000000001</v>
+        <v>1070.4000000000001</v>
       </c>
       <c r="E146" s="59">
         <f t="shared" si="17"/>
@@ -19428,11 +19425,11 @@
       </c>
       <c r="C147" s="60">
         <f t="shared" si="15"/>
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="D147" s="60">
         <f t="shared" si="16"/>
-        <v>1230.1500000000001</v>
+        <v>1218.1500000000001</v>
       </c>
       <c r="E147" s="60">
         <f t="shared" si="17"/>
@@ -19440,11 +19437,11 @@
       </c>
       <c r="F147" s="60">
         <f t="shared" si="18"/>
-        <v>1934.75</v>
+        <v>1942.75</v>
       </c>
       <c r="G147" s="60">
         <f t="shared" si="19"/>
-        <v>2245.1999999999998</v>
+        <v>2257.1999999999998</v>
       </c>
       <c r="H147" s="60">
         <f t="shared" si="20"/>
@@ -19483,11 +19480,11 @@
       </c>
       <c r="C148" s="59">
         <f t="shared" si="15"/>
-        <v>936</v>
+        <v>888</v>
       </c>
       <c r="D148" s="59">
         <f t="shared" si="16"/>
-        <v>1387.9</v>
+        <v>1365.9</v>
       </c>
       <c r="E148" s="59">
         <f t="shared" si="17"/>
@@ -19495,11 +19492,11 @@
       </c>
       <c r="F148" s="59">
         <f t="shared" si="18"/>
-        <v>2203.5</v>
+        <v>2221.5</v>
       </c>
       <c r="G148" s="59">
         <f t="shared" si="19"/>
-        <v>2567.1999999999998</v>
+        <v>2599.1999999999998</v>
       </c>
       <c r="H148" s="59">
         <f t="shared" si="20"/>
@@ -19538,11 +19535,11 @@
       </c>
       <c r="C149" s="60">
         <f t="shared" si="15"/>
-        <v>1036</v>
+        <v>968</v>
       </c>
       <c r="D149" s="60">
         <f t="shared" si="16"/>
-        <v>1545.65</v>
+        <v>1513.65</v>
       </c>
       <c r="E149" s="60">
         <f t="shared" si="17"/>
@@ -19550,11 +19547,11 @@
       </c>
       <c r="F149" s="60">
         <f t="shared" si="18"/>
-        <v>2472.25</v>
+        <v>2500.25</v>
       </c>
       <c r="G149" s="60">
         <f t="shared" si="19"/>
-        <v>2889.2</v>
+        <v>2941.2</v>
       </c>
       <c r="H149" s="60">
         <f t="shared" si="20"/>
@@ -19593,11 +19590,11 @@
       </c>
       <c r="C150" s="59">
         <f t="shared" si="15"/>
-        <v>1136.0000000000002</v>
+        <v>1048.0000000000002</v>
       </c>
       <c r="D150" s="59">
         <f t="shared" si="16"/>
-        <v>1703.4</v>
+        <v>1661.4</v>
       </c>
       <c r="E150" s="59">
         <f t="shared" si="17"/>
@@ -19605,11 +19602,11 @@
       </c>
       <c r="F150" s="59">
         <f t="shared" si="18"/>
-        <v>2741</v>
+        <v>2779</v>
       </c>
       <c r="G150" s="59">
         <f t="shared" si="19"/>
-        <v>3211.2000000000003</v>
+        <v>3283.2000000000007</v>
       </c>
       <c r="H150" s="59">
         <f t="shared" si="20"/>
@@ -19648,11 +19645,11 @@
       </c>
       <c r="C151" s="60">
         <f t="shared" si="15"/>
-        <v>1236</v>
+        <v>1128</v>
       </c>
       <c r="D151" s="60">
         <f t="shared" si="16"/>
-        <v>1861.1499999999999</v>
+        <v>1809.1499999999999</v>
       </c>
       <c r="E151" s="60">
         <f t="shared" si="17"/>
@@ -19660,11 +19657,11 @@
       </c>
       <c r="F151" s="60">
         <f t="shared" si="18"/>
-        <v>3009.75</v>
+        <v>3057.75</v>
       </c>
       <c r="G151" s="60">
         <f t="shared" si="19"/>
-        <v>3533.2</v>
+        <v>3625.2</v>
       </c>
       <c r="H151" s="60">
         <f t="shared" si="20"/>
@@ -19703,11 +19700,11 @@
       </c>
       <c r="C152" s="59">
         <f t="shared" si="15"/>
-        <v>1336</v>
+        <v>1208</v>
       </c>
       <c r="D152" s="59">
         <f t="shared" si="16"/>
-        <v>2018.9</v>
+        <v>1956.9</v>
       </c>
       <c r="E152" s="59">
         <f t="shared" si="17"/>
@@ -19715,11 +19712,11 @@
       </c>
       <c r="F152" s="59">
         <f t="shared" si="18"/>
-        <v>3278.5</v>
+        <v>3336.5</v>
       </c>
       <c r="G152" s="59">
         <f t="shared" si="19"/>
-        <v>3855.2000000000003</v>
+        <v>3967.2000000000003</v>
       </c>
       <c r="H152" s="59">
         <f t="shared" si="20"/>
@@ -19758,11 +19755,11 @@
       </c>
       <c r="C153" s="60">
         <f t="shared" si="15"/>
-        <v>1436</v>
+        <v>1288</v>
       </c>
       <c r="D153" s="60">
         <f t="shared" si="16"/>
-        <v>2176.6499999999996</v>
+        <v>2104.6499999999996</v>
       </c>
       <c r="E153" s="60">
         <f t="shared" si="17"/>
@@ -19770,11 +19767,11 @@
       </c>
       <c r="F153" s="60">
         <f t="shared" si="18"/>
-        <v>3547.25</v>
+        <v>3615.25</v>
       </c>
       <c r="G153" s="60">
         <f t="shared" si="19"/>
-        <v>4177.2</v>
+        <v>4309.2</v>
       </c>
       <c r="H153" s="60">
         <f t="shared" si="20"/>
@@ -19813,11 +19810,11 @@
       </c>
       <c r="C154" s="59">
         <f t="shared" si="15"/>
-        <v>1536</v>
+        <v>1368</v>
       </c>
       <c r="D154" s="59">
         <f t="shared" si="16"/>
-        <v>2334.4</v>
+        <v>2252.4</v>
       </c>
       <c r="E154" s="59">
         <f t="shared" si="17"/>
@@ -19825,11 +19822,11 @@
       </c>
       <c r="F154" s="59">
         <f t="shared" si="18"/>
-        <v>3816</v>
+        <v>3894</v>
       </c>
       <c r="G154" s="59">
         <f t="shared" si="19"/>
-        <v>4499.2</v>
+        <v>4651.2</v>
       </c>
       <c r="H154" s="59">
         <f t="shared" si="20"/>
@@ -19932,29 +19929,29 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="93" t="s">
+      <c r="B161" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="C161" s="93"/>
-      <c r="D161" s="93"/>
-      <c r="E161" s="93"/>
-      <c r="F161" s="93"/>
-      <c r="G161" s="93"/>
-      <c r="H161" s="93"/>
-      <c r="I161" s="93"/>
-      <c r="J161" s="93"/>
-      <c r="K161" s="93"/>
-      <c r="L161" s="93"/>
-      <c r="M161" s="93"/>
-      <c r="N161" s="93"/>
-      <c r="O161" s="93"/>
-      <c r="P161" s="93"/>
-      <c r="Q161" s="93"/>
-      <c r="R161" s="93"/>
-      <c r="S161" s="93"/>
-      <c r="T161" s="93"/>
-      <c r="U161" s="93"/>
-      <c r="V161" s="93"/>
+      <c r="C161" s="92"/>
+      <c r="D161" s="92"/>
+      <c r="E161" s="92"/>
+      <c r="F161" s="92"/>
+      <c r="G161" s="92"/>
+      <c r="H161" s="92"/>
+      <c r="I161" s="92"/>
+      <c r="J161" s="92"/>
+      <c r="K161" s="92"/>
+      <c r="L161" s="92"/>
+      <c r="M161" s="92"/>
+      <c r="N161" s="92"/>
+      <c r="O161" s="92"/>
+      <c r="P161" s="92"/>
+      <c r="Q161" s="92"/>
+      <c r="R161" s="92"/>
+      <c r="S161" s="92"/>
+      <c r="T161" s="92"/>
+      <c r="U161" s="92"/>
+      <c r="V161" s="92"/>
     </row>
     <row r="164" spans="2:22" ht="44" customHeight="1">
       <c r="B164" s="61" t="s">
@@ -20053,7 +20050,7 @@
       </c>
       <c r="J165" s="63">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
-        <v>2240</v>
+        <v>2320</v>
       </c>
       <c r="K165" s="63">
         <f>IF(Calculator!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R165)+(INDEX(Parameters!$D$14:$H$14,1,R165+1)-INDEX(Parameters!$D$14:$H$14,1,R165))*U165)</f>
@@ -20061,7 +20058,7 @@
       </c>
       <c r="L165" s="63">
         <f>I165+J165</f>
-        <v>4520</v>
+        <v>4600</v>
       </c>
       <c r="M165" s="63">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>

--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8BB36E-8F5B-4273-83D4-C74ED369B666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2864DD24-F19D-42A4-891D-ED0170CD851A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1993,11 +1993,47 @@
     <xf numFmtId="0" fontId="78" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -2011,14 +2047,17 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="24" fillId="15" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -2026,47 +2065,8 @@
     <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="33" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="41" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="42" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="46" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2279,28 +2279,28 @@
                   <c:v>720</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>880.00000000000011</c:v>
+                  <c:v>885.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1040</c:v>
+                  <c:v>1050</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1200</c:v>
+                  <c:v>1215</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1360.0000000000002</c:v>
+                  <c:v>1380.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1520</c:v>
+                  <c:v>1545</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1680</c:v>
+                  <c:v>1710</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1840</c:v>
+                  <c:v>1875</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2000</c:v>
+                  <c:v>2040</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2455,28 +2455,28 @@
                   <c:v>1058.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1246.1500000000001</c:v>
+                  <c:v>1251.1500000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1433.9</c:v>
+                  <c:v>1443.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1621.65</c:v>
+                  <c:v>1636.65</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1809.4</c:v>
+                  <c:v>1829.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1997.1499999999999</c:v>
+                  <c:v>2022.1499999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2184.9</c:v>
+                  <c:v>2214.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2372.6499999999996</c:v>
+                  <c:v>2407.6499999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2560.4</c:v>
+                  <c:v>2600.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2631,28 +2631,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1596.4</c:v>
+                  <c:v>1601.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1810.3999999999999</c:v>
+                  <c:v>1820.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2024.4</c:v>
+                  <c:v>2039.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2238.4</c:v>
+                  <c:v>2258.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2452.3999999999996</c:v>
+                  <c:v>2477.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2666.4</c:v>
+                  <c:v>2696.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2880.3999999999996</c:v>
+                  <c:v>2915.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3094.4</c:v>
+                  <c:v>3134.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2807,28 +2807,28 @@
                   <c:v>1692</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1930.75</c:v>
+                  <c:v>1935.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2169.5</c:v>
+                  <c:v>2179.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2408.25</c:v>
+                  <c:v>2423.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2647</c:v>
+                  <c:v>2667</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2885.75</c:v>
+                  <c:v>2910.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3124.5</c:v>
+                  <c:v>3154.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3363.25</c:v>
+                  <c:v>3398.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3602</c:v>
+                  <c:v>3642</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2983,28 +2983,28 @@
                   <c:v>1987.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2249.1999999999998</c:v>
+                  <c:v>2254.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2511.1999999999998</c:v>
+                  <c:v>2521.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2773.2</c:v>
+                  <c:v>2788.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3035.2000000000003</c:v>
+                  <c:v>3055.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3297.2</c:v>
+                  <c:v>3322.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3559.2000000000003</c:v>
+                  <c:v>3589.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3821.2</c:v>
+                  <c:v>3856.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4083.2</c:v>
+                  <c:v>4123.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3356,31 +3356,31 @@
                   <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1390.3999999999999</c:v>
+                  <c:v>1392.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1524.4</c:v>
+                  <c:v>1531.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1658.3999999999999</c:v>
+                  <c:v>1670.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1792.4</c:v>
+                  <c:v>1809.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1926.4</c:v>
+                  <c:v>1948.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2060.3999999999996</c:v>
+                  <c:v>2087.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2194.4</c:v>
+                  <c:v>2226.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2328.3999999999996</c:v>
+                  <c:v>2365.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2462.4</c:v>
+                  <c:v>2504.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3532,31 +3532,31 @@
                   <c:v>1268.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1394.3999999999999</c:v>
+                  <c:v>1395.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1568.4</c:v>
+                  <c:v>1574.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1742.3999999999999</c:v>
+                  <c:v>1753.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1916.4</c:v>
+                  <c:v>1932.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2090.4</c:v>
+                  <c:v>2111.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2264.3999999999996</c:v>
+                  <c:v>2290.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2438.4</c:v>
+                  <c:v>2469.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2612.3999999999996</c:v>
+                  <c:v>2648.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2786.4</c:v>
+                  <c:v>2827.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3711,28 +3711,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1596.4</c:v>
+                  <c:v>1601.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1810.3999999999999</c:v>
+                  <c:v>1820.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2024.4</c:v>
+                  <c:v>2039.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2238.4</c:v>
+                  <c:v>2258.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2452.3999999999996</c:v>
+                  <c:v>2477.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2666.4</c:v>
+                  <c:v>2696.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2880.3999999999996</c:v>
+                  <c:v>2915.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3094.4</c:v>
+                  <c:v>3134.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3887,28 +3887,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1608.4</c:v>
+                  <c:v>1612.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1862.3999999999999</c:v>
+                  <c:v>1871.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2116.4</c:v>
+                  <c:v>2130.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2370.4</c:v>
+                  <c:v>2389.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2624.3999999999996</c:v>
+                  <c:v>2648.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2878.4</c:v>
+                  <c:v>2907.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3132.3999999999996</c:v>
+                  <c:v>3166.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3386.4</c:v>
+                  <c:v>3425.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4063,28 +4063,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1604.4</c:v>
+                  <c:v>1607.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1898.3999999999996</c:v>
+                  <c:v>1906.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2192.4</c:v>
+                  <c:v>2205.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2486.4000000000005</c:v>
+                  <c:v>2504.4000000000005</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2780.3999999999996</c:v>
+                  <c:v>2803.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3074.4</c:v>
+                  <c:v>3102.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3368.3999999999996</c:v>
+                  <c:v>3401.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3662.4</c:v>
+                  <c:v>3700.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5509,31 +5509,31 @@
                   <c:v>660.00000000000011</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>728</c:v>
+                  <c:v>730</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>808</c:v>
+                  <c:v>815</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>888</c:v>
+                  <c:v>900</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>968</c:v>
+                  <c:v>985</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1048.0000000000002</c:v>
+                  <c:v>1070.0000000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1128</c:v>
+                  <c:v>1155</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1208</c:v>
+                  <c:v>1240</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1288</c:v>
+                  <c:v>1325</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1368</c:v>
+                  <c:v>1410</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5685,31 +5685,31 @@
                   <c:v>970.65000000000009</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1070.4000000000001</c:v>
+                  <c:v>1071.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1218.1500000000001</c:v>
+                  <c:v>1224.1500000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1365.9</c:v>
+                  <c:v>1376.9</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1513.65</c:v>
+                  <c:v>1529.65</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1661.4</c:v>
+                  <c:v>1682.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1809.1499999999999</c:v>
+                  <c:v>1835.1499999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1956.9</c:v>
+                  <c:v>1987.9</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2104.6499999999996</c:v>
+                  <c:v>2140.6499999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2252.4</c:v>
+                  <c:v>2293.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5864,28 +5864,28 @@
                   <c:v>1382.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1596.4</c:v>
+                  <c:v>1601.4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1810.3999999999999</c:v>
+                  <c:v>1820.3999999999999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2024.4</c:v>
+                  <c:v>2039.4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2238.4</c:v>
+                  <c:v>2258.4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2452.3999999999996</c:v>
+                  <c:v>2477.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2666.4</c:v>
+                  <c:v>2696.4</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2880.3999999999996</c:v>
+                  <c:v>2915.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3094.4</c:v>
+                  <c:v>3134.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6040,28 +6040,28 @@
                   <c:v>1692</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1942.75</c:v>
+                  <c:v>1946.75</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2221.5</c:v>
+                  <c:v>2230.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2500.25</c:v>
+                  <c:v>2514.25</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2779</c:v>
+                  <c:v>2798</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3057.75</c:v>
+                  <c:v>3081.75</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3336.5</c:v>
+                  <c:v>3365.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3615.25</c:v>
+                  <c:v>3649.25</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3894</c:v>
+                  <c:v>3933</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6216,28 +6216,28 @@
                   <c:v>1987.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2257.1999999999998</c:v>
+                  <c:v>2260.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2599.1999999999998</c:v>
+                  <c:v>2607.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2941.2</c:v>
+                  <c:v>2954.2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3283.2000000000007</c:v>
+                  <c:v>3301.2000000000007</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3625.2</c:v>
+                  <c:v>3648.2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3967.2000000000003</c:v>
+                  <c:v>3995.2000000000003</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4309.2</c:v>
+                  <c:v>4342.2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4651.2</c:v>
+                  <c:v>4689.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7661,14 +7661,14 @@
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7719,7 +7719,7 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="82" t="s">
         <v>77</v>
       </c>
       <c r="C6" s="6"/>
@@ -7739,7 +7739,7 @@
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="70"/>
+      <c r="B7" s="82"/>
       <c r="C7" s="6"/>
       <c r="D7" s="12" t="s">
         <v>79</v>
@@ -7873,20 +7873,20 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="79"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
@@ -7894,9 +7894,9 @@
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="67"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="67"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -8030,15 +8030,15 @@
         <v>95</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8069,13 +8069,13 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="71" t="s">
+      <c r="F6" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -8116,13 +8116,13 @@
       <c r="F8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="74">
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
+      <c r="I8" s="87">
         <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
-        <v>3213.12</v>
-      </c>
-      <c r="J8" s="75"/>
+        <v>3252.7200000000003</v>
+      </c>
+      <c r="J8" s="88"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -8163,13 +8163,13 @@
       <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="74">
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="87">
         <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
         <v>1832</v>
       </c>
-      <c r="J10" s="75"/>
+      <c r="J10" s="88"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -8221,13 +8221,13 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="71" t="s">
+      <c r="F13" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="72"/>
-      <c r="H13" s="72"/>
-      <c r="I13" s="72"/>
-      <c r="J13" s="72"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
       <c r="I14" s="32">
         <f>Samples!F165</f>
         <v>2400</v>
@@ -8274,11 +8274,11 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="73" t="s">
+      <c r="F15" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
       <c r="I15" s="33">
         <f>Samples!I165</f>
         <v>2280</v>
@@ -8298,14 +8298,14 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="79" t="s">
+      <c r="F16" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
       <c r="I16" s="32">
         <f>Samples!J165</f>
-        <v>2320</v>
+        <v>2420</v>
       </c>
       <c r="J16" s="23" t="s">
         <v>11</v>
@@ -8325,11 +8325,11 @@
       <c r="F17" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
       <c r="I17" s="33">
         <f>Samples!L165</f>
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="J17" s="26" t="s">
         <v>11</v>
@@ -8368,11 +8368,11 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="76" t="s">
+      <c r="F19" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
       <c r="I19" s="32">
         <f>Samples!M165</f>
         <v>2000</v>
@@ -8392,11 +8392,11 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="73" t="s">
+      <c r="F20" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
       <c r="I20" s="33">
         <f>Samples!P165</f>
         <v>1760</v>
@@ -8433,11 +8433,11 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="79" t="s">
+      <c r="F22" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
       <c r="I22" s="35">
         <f>Samples!G165</f>
         <v>0.12</v>
@@ -8460,8 +8460,8 @@
       <c r="F23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
       <c r="I23" s="36">
         <f>Samples!K165</f>
         <v>0.60399999999999998</v>
@@ -8481,11 +8481,11 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
       <c r="I24" s="35">
         <f>Samples!N165</f>
         <v>0.3</v>
@@ -8535,20 +8535,20 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="80" t="s">
+      <c r="B27" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="81"/>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-      <c r="J27" s="81"/>
-      <c r="K27" s="81"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="81"/>
+      <c r="C27" s="84"/>
+      <c r="D27" s="84"/>
+      <c r="E27" s="84"/>
+      <c r="F27" s="84"/>
+      <c r="G27" s="84"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="84"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -8809,17 +8809,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8827,6 +8816,17 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -8926,15 +8926,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9556,18 +9556,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="89"/>
+      <c r="M41" s="89"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9684,15 +9684,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -10314,18 +10314,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="89"/>
+      <c r="M41" s="89"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10442,15 +10442,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11068,18 +11068,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="89"/>
+      <c r="M41" s="89"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11192,15 +11192,15 @@
         <v>1</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="86"/>
+      <c r="J4" s="86"/>
+      <c r="K4" s="86"/>
+      <c r="L4" s="86"/>
+      <c r="M4" s="86"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11818,18 +11818,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="66"/>
-      <c r="M41" s="66"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="89"/>
+      <c r="D41" s="89"/>
+      <c r="E41" s="89"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="89"/>
+      <c r="K41" s="89"/>
+      <c r="L41" s="89"/>
+      <c r="M41" s="89"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11922,21 +11922,21 @@
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -11960,21 +11960,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
@@ -12286,21 +12286,21 @@
         <v>11</v>
       </c>
       <c r="D13" s="27">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E13" s="41">
         <f>(D13+F13)/2</f>
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F13" s="27">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G13" s="41">
         <f>(F13+H13)/2</f>
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="H13" s="27">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="27">
@@ -12606,44 +12606,44 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="71" t="s">
+      <c r="B22" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="71"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="79" t="s">
+      <c r="B23" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="77"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="29">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="84" t="s">
+      <c r="F23" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="85"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="77"/>
+      <c r="K23" s="77"/>
+      <c r="L23" s="77"/>
+      <c r="M23" s="77"/>
+      <c r="N23" s="77"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
@@ -12651,28 +12651,28 @@
       <c r="B24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="78"/>
+      <c r="C24" s="68"/>
       <c r="D24" s="31">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="85"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="85"/>
-      <c r="I24" s="85"/>
-      <c r="J24" s="85"/>
-      <c r="K24" s="85"/>
-      <c r="L24" s="85"/>
-      <c r="M24" s="85"/>
-      <c r="N24" s="85"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="77"/>
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="77"/>
+      <c r="K24" s="77"/>
+      <c r="L24" s="77"/>
+      <c r="M24" s="77"/>
+      <c r="N24" s="77"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="79" t="s">
+      <c r="B25" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C25" s="77"/>
+      <c r="C25" s="74"/>
       <c r="D25" s="29">
         <v>40</v>
       </c>
@@ -12690,25 +12690,25 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="73" t="s">
+      <c r="B26" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="78"/>
+      <c r="C26" s="68"/>
       <c r="D26" s="31">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="86" t="s">
+      <c r="F26" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
@@ -12716,7 +12716,7 @@
       <c r="B27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="78"/>
+      <c r="C27" s="68"/>
       <c r="D27" s="31">
         <v>10</v>
       </c>
@@ -12734,21 +12734,21 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="87" t="s">
+      <c r="B28" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="88"/>
-      <c r="D28" s="88"/>
-      <c r="E28" s="88"/>
-      <c r="F28" s="88"/>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88"/>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88"/>
-      <c r="M28" s="88"/>
-      <c r="N28" s="88"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
@@ -12770,19 +12770,19 @@
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="89"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
-      <c r="L30" s="89"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="89"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
+      <c r="L30" s="67"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="67"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
@@ -12974,14 +12974,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12994,6 +12986,14 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="J5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R5)+(INDEX(Parameters!$J$13:$N$13,1,R5+1)-INDEX(Parameters!$J$13:$N$13,1,R5))*U5,INDEX(Parameters!$D$13:$H$13,1,R5)+(INDEX(Parameters!$D$13:$H$13,1,R5+1)-INDEX(Parameters!$D$13:$H$13,1,R5))*U5)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R5)+(INDEX(Parameters!$D$14:$H$14,1,R5+1)-INDEX(Parameters!$D$14:$H$14,1,R5))*U5)</f>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="L5" s="49">
         <f>I5+J5</f>
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="M5" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S5)+(INDEX(Parameters!$J$17:$N$17,1,S5+1)-INDEX(Parameters!$J$17:$N$17,1,S5))*V5,INDEX(Parameters!$D$17:$H$17,1,S5)+(INDEX(Parameters!$D$17:$H$17,1,S5+1)-INDEX(Parameters!$D$17:$H$17,1,S5))*V5)</f>
@@ -13276,7 +13276,7 @@
       </c>
       <c r="J6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R6)+(INDEX(Parameters!$J$13:$N$13,1,R6+1)-INDEX(Parameters!$J$13:$N$13,1,R6))*U6,INDEX(Parameters!$D$13:$H$13,1,R6)+(INDEX(Parameters!$D$13:$H$13,1,R6+1)-INDEX(Parameters!$D$13:$H$13,1,R6))*U6)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R6)+(INDEX(Parameters!$D$14:$H$14,1,R6+1)-INDEX(Parameters!$D$14:$H$14,1,R6))*U6)</f>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="L6" s="51">
         <f>I6+J6</f>
-        <v>3755</v>
+        <v>3855</v>
       </c>
       <c r="M6" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S6)+(INDEX(Parameters!$J$17:$N$17,1,S6+1)-INDEX(Parameters!$J$17:$N$17,1,S6))*V6,INDEX(Parameters!$D$17:$H$17,1,S6)+(INDEX(Parameters!$D$17:$H$17,1,S6+1)-INDEX(Parameters!$D$17:$H$17,1,S6))*V6)</f>
@@ -13363,7 +13363,7 @@
       </c>
       <c r="J7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R7)+(INDEX(Parameters!$J$13:$N$13,1,R7+1)-INDEX(Parameters!$J$13:$N$13,1,R7))*U7,INDEX(Parameters!$D$13:$H$13,1,R7)+(INDEX(Parameters!$D$13:$H$13,1,R7+1)-INDEX(Parameters!$D$13:$H$13,1,R7))*U7)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R7)+(INDEX(Parameters!$D$14:$H$14,1,R7+1)-INDEX(Parameters!$D$14:$H$14,1,R7))*U7)</f>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="L7" s="49">
         <f>I7+J7</f>
-        <v>4280</v>
+        <v>4380</v>
       </c>
       <c r="M7" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S7)+(INDEX(Parameters!$J$17:$N$17,1,S7+1)-INDEX(Parameters!$J$17:$N$17,1,S7))*V7,INDEX(Parameters!$D$17:$H$17,1,S7)+(INDEX(Parameters!$D$17:$H$17,1,S7+1)-INDEX(Parameters!$D$17:$H$17,1,S7))*V7)</f>
@@ -13450,7 +13450,7 @@
       </c>
       <c r="J8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R8)+(INDEX(Parameters!$J$13:$N$13,1,R8+1)-INDEX(Parameters!$J$13:$N$13,1,R8))*U8,INDEX(Parameters!$D$13:$H$13,1,R8)+(INDEX(Parameters!$D$13:$H$13,1,R8+1)-INDEX(Parameters!$D$13:$H$13,1,R8))*U8)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R8)+(INDEX(Parameters!$D$14:$H$14,1,R8+1)-INDEX(Parameters!$D$14:$H$14,1,R8))*U8)</f>
@@ -13458,7 +13458,7 @@
       </c>
       <c r="L8" s="51">
         <f>I8+J8</f>
-        <v>4775</v>
+        <v>4875</v>
       </c>
       <c r="M8" s="51">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S8)+(INDEX(Parameters!$J$17:$N$17,1,S8+1)-INDEX(Parameters!$J$17:$N$17,1,S8))*V8,INDEX(Parameters!$D$17:$H$17,1,S8)+(INDEX(Parameters!$D$17:$H$17,1,S8+1)-INDEX(Parameters!$D$17:$H$17,1,S8))*V8)</f>
@@ -13537,7 +13537,7 @@
       </c>
       <c r="J9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R9)+(INDEX(Parameters!$J$13:$N$13,1,R9+1)-INDEX(Parameters!$J$13:$N$13,1,R9))*U9,INDEX(Parameters!$D$13:$H$13,1,R9)+(INDEX(Parameters!$D$13:$H$13,1,R9+1)-INDEX(Parameters!$D$13:$H$13,1,R9))*U9)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R9)+(INDEX(Parameters!$D$14:$H$14,1,R9+1)-INDEX(Parameters!$D$14:$H$14,1,R9))*U9)</f>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="L9" s="49">
         <f>I9+J9</f>
-        <v>5240</v>
+        <v>5340</v>
       </c>
       <c r="M9" s="49">
         <f>IF('LSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S9)+(INDEX(Parameters!$J$17:$N$17,1,S9+1)-INDEX(Parameters!$J$17:$N$17,1,S9))*V9,INDEX(Parameters!$D$17:$H$17,1,S9)+(INDEX(Parameters!$D$17:$H$17,1,S9+1)-INDEX(Parameters!$D$17:$H$17,1,S9))*V9)</f>
@@ -14241,23 +14241,23 @@
       </c>
       <c r="C27" s="56">
         <f t="shared" si="0"/>
-        <v>880.00000000000011</v>
+        <v>885.00000000000011</v>
       </c>
       <c r="D27" s="56">
         <f t="shared" si="1"/>
-        <v>1246.1500000000001</v>
+        <v>1251.1500000000001</v>
       </c>
       <c r="E27" s="56">
         <f t="shared" si="2"/>
-        <v>1596.4</v>
+        <v>1601.4</v>
       </c>
       <c r="F27" s="56">
         <f t="shared" si="3"/>
-        <v>1930.75</v>
+        <v>1935.75</v>
       </c>
       <c r="G27" s="56">
         <f t="shared" si="4"/>
-        <v>2249.1999999999998</v>
+        <v>2254.1999999999998</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -14282,23 +14282,23 @@
       </c>
       <c r="C28" s="55">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="D28" s="55">
         <f t="shared" si="1"/>
-        <v>1433.9</v>
+        <v>1443.9</v>
       </c>
       <c r="E28" s="55">
         <f t="shared" si="2"/>
-        <v>1810.3999999999999</v>
+        <v>1820.3999999999999</v>
       </c>
       <c r="F28" s="55">
         <f t="shared" si="3"/>
-        <v>2169.5</v>
+        <v>2179.5</v>
       </c>
       <c r="G28" s="55">
         <f t="shared" si="4"/>
-        <v>2511.1999999999998</v>
+        <v>2521.1999999999998</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -14323,23 +14323,23 @@
       </c>
       <c r="C29" s="56">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1215</v>
       </c>
       <c r="D29" s="56">
         <f t="shared" si="1"/>
-        <v>1621.65</v>
+        <v>1636.65</v>
       </c>
       <c r="E29" s="56">
         <f t="shared" si="2"/>
-        <v>2024.4</v>
+        <v>2039.4</v>
       </c>
       <c r="F29" s="56">
         <f t="shared" si="3"/>
-        <v>2408.25</v>
+        <v>2423.25</v>
       </c>
       <c r="G29" s="56">
         <f t="shared" si="4"/>
-        <v>2773.2</v>
+        <v>2788.2</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -14364,23 +14364,23 @@
       </c>
       <c r="C30" s="55">
         <f t="shared" si="0"/>
-        <v>1360.0000000000002</v>
+        <v>1380.0000000000002</v>
       </c>
       <c r="D30" s="55">
         <f t="shared" si="1"/>
-        <v>1809.4</v>
+        <v>1829.4</v>
       </c>
       <c r="E30" s="55">
         <f t="shared" si="2"/>
-        <v>2238.4</v>
+        <v>2258.4</v>
       </c>
       <c r="F30" s="55">
         <f t="shared" si="3"/>
-        <v>2647</v>
+        <v>2667</v>
       </c>
       <c r="G30" s="55">
         <f t="shared" si="4"/>
-        <v>3035.2000000000003</v>
+        <v>3055.2000000000003</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -14405,23 +14405,23 @@
       </c>
       <c r="C31" s="56">
         <f t="shared" si="0"/>
-        <v>1520</v>
+        <v>1545</v>
       </c>
       <c r="D31" s="56">
         <f t="shared" si="1"/>
-        <v>1997.1499999999999</v>
+        <v>2022.1499999999999</v>
       </c>
       <c r="E31" s="56">
         <f t="shared" si="2"/>
-        <v>2452.3999999999996</v>
+        <v>2477.3999999999996</v>
       </c>
       <c r="F31" s="56">
         <f t="shared" si="3"/>
-        <v>2885.75</v>
+        <v>2910.75</v>
       </c>
       <c r="G31" s="56">
         <f t="shared" si="4"/>
-        <v>3297.2</v>
+        <v>3322.2</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -14446,23 +14446,23 @@
       </c>
       <c r="C32" s="55">
         <f t="shared" si="0"/>
-        <v>1680</v>
+        <v>1710</v>
       </c>
       <c r="D32" s="55">
         <f t="shared" si="1"/>
-        <v>2184.9</v>
+        <v>2214.9</v>
       </c>
       <c r="E32" s="55">
         <f t="shared" si="2"/>
-        <v>2666.4</v>
+        <v>2696.4</v>
       </c>
       <c r="F32" s="55">
         <f t="shared" si="3"/>
-        <v>3124.5</v>
+        <v>3154.5</v>
       </c>
       <c r="G32" s="55">
         <f t="shared" si="4"/>
-        <v>3559.2000000000003</v>
+        <v>3589.2000000000003</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -14487,23 +14487,23 @@
       </c>
       <c r="C33" s="56">
         <f t="shared" si="0"/>
-        <v>1840</v>
+        <v>1875</v>
       </c>
       <c r="D33" s="56">
         <f t="shared" si="1"/>
-        <v>2372.6499999999996</v>
+        <v>2407.6499999999996</v>
       </c>
       <c r="E33" s="56">
         <f t="shared" si="2"/>
-        <v>2880.3999999999996</v>
+        <v>2915.3999999999996</v>
       </c>
       <c r="F33" s="56">
         <f t="shared" si="3"/>
-        <v>3363.25</v>
+        <v>3398.25</v>
       </c>
       <c r="G33" s="56">
         <f t="shared" si="4"/>
-        <v>3821.2</v>
+        <v>3856.2</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -14528,23 +14528,23 @@
       </c>
       <c r="C34" s="55">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>2040</v>
       </c>
       <c r="D34" s="55">
         <f t="shared" si="1"/>
-        <v>2560.4</v>
+        <v>2600.4</v>
       </c>
       <c r="E34" s="55">
         <f t="shared" si="2"/>
-        <v>3094.4</v>
+        <v>3134.4</v>
       </c>
       <c r="F34" s="55">
         <f t="shared" si="3"/>
-        <v>3602</v>
+        <v>3642</v>
       </c>
       <c r="G34" s="55">
         <f t="shared" si="4"/>
-        <v>4083.2</v>
+        <v>4123.2</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="J45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R45)+(INDEX(Parameters!$J$13:$N$13,1,R45+1)-INDEX(Parameters!$J$13:$N$13,1,R45))*U45,INDEX(Parameters!$D$13:$H$13,1,R45)+(INDEX(Parameters!$D$13:$H$13,1,R45+1)-INDEX(Parameters!$D$13:$H$13,1,R45))*U45)</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R45)+(INDEX(Parameters!$D$14:$H$14,1,R45+1)-INDEX(Parameters!$D$14:$H$14,1,R45))*U45)</f>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="L45" s="50">
         <f>I45+J45</f>
-        <v>2680</v>
+        <v>2780</v>
       </c>
       <c r="M45" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S45)+(INDEX(Parameters!$J$17:$N$17,1,S45+1)-INDEX(Parameters!$J$17:$N$17,1,S45))*V45,INDEX(Parameters!$D$17:$H$17,1,S45)+(INDEX(Parameters!$D$17:$H$17,1,S45+1)-INDEX(Parameters!$D$17:$H$17,1,S45))*V45)</f>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="J46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R46)+(INDEX(Parameters!$J$13:$N$13,1,R46+1)-INDEX(Parameters!$J$13:$N$13,1,R46))*U46,INDEX(Parameters!$D$13:$H$13,1,R46)+(INDEX(Parameters!$D$13:$H$13,1,R46+1)-INDEX(Parameters!$D$13:$H$13,1,R46))*U46)</f>
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="K46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R46)+(INDEX(Parameters!$D$14:$H$14,1,R46+1)-INDEX(Parameters!$D$14:$H$14,1,R46))*U46)</f>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="L46" s="52">
         <f>I46+J46</f>
-        <v>3480</v>
+        <v>3580</v>
       </c>
       <c r="M46" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S46)+(INDEX(Parameters!$J$17:$N$17,1,S46+1)-INDEX(Parameters!$J$17:$N$17,1,S46))*V46,INDEX(Parameters!$D$17:$H$17,1,S46)+(INDEX(Parameters!$D$17:$H$17,1,S46+1)-INDEX(Parameters!$D$17:$H$17,1,S46))*V46)</f>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="J47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R47)+(INDEX(Parameters!$J$13:$N$13,1,R47+1)-INDEX(Parameters!$J$13:$N$13,1,R47))*U47,INDEX(Parameters!$D$13:$H$13,1,R47)+(INDEX(Parameters!$D$13:$H$13,1,R47+1)-INDEX(Parameters!$D$13:$H$13,1,R47))*U47)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R47)+(INDEX(Parameters!$D$14:$H$14,1,R47+1)-INDEX(Parameters!$D$14:$H$14,1,R47))*U47)</f>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="L47" s="50">
         <f>I47+J47</f>
-        <v>4280</v>
+        <v>4380</v>
       </c>
       <c r="M47" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S47)+(INDEX(Parameters!$J$17:$N$17,1,S47+1)-INDEX(Parameters!$J$17:$N$17,1,S47))*V47,INDEX(Parameters!$D$17:$H$17,1,S47)+(INDEX(Parameters!$D$17:$H$17,1,S47+1)-INDEX(Parameters!$D$17:$H$17,1,S47))*V47)</f>
@@ -15137,7 +15137,7 @@
       </c>
       <c r="J48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R48)+(INDEX(Parameters!$J$13:$N$13,1,R48+1)-INDEX(Parameters!$J$13:$N$13,1,R48))*U48,INDEX(Parameters!$D$13:$H$13,1,R48)+(INDEX(Parameters!$D$13:$H$13,1,R48+1)-INDEX(Parameters!$D$13:$H$13,1,R48))*U48)</f>
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="K48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R48)+(INDEX(Parameters!$D$14:$H$14,1,R48+1)-INDEX(Parameters!$D$14:$H$14,1,R48))*U48)</f>
@@ -15145,7 +15145,7 @@
       </c>
       <c r="L48" s="52">
         <f>I48+J48</f>
-        <v>5080</v>
+        <v>5180</v>
       </c>
       <c r="M48" s="52">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S48)+(INDEX(Parameters!$J$17:$N$17,1,S48+1)-INDEX(Parameters!$J$17:$N$17,1,S48))*V48,INDEX(Parameters!$D$17:$H$17,1,S48)+(INDEX(Parameters!$D$17:$H$17,1,S48+1)-INDEX(Parameters!$D$17:$H$17,1,S48))*V48)</f>
@@ -15223,7 +15223,7 @@
       </c>
       <c r="J49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R49)+(INDEX(Parameters!$J$13:$N$13,1,R49+1)-INDEX(Parameters!$J$13:$N$13,1,R49))*U49,INDEX(Parameters!$D$13:$H$13,1,R49)+(INDEX(Parameters!$D$13:$H$13,1,R49+1)-INDEX(Parameters!$D$13:$H$13,1,R49))*U49)</f>
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="K49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R49)+(INDEX(Parameters!$D$14:$H$14,1,R49+1)-INDEX(Parameters!$D$14:$H$14,1,R49))*U49)</f>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="L49" s="50">
         <f>I49+J49</f>
-        <v>5880</v>
+        <v>5980</v>
       </c>
       <c r="M49" s="50">
         <f>IF('HSC Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S49)+(INDEX(Parameters!$J$17:$N$17,1,S49+1)-INDEX(Parameters!$J$17:$N$17,1,S49))*V49,INDEX(Parameters!$D$17:$H$17,1,S49)+(INDEX(Parameters!$D$17:$H$17,1,S49+1)-INDEX(Parameters!$D$17:$H$17,1,S49))*V49)</f>
@@ -15869,11 +15869,11 @@
       </c>
       <c r="C66" s="59">
         <f t="shared" si="5"/>
-        <v>1390.3999999999999</v>
+        <v>1392.3999999999999</v>
       </c>
       <c r="D66" s="59">
         <f t="shared" si="6"/>
-        <v>1394.3999999999999</v>
+        <v>1395.3999999999999</v>
       </c>
       <c r="E66" s="59">
         <f t="shared" si="7"/>
@@ -15909,23 +15909,23 @@
       </c>
       <c r="C67" s="60">
         <f t="shared" si="5"/>
-        <v>1524.4</v>
+        <v>1531.4</v>
       </c>
       <c r="D67" s="60">
         <f t="shared" si="6"/>
-        <v>1568.4</v>
+        <v>1574.4</v>
       </c>
       <c r="E67" s="60">
         <f t="shared" si="7"/>
-        <v>1596.4</v>
+        <v>1601.4</v>
       </c>
       <c r="F67" s="60">
         <f t="shared" si="8"/>
-        <v>1608.4</v>
+        <v>1612.4</v>
       </c>
       <c r="G67" s="60">
         <f t="shared" si="9"/>
-        <v>1604.4</v>
+        <v>1607.4</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -15949,23 +15949,23 @@
       </c>
       <c r="C68" s="59">
         <f t="shared" si="5"/>
-        <v>1658.3999999999999</v>
+        <v>1670.3999999999999</v>
       </c>
       <c r="D68" s="59">
         <f t="shared" si="6"/>
-        <v>1742.3999999999999</v>
+        <v>1753.3999999999999</v>
       </c>
       <c r="E68" s="59">
         <f t="shared" si="7"/>
-        <v>1810.3999999999999</v>
+        <v>1820.3999999999999</v>
       </c>
       <c r="F68" s="59">
         <f t="shared" si="8"/>
-        <v>1862.3999999999999</v>
+        <v>1871.3999999999996</v>
       </c>
       <c r="G68" s="59">
         <f t="shared" si="9"/>
-        <v>1898.3999999999996</v>
+        <v>1906.3999999999996</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -15989,23 +15989,23 @@
       </c>
       <c r="C69" s="60">
         <f t="shared" si="5"/>
-        <v>1792.4</v>
+        <v>1809.4</v>
       </c>
       <c r="D69" s="60">
         <f t="shared" si="6"/>
-        <v>1916.4</v>
+        <v>1932.4</v>
       </c>
       <c r="E69" s="60">
         <f t="shared" si="7"/>
-        <v>2024.4</v>
+        <v>2039.4</v>
       </c>
       <c r="F69" s="60">
         <f t="shared" si="8"/>
-        <v>2116.4</v>
+        <v>2130.4</v>
       </c>
       <c r="G69" s="60">
         <f t="shared" si="9"/>
-        <v>2192.4</v>
+        <v>2205.4</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -16029,23 +16029,23 @@
       </c>
       <c r="C70" s="59">
         <f t="shared" si="5"/>
-        <v>1926.4</v>
+        <v>1948.4</v>
       </c>
       <c r="D70" s="59">
         <f t="shared" si="6"/>
-        <v>2090.4</v>
+        <v>2111.4</v>
       </c>
       <c r="E70" s="59">
         <f t="shared" si="7"/>
-        <v>2238.4</v>
+        <v>2258.4</v>
       </c>
       <c r="F70" s="59">
         <f t="shared" si="8"/>
-        <v>2370.4</v>
+        <v>2389.4</v>
       </c>
       <c r="G70" s="59">
         <f t="shared" si="9"/>
-        <v>2486.4000000000005</v>
+        <v>2504.4000000000005</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -16069,23 +16069,23 @@
       </c>
       <c r="C71" s="60">
         <f t="shared" si="5"/>
-        <v>2060.3999999999996</v>
+        <v>2087.3999999999996</v>
       </c>
       <c r="D71" s="60">
         <f t="shared" si="6"/>
-        <v>2264.3999999999996</v>
+        <v>2290.3999999999996</v>
       </c>
       <c r="E71" s="60">
         <f t="shared" si="7"/>
-        <v>2452.3999999999996</v>
+        <v>2477.3999999999996</v>
       </c>
       <c r="F71" s="60">
         <f t="shared" si="8"/>
-        <v>2624.3999999999996</v>
+        <v>2648.3999999999996</v>
       </c>
       <c r="G71" s="60">
         <f t="shared" si="9"/>
-        <v>2780.3999999999996</v>
+        <v>2803.3999999999996</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -16109,23 +16109,23 @@
       </c>
       <c r="C72" s="59">
         <f t="shared" si="5"/>
-        <v>2194.4</v>
+        <v>2226.4</v>
       </c>
       <c r="D72" s="59">
         <f t="shared" si="6"/>
-        <v>2438.4</v>
+        <v>2469.4</v>
       </c>
       <c r="E72" s="59">
         <f t="shared" si="7"/>
-        <v>2666.4</v>
+        <v>2696.4</v>
       </c>
       <c r="F72" s="59">
         <f t="shared" si="8"/>
-        <v>2878.4</v>
+        <v>2907.4</v>
       </c>
       <c r="G72" s="59">
         <f t="shared" si="9"/>
-        <v>3074.4</v>
+        <v>3102.4</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -16149,23 +16149,23 @@
       </c>
       <c r="C73" s="60">
         <f t="shared" si="5"/>
-        <v>2328.3999999999996</v>
+        <v>2365.3999999999996</v>
       </c>
       <c r="D73" s="60">
         <f t="shared" si="6"/>
-        <v>2612.3999999999996</v>
+        <v>2648.3999999999996</v>
       </c>
       <c r="E73" s="60">
         <f t="shared" si="7"/>
-        <v>2880.3999999999996</v>
+        <v>2915.3999999999996</v>
       </c>
       <c r="F73" s="60">
         <f t="shared" si="8"/>
-        <v>3132.3999999999996</v>
+        <v>3166.3999999999996</v>
       </c>
       <c r="G73" s="60">
         <f t="shared" si="9"/>
-        <v>3368.3999999999996</v>
+        <v>3401.3999999999996</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -16189,23 +16189,23 @@
       </c>
       <c r="C74" s="59">
         <f t="shared" si="5"/>
-        <v>2462.4</v>
+        <v>2504.4</v>
       </c>
       <c r="D74" s="59">
         <f t="shared" si="6"/>
-        <v>2786.4</v>
+        <v>2827.4</v>
       </c>
       <c r="E74" s="59">
         <f t="shared" si="7"/>
-        <v>3094.4</v>
+        <v>3134.4</v>
       </c>
       <c r="F74" s="59">
         <f t="shared" si="8"/>
-        <v>3386.4</v>
+        <v>3425.4</v>
       </c>
       <c r="G74" s="59">
         <f t="shared" si="9"/>
-        <v>3662.4</v>
+        <v>3700.4</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="J85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R85)+(INDEX(Parameters!$J$13:$N$13,1,R85+1)-INDEX(Parameters!$J$13:$N$13,1,R85))*U85,INDEX(Parameters!$D$13:$H$13,1,R85)+(INDEX(Parameters!$D$13:$H$13,1,R85+1)-INDEX(Parameters!$D$13:$H$13,1,R85))*U85)</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R85)+(INDEX(Parameters!$D$14:$H$14,1,R85+1)-INDEX(Parameters!$D$14:$H$14,1,R85))*U85)</f>
@@ -16540,7 +16540,7 @@
       </c>
       <c r="L85" s="50">
         <f>I85+J85</f>
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="M85" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S85)+(INDEX(Parameters!$J$17:$N$17,1,S85+1)-INDEX(Parameters!$J$17:$N$17,1,S85))*V85,INDEX(Parameters!$D$17:$H$17,1,S85)+(INDEX(Parameters!$D$17:$H$17,1,S85+1)-INDEX(Parameters!$D$17:$H$17,1,S85))*V85)</f>
@@ -16618,7 +16618,7 @@
       </c>
       <c r="J86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R86)+(INDEX(Parameters!$J$13:$N$13,1,R86+1)-INDEX(Parameters!$J$13:$N$13,1,R86))*U86,INDEX(Parameters!$D$13:$H$13,1,R86)+(INDEX(Parameters!$D$13:$H$13,1,R86+1)-INDEX(Parameters!$D$13:$H$13,1,R86))*U86)</f>
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="K86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R86)+(INDEX(Parameters!$D$14:$H$14,1,R86+1)-INDEX(Parameters!$D$14:$H$14,1,R86))*U86)</f>
@@ -16626,7 +16626,7 @@
       </c>
       <c r="L86" s="52">
         <f>I86+J86</f>
-        <v>2955</v>
+        <v>3055</v>
       </c>
       <c r="M86" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S86)+(INDEX(Parameters!$J$17:$N$17,1,S86+1)-INDEX(Parameters!$J$17:$N$17,1,S86))*V86,INDEX(Parameters!$D$17:$H$17,1,S86)+(INDEX(Parameters!$D$17:$H$17,1,S86+1)-INDEX(Parameters!$D$17:$H$17,1,S86))*V86)</f>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="J87" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R87)+(INDEX(Parameters!$J$13:$N$13,1,R87+1)-INDEX(Parameters!$J$13:$N$13,1,R87))*U87,INDEX(Parameters!$D$13:$H$13,1,R87)+(INDEX(Parameters!$D$13:$H$13,1,R87+1)-INDEX(Parameters!$D$13:$H$13,1,R87))*U87)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K87" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R87)+(INDEX(Parameters!$D$14:$H$14,1,R87+1)-INDEX(Parameters!$D$14:$H$14,1,R87))*U87)</f>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="L87" s="50">
         <f>I87+J87</f>
-        <v>4280</v>
+        <v>4380</v>
       </c>
       <c r="M87" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S87)+(INDEX(Parameters!$J$17:$N$17,1,S87+1)-INDEX(Parameters!$J$17:$N$17,1,S87))*V87,INDEX(Parameters!$D$17:$H$17,1,S87)+(INDEX(Parameters!$D$17:$H$17,1,S87+1)-INDEX(Parameters!$D$17:$H$17,1,S87))*V87)</f>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="J88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R88)+(INDEX(Parameters!$J$13:$N$13,1,R88+1)-INDEX(Parameters!$J$13:$N$13,1,R88))*U88,INDEX(Parameters!$D$13:$H$13,1,R88)+(INDEX(Parameters!$D$13:$H$13,1,R88+1)-INDEX(Parameters!$D$13:$H$13,1,R88))*U88)</f>
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="K88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R88)+(INDEX(Parameters!$D$14:$H$14,1,R88+1)-INDEX(Parameters!$D$14:$H$14,1,R88))*U88)</f>
@@ -16798,7 +16798,7 @@
       </c>
       <c r="L88" s="52">
         <f>I88+J88</f>
-        <v>5575</v>
+        <v>5675</v>
       </c>
       <c r="M88" s="52">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S88)+(INDEX(Parameters!$J$17:$N$17,1,S88+1)-INDEX(Parameters!$J$17:$N$17,1,S88))*V88,INDEX(Parameters!$D$17:$H$17,1,S88)+(INDEX(Parameters!$D$17:$H$17,1,S88+1)-INDEX(Parameters!$D$17:$H$17,1,S88))*V88)</f>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="J89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R89)+(INDEX(Parameters!$J$13:$N$13,1,R89+1)-INDEX(Parameters!$J$13:$N$13,1,R89))*U89,INDEX(Parameters!$D$13:$H$13,1,R89)+(INDEX(Parameters!$D$13:$H$13,1,R89+1)-INDEX(Parameters!$D$13:$H$13,1,R89))*U89)</f>
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="K89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R89)+(INDEX(Parameters!$D$14:$H$14,1,R89+1)-INDEX(Parameters!$D$14:$H$14,1,R89))*U89)</f>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="L89" s="50">
         <f>I89+J89</f>
-        <v>6840</v>
+        <v>6940</v>
       </c>
       <c r="M89" s="50">
         <f>IF('LSR Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S89)+(INDEX(Parameters!$J$17:$N$17,1,S89+1)-INDEX(Parameters!$J$17:$N$17,1,S89))*V89,INDEX(Parameters!$D$17:$H$17,1,S89)+(INDEX(Parameters!$D$17:$H$17,1,S89+1)-INDEX(Parameters!$D$17:$H$17,1,S89))*V89)</f>
@@ -18185,7 +18185,7 @@
       </c>
       <c r="J125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R125)+(INDEX(Parameters!$J$13:$N$13,1,R125+1)-INDEX(Parameters!$J$13:$N$13,1,R125))*U125,INDEX(Parameters!$D$13:$H$13,1,R125)+(INDEX(Parameters!$D$13:$H$13,1,R125+1)-INDEX(Parameters!$D$13:$H$13,1,R125))*U125)</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R125)+(INDEX(Parameters!$D$14:$H$14,1,R125+1)-INDEX(Parameters!$D$14:$H$14,1,R125))*U125)</f>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="L125" s="50">
         <f>I125+J125</f>
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="M125" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S125)+(INDEX(Parameters!$J$17:$N$17,1,S125+1)-INDEX(Parameters!$J$17:$N$17,1,S125))*V125,INDEX(Parameters!$D$17:$H$17,1,S125)+(INDEX(Parameters!$D$17:$H$17,1,S125+1)-INDEX(Parameters!$D$17:$H$17,1,S125))*V125)</f>
@@ -18271,7 +18271,7 @@
       </c>
       <c r="J126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R126)+(INDEX(Parameters!$J$13:$N$13,1,R126+1)-INDEX(Parameters!$J$13:$N$13,1,R126))*U126,INDEX(Parameters!$D$13:$H$13,1,R126)+(INDEX(Parameters!$D$13:$H$13,1,R126+1)-INDEX(Parameters!$D$13:$H$13,1,R126))*U126)</f>
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="K126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R126)+(INDEX(Parameters!$D$14:$H$14,1,R126+1)-INDEX(Parameters!$D$14:$H$14,1,R126))*U126)</f>
@@ -18279,7 +18279,7 @@
       </c>
       <c r="L126" s="52">
         <f>I126+J126</f>
-        <v>2955</v>
+        <v>3055</v>
       </c>
       <c r="M126" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S126)+(INDEX(Parameters!$J$17:$N$17,1,S126+1)-INDEX(Parameters!$J$17:$N$17,1,S126))*V126,INDEX(Parameters!$D$17:$H$17,1,S126)+(INDEX(Parameters!$D$17:$H$17,1,S126+1)-INDEX(Parameters!$D$17:$H$17,1,S126))*V126)</f>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="J127" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R127)+(INDEX(Parameters!$J$13:$N$13,1,R127+1)-INDEX(Parameters!$J$13:$N$13,1,R127))*U127,INDEX(Parameters!$D$13:$H$13,1,R127)+(INDEX(Parameters!$D$13:$H$13,1,R127+1)-INDEX(Parameters!$D$13:$H$13,1,R127))*U127)</f>
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="K127" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R127)+(INDEX(Parameters!$D$14:$H$14,1,R127+1)-INDEX(Parameters!$D$14:$H$14,1,R127))*U127)</f>
@@ -18365,7 +18365,7 @@
       </c>
       <c r="L127" s="50">
         <f>I127+J127</f>
-        <v>4280</v>
+        <v>4380</v>
       </c>
       <c r="M127" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S127)+(INDEX(Parameters!$J$17:$N$17,1,S127+1)-INDEX(Parameters!$J$17:$N$17,1,S127))*V127,INDEX(Parameters!$D$17:$H$17,1,S127)+(INDEX(Parameters!$D$17:$H$17,1,S127+1)-INDEX(Parameters!$D$17:$H$17,1,S127))*V127)</f>
@@ -18443,7 +18443,7 @@
       </c>
       <c r="J128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R128)+(INDEX(Parameters!$J$13:$N$13,1,R128+1)-INDEX(Parameters!$J$13:$N$13,1,R128))*U128,INDEX(Parameters!$D$13:$H$13,1,R128)+(INDEX(Parameters!$D$13:$H$13,1,R128+1)-INDEX(Parameters!$D$13:$H$13,1,R128))*U128)</f>
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="K128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R128)+(INDEX(Parameters!$D$14:$H$14,1,R128+1)-INDEX(Parameters!$D$14:$H$14,1,R128))*U128)</f>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="L128" s="52">
         <f>I128+J128</f>
-        <v>5575</v>
+        <v>5675</v>
       </c>
       <c r="M128" s="52">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S128)+(INDEX(Parameters!$J$17:$N$17,1,S128+1)-INDEX(Parameters!$J$17:$N$17,1,S128))*V128,INDEX(Parameters!$D$17:$H$17,1,S128)+(INDEX(Parameters!$D$17:$H$17,1,S128+1)-INDEX(Parameters!$D$17:$H$17,1,S128))*V128)</f>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="J129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R129)+(INDEX(Parameters!$J$13:$N$13,1,R129+1)-INDEX(Parameters!$J$13:$N$13,1,R129))*U129,INDEX(Parameters!$D$13:$H$13,1,R129)+(INDEX(Parameters!$D$13:$H$13,1,R129+1)-INDEX(Parameters!$D$13:$H$13,1,R129))*U129)</f>
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="K129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R129)+(INDEX(Parameters!$D$14:$H$14,1,R129+1)-INDEX(Parameters!$D$14:$H$14,1,R129))*U129)</f>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="L129" s="50">
         <f>I129+J129</f>
-        <v>6840</v>
+        <v>6940</v>
       </c>
       <c r="M129" s="50">
         <f>IF('Full Sweep'!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S129)+(INDEX(Parameters!$J$17:$N$17,1,S129+1)-INDEX(Parameters!$J$17:$N$17,1,S129))*V129,INDEX(Parameters!$D$17:$H$17,1,S129)+(INDEX(Parameters!$D$17:$H$17,1,S129+1)-INDEX(Parameters!$D$17:$H$17,1,S129))*V129)</f>
@@ -19370,11 +19370,11 @@
       </c>
       <c r="C146" s="59">
         <f t="shared" si="15"/>
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D146" s="59">
         <f t="shared" si="16"/>
-        <v>1070.4000000000001</v>
+        <v>1071.4000000000001</v>
       </c>
       <c r="E146" s="59">
         <f t="shared" si="17"/>
@@ -19425,23 +19425,23 @@
       </c>
       <c r="C147" s="60">
         <f t="shared" si="15"/>
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="D147" s="60">
         <f t="shared" si="16"/>
-        <v>1218.1500000000001</v>
+        <v>1224.1500000000001</v>
       </c>
       <c r="E147" s="60">
         <f t="shared" si="17"/>
-        <v>1596.4</v>
+        <v>1601.4</v>
       </c>
       <c r="F147" s="60">
         <f t="shared" si="18"/>
-        <v>1942.75</v>
+        <v>1946.75</v>
       </c>
       <c r="G147" s="60">
         <f t="shared" si="19"/>
-        <v>2257.1999999999998</v>
+        <v>2260.1999999999998</v>
       </c>
       <c r="H147" s="60">
         <f t="shared" si="20"/>
@@ -19480,23 +19480,23 @@
       </c>
       <c r="C148" s="59">
         <f t="shared" si="15"/>
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D148" s="59">
         <f t="shared" si="16"/>
-        <v>1365.9</v>
+        <v>1376.9</v>
       </c>
       <c r="E148" s="59">
         <f t="shared" si="17"/>
-        <v>1810.3999999999999</v>
+        <v>1820.3999999999999</v>
       </c>
       <c r="F148" s="59">
         <f t="shared" si="18"/>
-        <v>2221.5</v>
+        <v>2230.5</v>
       </c>
       <c r="G148" s="59">
         <f t="shared" si="19"/>
-        <v>2599.1999999999998</v>
+        <v>2607.1999999999998</v>
       </c>
       <c r="H148" s="59">
         <f t="shared" si="20"/>
@@ -19535,23 +19535,23 @@
       </c>
       <c r="C149" s="60">
         <f t="shared" si="15"/>
-        <v>968</v>
+        <v>985</v>
       </c>
       <c r="D149" s="60">
         <f t="shared" si="16"/>
-        <v>1513.65</v>
+        <v>1529.65</v>
       </c>
       <c r="E149" s="60">
         <f t="shared" si="17"/>
-        <v>2024.4</v>
+        <v>2039.4</v>
       </c>
       <c r="F149" s="60">
         <f t="shared" si="18"/>
-        <v>2500.25</v>
+        <v>2514.25</v>
       </c>
       <c r="G149" s="60">
         <f t="shared" si="19"/>
-        <v>2941.2</v>
+        <v>2954.2</v>
       </c>
       <c r="H149" s="60">
         <f t="shared" si="20"/>
@@ -19590,23 +19590,23 @@
       </c>
       <c r="C150" s="59">
         <f t="shared" si="15"/>
-        <v>1048.0000000000002</v>
+        <v>1070.0000000000002</v>
       </c>
       <c r="D150" s="59">
         <f t="shared" si="16"/>
-        <v>1661.4</v>
+        <v>1682.4</v>
       </c>
       <c r="E150" s="59">
         <f t="shared" si="17"/>
-        <v>2238.4</v>
+        <v>2258.4</v>
       </c>
       <c r="F150" s="59">
         <f t="shared" si="18"/>
-        <v>2779</v>
+        <v>2798</v>
       </c>
       <c r="G150" s="59">
         <f t="shared" si="19"/>
-        <v>3283.2000000000007</v>
+        <v>3301.2000000000007</v>
       </c>
       <c r="H150" s="59">
         <f t="shared" si="20"/>
@@ -19645,23 +19645,23 @@
       </c>
       <c r="C151" s="60">
         <f t="shared" si="15"/>
-        <v>1128</v>
+        <v>1155</v>
       </c>
       <c r="D151" s="60">
         <f t="shared" si="16"/>
-        <v>1809.1499999999999</v>
+        <v>1835.1499999999999</v>
       </c>
       <c r="E151" s="60">
         <f t="shared" si="17"/>
-        <v>2452.3999999999996</v>
+        <v>2477.3999999999996</v>
       </c>
       <c r="F151" s="60">
         <f t="shared" si="18"/>
-        <v>3057.75</v>
+        <v>3081.75</v>
       </c>
       <c r="G151" s="60">
         <f t="shared" si="19"/>
-        <v>3625.2</v>
+        <v>3648.2</v>
       </c>
       <c r="H151" s="60">
         <f t="shared" si="20"/>
@@ -19700,23 +19700,23 @@
       </c>
       <c r="C152" s="59">
         <f t="shared" si="15"/>
-        <v>1208</v>
+        <v>1240</v>
       </c>
       <c r="D152" s="59">
         <f t="shared" si="16"/>
-        <v>1956.9</v>
+        <v>1987.9</v>
       </c>
       <c r="E152" s="59">
         <f t="shared" si="17"/>
-        <v>2666.4</v>
+        <v>2696.4</v>
       </c>
       <c r="F152" s="59">
         <f t="shared" si="18"/>
-        <v>3336.5</v>
+        <v>3365.5</v>
       </c>
       <c r="G152" s="59">
         <f t="shared" si="19"/>
-        <v>3967.2000000000003</v>
+        <v>3995.2000000000003</v>
       </c>
       <c r="H152" s="59">
         <f t="shared" si="20"/>
@@ -19755,23 +19755,23 @@
       </c>
       <c r="C153" s="60">
         <f t="shared" si="15"/>
-        <v>1288</v>
+        <v>1325</v>
       </c>
       <c r="D153" s="60">
         <f t="shared" si="16"/>
-        <v>2104.6499999999996</v>
+        <v>2140.6499999999996</v>
       </c>
       <c r="E153" s="60">
         <f t="shared" si="17"/>
-        <v>2880.3999999999996</v>
+        <v>2915.3999999999996</v>
       </c>
       <c r="F153" s="60">
         <f t="shared" si="18"/>
-        <v>3615.25</v>
+        <v>3649.25</v>
       </c>
       <c r="G153" s="60">
         <f t="shared" si="19"/>
-        <v>4309.2</v>
+        <v>4342.2</v>
       </c>
       <c r="H153" s="60">
         <f t="shared" si="20"/>
@@ -19810,23 +19810,23 @@
       </c>
       <c r="C154" s="59">
         <f t="shared" si="15"/>
-        <v>1368</v>
+        <v>1410</v>
       </c>
       <c r="D154" s="59">
         <f t="shared" si="16"/>
-        <v>2252.4</v>
+        <v>2293.4</v>
       </c>
       <c r="E154" s="59">
         <f t="shared" si="17"/>
-        <v>3094.4</v>
+        <v>3134.4</v>
       </c>
       <c r="F154" s="59">
         <f t="shared" si="18"/>
-        <v>3894</v>
+        <v>3933</v>
       </c>
       <c r="G154" s="59">
         <f t="shared" si="19"/>
-        <v>4651.2</v>
+        <v>4689.2</v>
       </c>
       <c r="H154" s="59">
         <f t="shared" si="20"/>
@@ -20050,7 +20050,7 @@
       </c>
       <c r="J165" s="63">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$13:$N$13,1,R165)+(INDEX(Parameters!$J$13:$N$13,1,R165+1)-INDEX(Parameters!$J$13:$N$13,1,R165))*U165,INDEX(Parameters!$D$13:$H$13,1,R165)+(INDEX(Parameters!$D$13:$H$13,1,R165+1)-INDEX(Parameters!$D$13:$H$13,1,R165))*U165)</f>
-        <v>2320</v>
+        <v>2420</v>
       </c>
       <c r="K165" s="63">
         <f>IF(Calculator!$C$4="Type-B",Parameters!$L$14,INDEX(Parameters!$D$14:$H$14,1,R165)+(INDEX(Parameters!$D$14:$H$14,1,R165+1)-INDEX(Parameters!$D$14:$H$14,1,R165))*U165)</f>
@@ -20058,7 +20058,7 @@
       </c>
       <c r="L165" s="63">
         <f>I165+J165</f>
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="M165" s="63">
         <f>IF(Calculator!$C$4="Type-B",INDEX(Parameters!$J$17:$N$17,1,S165)+(INDEX(Parameters!$J$17:$N$17,1,S165+1)-INDEX(Parameters!$J$17:$N$17,1,S165))*V165,INDEX(Parameters!$D$17:$H$17,1,S165)+(INDEX(Parameters!$D$17:$H$17,1,S165+1)-INDEX(Parameters!$D$17:$H$17,1,S165))*V165)</f>

--- a/docs/damping_curve_RAx5.xlsx
+++ b/docs/damping_curve_RAx5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mods\unpacked\un1corn_qlourie_astral_r\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\un1corn\.codex\visualizations\2026\09\05\01a07025-ed7a-7f60-89f7-3275b6531400\xlsx-locale-20261027\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2864DD24-F19D-42A4-891D-ED0170CD851A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3CE58A-093E-4279-B95C-F8D37C45C666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="8" r:id="rId1"/>
@@ -20,7 +20,8 @@
     <sheet name="LSR Sweep" sheetId="3" r:id="rId5"/>
     <sheet name="Full Sweep" sheetId="4" r:id="rId6"/>
     <sheet name="Parameters" sheetId="5" r:id="rId7"/>
-    <sheet name="Samples" sheetId="7" r:id="rId8"/>
+    <sheet name="Locale" sheetId="9" state="hidden" r:id="rId8"/>
+    <sheet name="Samples" sheetId="7" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Catalog!$B$2:$G$18</definedName>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="272">
   <si>
     <t>Valving</t>
   </si>
@@ -51,12 +52,6 @@
     <t>Type-A</t>
   </si>
   <si>
-    <t>固定 HSC</t>
-  </si>
-  <si>
-    <t>固定 LSC</t>
-  </si>
-  <si>
     <t>Type-B</t>
   </si>
   <si>
@@ -90,9 +85,6 @@
     <t>倍率</t>
   </si>
   <si>
-    <t>rebound</t>
-  </si>
-  <si>
     <t>Rebound knee</t>
   </si>
   <si>
@@ -177,12 +169,6 @@
     <t>LSR 区间位置</t>
   </si>
   <si>
-    <t>第一 knee</t>
-  </si>
-  <si>
-    <t>第二 knee</t>
-  </si>
-  <si>
     <t>CTM Racing · RAx5 · Damping Calculator</t>
   </si>
   <si>
@@ -195,15 +181,9 @@
     <t>CTM Racing · RAx5 · Valving Parameters</t>
   </si>
   <si>
-    <t>HSbump · 高速增量</t>
-  </si>
-  <si>
     <t>LSR · R（RA65）</t>
   </si>
   <si>
-    <t>Adjusters · 调节格数</t>
-  </si>
-  <si>
     <t>CTM Racing · RAx5 · LSC Sweep</t>
   </si>
   <si>
@@ -256,12 +236,6 @@
   </si>
   <si>
     <t>固定</t>
-  </si>
-  <si>
-    <t>可调 · 16 clicks</t>
-  </si>
-  <si>
-    <t>可调 · 8 clicks</t>
   </si>
   <si>
     <t>HRS</t>
@@ -280,61 +254,614 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
+    <t>低速压缩 · c</t>
+  </si>
+  <si>
+    <t>高速压缩 · C</t>
+  </si>
+  <si>
+    <t>回弹 · R</t>
+  </si>
+  <si>
+    <t>黄色单元格为手动输入。</t>
+  </si>
+  <si>
+    <t>HSC · 8 系</t>
+  </si>
+  <si>
+    <t>0 为最硬，负数为退出格数。</t>
+  </si>
+  <si>
+    <t>HSC · 6 系</t>
+  </si>
+  <si>
+    <t>连续分段理论曲线，仅基础阻尼。</t>
+  </si>
+  <si>
+    <t>LSC Sweep</t>
+  </si>
+  <si>
+    <t>HSC Sweep</t>
+  </si>
+  <si>
+    <t>LSR Sweep</t>
+  </si>
+  <si>
+    <t>Full Sweep</t>
+  </si>
+  <si>
+    <t>Calculator</t>
+  </si>
+  <si>
+    <t>Type-A</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Language / 语言</t>
+  </si>
+  <si>
+    <t>简体中文</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>en-US</t>
+  </si>
+  <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>chart.rax5CompressionRebound</t>
+  </si>
+  <si>
+    <t>RAx5 · Compression (+) / Rebound (−)</t>
+  </si>
+  <si>
+    <t>RAx5 · 压缩 (+) / 回弹 (−)</t>
+  </si>
+  <si>
+    <t>chart.rax5HscSweep</t>
+  </si>
+  <si>
+    <t>RAx5 · HSC Sweep</t>
+  </si>
+  <si>
+    <t>RAx5 · 高速压缩调节曲线</t>
+  </si>
+  <si>
+    <t>chart.rax5LscSweep</t>
+  </si>
+  <si>
+    <t>RAx5 · LSC Sweep</t>
+  </si>
+  <si>
+    <t>RAx5 · 低速压缩调节曲线</t>
+  </si>
+  <si>
+    <t>chart.rax5LsrSweep</t>
+  </si>
+  <si>
+    <t>RAx5 · LSR Sweep</t>
+  </si>
+  <si>
+    <t>RAx5 · 低速回弹调节曲线</t>
+  </si>
+  <si>
+    <t>label.adjustableEightClicks</t>
+  </si>
+  <si>
+    <t>Adjustable · 8 clicks</t>
+  </si>
+  <si>
+    <t>可调 · 8 格</t>
+  </si>
+  <si>
+    <t>label.adjustableSixteenClicks</t>
+  </si>
+  <si>
+    <t>Adjustable · 16 clicks</t>
+  </si>
+  <si>
+    <t>可调 · 16 格</t>
+  </si>
+  <si>
+    <t>label.adjusterClicks</t>
+  </si>
+  <si>
+    <t>Adjusters · Clicks</t>
+  </si>
+  <si>
+    <t>调节格数</t>
+  </si>
+  <si>
+    <t>label.adjusterPosition</t>
+  </si>
+  <si>
+    <t>Adjuster position</t>
+  </si>
+  <si>
+    <t>label.available</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>label.bump2Multiplier</t>
+  </si>
+  <si>
+    <t>bump2 multiplier</t>
+  </si>
+  <si>
+    <t>label.bumpDampingForceN</t>
+  </si>
+  <si>
+    <t>Bump damping force (N)</t>
+  </si>
+  <si>
+    <t>压缩阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.cTotalClicks</t>
+  </si>
+  <si>
+    <t>c total clicks</t>
+  </si>
+  <si>
+    <t>label.calculator</t>
+  </si>
+  <si>
+    <t>计算器</t>
+  </si>
+  <si>
+    <t>label.clicks</t>
+  </si>
+  <si>
+    <t>clicks</t>
+  </si>
+  <si>
+    <t>label.compressionForceN</t>
+  </si>
+  <si>
+    <t>Compression force (N)</t>
+  </si>
+  <si>
+    <t>label.curve</t>
+  </si>
+  <si>
+    <t>Curve</t>
+  </si>
+  <si>
+    <t>label.damperModel</t>
+  </si>
+  <si>
+    <t>Damper model</t>
+  </si>
+  <si>
+    <t>label.dampingAdjustment</t>
+  </si>
+  <si>
+    <t>Damping adjustment</t>
+  </si>
+  <si>
+    <t>label.dampingForceN</t>
+  </si>
+  <si>
+    <t>Damping force (N)</t>
+  </si>
+  <si>
+    <t>阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.extensionSpeed</t>
+  </si>
+  <si>
+    <t>Extension speed (m/s)</t>
+  </si>
+  <si>
+    <t>伸展速度 (m/s)</t>
+  </si>
+  <si>
+    <t>label.firstKnee</t>
+  </si>
+  <si>
+    <t>First knee</t>
+  </si>
+  <si>
+    <t>第一拐点</t>
+  </si>
+  <si>
+    <t>label.fixed</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>label.fixedHsc</t>
+  </si>
+  <si>
+    <t>Fixed HSC</t>
+  </si>
+  <si>
+    <t>固定高速压缩</t>
+  </si>
+  <si>
+    <t>label.fixedLsc</t>
+  </si>
+  <si>
+    <t>Fixed LSC</t>
+  </si>
+  <si>
+    <t>固定低速压缩</t>
+  </si>
+  <si>
+    <t>label.fullSweep</t>
+  </si>
+  <si>
+    <t>全范围扫描</t>
+  </si>
+  <si>
+    <t>label.highSpeedBumpIncrement</t>
+  </si>
+  <si>
+    <t>HSbump · High-speed increment</t>
+  </si>
+  <si>
+    <t>label.highSpeedCompressionC</t>
+  </si>
+  <si>
+    <t>High-speed compression · C</t>
+  </si>
+  <si>
+    <t>label.hscEightSeries</t>
+  </si>
+  <si>
+    <t>HSC · 8 series</t>
+  </si>
+  <si>
+    <t>label.hscRange</t>
+  </si>
+  <si>
+    <t>HSC range</t>
+  </si>
+  <si>
+    <t>label.hscRangePosition</t>
+  </si>
+  <si>
+    <t>HSC range position</t>
+  </si>
+  <si>
+    <t>label.hscSixSeries</t>
+  </si>
+  <si>
+    <t>HSC · 6 series</t>
+  </si>
+  <si>
+    <t>label.hscSweep</t>
+  </si>
+  <si>
+    <t>HSC 扫描</t>
+  </si>
+  <si>
+    <t>label.hscTotalClicks</t>
+  </si>
+  <si>
+    <t>C total clicks</t>
+  </si>
+  <si>
+    <t>label.hsrMultiplier</t>
+  </si>
+  <si>
+    <t>HSR multiplier</t>
+  </si>
+  <si>
+    <t>label.inputCheck</t>
+  </si>
+  <si>
+    <t>Input check</t>
+  </si>
+  <si>
+    <t>label.lowSpeedCompressionC</t>
+  </si>
+  <si>
+    <t>Low-speed compression · c</t>
+  </si>
+  <si>
+    <t>label.lscAllSeries</t>
+  </si>
+  <si>
+    <t>LSC · All series</t>
+  </si>
+  <si>
+    <t>label.lscRange</t>
+  </si>
+  <si>
+    <t>LSC range</t>
+  </si>
+  <si>
+    <t>label.lscRangePosition</t>
+  </si>
+  <si>
+    <t>LSC range position</t>
+  </si>
+  <si>
+    <t>label.lscSweep</t>
+  </si>
+  <si>
+    <t>LSC 扫描</t>
+  </si>
+  <si>
+    <t>label.lsrRa65EightVariant</t>
+  </si>
+  <si>
+    <t>LSR · RA65 / 8-series variant</t>
+  </si>
+  <si>
+    <t>label.lsrRange</t>
+  </si>
+  <si>
+    <t>LSR range</t>
+  </si>
+  <si>
+    <t>label.lsrRangePosition</t>
+  </si>
+  <si>
+    <t>LSR range position</t>
+  </si>
+  <si>
+    <t>label.lsrSweep</t>
+  </si>
+  <si>
+    <t>LSR 扫描</t>
+  </si>
+  <si>
+    <t>label.lsrTotalClicks</t>
+  </si>
+  <si>
+    <t>R total clicks</t>
+  </si>
+  <si>
+    <t>label.multiplier</t>
+  </si>
+  <si>
+    <t>Multiplier</t>
+  </si>
+  <si>
+    <t>label.pistonTravel</t>
+  </si>
+  <si>
+    <t>Piston travel</t>
+  </si>
+  <si>
+    <t>活塞行程</t>
+  </si>
+  <si>
+    <t>label.rally</t>
+  </si>
+  <si>
+    <t>拉力</t>
+  </si>
+  <si>
+    <t>label.rallycross</t>
+  </si>
+  <si>
     <t>Rallycross</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>低速压缩 · c</t>
-  </si>
-  <si>
-    <t>高速压缩 · C</t>
-  </si>
-  <si>
-    <t>回弹 · R</t>
-  </si>
-  <si>
-    <t>活塞行程</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>跨界拉力</t>
+  </si>
+  <si>
+    <t>label.ratio</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>label.rebound</t>
+  </si>
+  <si>
+    <t>Rebound</t>
+  </si>
+  <si>
+    <t>回弹</t>
+  </si>
+  <si>
+    <t>label.reboundDampingForceN</t>
+  </si>
+  <si>
+    <t>Rebound damping force (N)</t>
+  </si>
+  <si>
+    <t>回弹阻尼力 (N)</t>
+  </si>
+  <si>
+    <t>label.reboundForceN</t>
+  </si>
+  <si>
+    <t>Rebound force (N)</t>
+  </si>
+  <si>
+    <t>label.reboundKnee</t>
+  </si>
+  <si>
+    <t>回弹拐点</t>
+  </si>
+  <si>
+    <t>label.reboundR</t>
+  </si>
+  <si>
+    <t>Rebound · R</t>
+  </si>
+  <si>
+    <t>label.secondKnee</t>
+  </si>
+  <si>
+    <t>Second knee</t>
+  </si>
+  <si>
+    <t>第二拐点</t>
+  </si>
+  <si>
+    <t>label.shaftSpeedMagnitudeMps</t>
+  </si>
+  <si>
+    <t>Shaft speed magnitude (m/s)</t>
+  </si>
+  <si>
+    <t>轴速大小 (m/s)</t>
+  </si>
+  <si>
+    <t>label.shaftSpeedMps</t>
+  </si>
+  <si>
+    <t>Shaft speed (m/s)</t>
+  </si>
+  <si>
+    <t>label.shaftVelocityMps</t>
+  </si>
+  <si>
+    <t>label.specification</t>
+  </si>
+  <si>
+    <t>Specification</t>
+  </si>
+  <si>
+    <t>label.threePlusOneWay</t>
+  </si>
+  <si>
+    <t>3+1 向调节</t>
+  </si>
+  <si>
+    <t>label.threeWay</t>
+  </si>
+  <si>
+    <t>3 向调节</t>
+  </si>
+  <si>
+    <t>label.totalHighSpeedCoefficient</t>
+  </si>
+  <si>
+    <t>Total high-speed coefficient</t>
+  </si>
+  <si>
+    <t>label.totalHsCoefficient</t>
+  </si>
+  <si>
+    <t>Total HS coefficient</t>
+  </si>
+  <si>
+    <t>label.valving</t>
+  </si>
+  <si>
+    <t>阀系</t>
+  </si>
+  <si>
+    <t>note.adjusterClicks</t>
+  </si>
+  <si>
+    <t>0 is the hardest setting; negative values are clicks out.</t>
+  </si>
+  <si>
+    <t>note.baseDampingCurve</t>
+  </si>
+  <si>
+    <t>Continuous piecewise theoretical curve; base damping only.</t>
+  </si>
+  <si>
+    <t>note.sweepEightSeriesClicks</t>
+  </si>
+  <si>
+    <t>Sweep uses 8-series C and 40 R clicks.</t>
+  </si>
+  <si>
+    <t>调节曲线使用 8 系 C、40 格 R。</t>
+  </si>
+  <si>
+    <t>note.yellowInputs</t>
+  </si>
+  <si>
+    <t>Yellow cells are manual inputs.</t>
+  </si>
+  <si>
+    <t>status.checkInput</t>
+  </si>
+  <si>
+    <t>Check input</t>
+  </si>
+  <si>
+    <t>检查输入</t>
+  </si>
+  <si>
+    <t>status.ok</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>title.currentCurveParameters</t>
+  </si>
+  <si>
+    <t>Current curve parameters</t>
+  </si>
+  <si>
+    <t>title.currentDampingForce</t>
+  </si>
+  <si>
+    <t>Current input · damping force magnitude</t>
+  </si>
+  <si>
+    <t>title.raDamperCatalog</t>
   </si>
   <si>
     <t>CTM Racing · RA · Damper Catalog</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄色单元格为手动输入。</t>
-  </si>
-  <si>
-    <t>Sweep 使用 8 系 C、40 格 R。</t>
-  </si>
-  <si>
-    <t>HSC · 8 系</t>
-  </si>
-  <si>
-    <t>0 为最硬，负数为退出格数。</t>
-  </si>
-  <si>
-    <t>HSC · 6 系</t>
-  </si>
-  <si>
-    <t>连续分段理论曲线，仅基础阻尼。</t>
-  </si>
-  <si>
-    <t>LSC Sweep</t>
-  </si>
-  <si>
-    <t>HSC Sweep</t>
-  </si>
-  <si>
-    <t>LSR Sweep</t>
-  </si>
-  <si>
-    <t>Full Sweep</t>
-  </si>
-  <si>
-    <t>Calculator</t>
-  </si>
-  <si>
-    <t>Type-A</t>
+  </si>
+  <si>
+    <t>CTM Racing · RA · 避震器目录</t>
+  </si>
+  <si>
+    <t>title.rax5DampingCalculator</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx5 · 阻尼计算器</t>
+  </si>
+  <si>
+    <t>title.rax5FullSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx5 · 全范围扫描</t>
+  </si>
+  <si>
+    <t>title.rax5HSCSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx5 · HSC 扫描</t>
+  </si>
+  <si>
+    <t>title.rax5LSCSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx5 · LSC 扫描</t>
+  </si>
+  <si>
+    <t>title.rax5LSRSweep</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx5 · LSR 扫描</t>
+  </si>
+  <si>
+    <t>title.rax5ValvingParameters</t>
+  </si>
+  <si>
+    <t>CTM Racing · RAx5 · 阀系参数</t>
+  </si>
+  <si>
+    <t>简体中文</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -347,7 +874,7 @@
     <numFmt numFmtId="177" formatCode="0&quot; mm&quot;"/>
     <numFmt numFmtId="178" formatCode="0&quot; clicks&quot;"/>
   </numFmts>
-  <fonts count="79">
+  <fonts count="81">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -865,8 +1392,21 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="70">
+  <fills count="73">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1213,8 +1753,21 @@
         <fgColor rgb="FFF5F7FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="71">
+  <borders count="72">
     <border>
       <left/>
       <right/>
@@ -1794,6 +2347,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1801,7 +2361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1993,15 +2553,8 @@
     <xf numFmtId="0" fontId="78" fillId="69" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="79" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="80" fillId="72" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="24" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2035,6 +2588,15 @@
     <xf numFmtId="0" fontId="52" fillId="43" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="44" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="45" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2047,14 +2609,11 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="79" fillId="70" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="79" fillId="71" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2064,6 +2623,15 @@
     </xf>
     <xf numFmtId="2" fontId="25" fillId="16" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2103,22 +2671,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx5 · LSC Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$4</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx5 · 低速压缩调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3047,22 +3624,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Bump damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>压缩阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -3075,7 +3661,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -3098,22 +3684,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$59</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -3133,7 +3728,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -3156,7 +3751,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -3179,7 +3774,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -3193,22 +3788,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx5 · HSC Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$3</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx5 · 高速压缩调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4127,22 +4731,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Bump damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>压缩阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -4155,7 +4768,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -4178,22 +4791,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$59</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -4213,7 +4835,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -4236,7 +4858,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -4259,7 +4881,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -4273,22 +4895,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx5 · LSR Sweep</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$5</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx5 · 低速回弹调节曲线</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -5207,22 +5838,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Rebound damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$53</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>回弹阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -5235,7 +5875,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -5258,22 +5898,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Extension speed (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$21</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>伸展速度 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -5286,7 +5935,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -5309,7 +5958,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -5332,7 +5981,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -5346,22 +5995,31 @@
   <c:chart>
     <c:title>
       <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
-                <a:cs typeface="Arial"/>
-              </a:rPr>
-              <a:t>RAx5 · Compression (+) / Rebound (−)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
+        <c:strRef>
+          <c:f>Locale!$D$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>RAx5 · 压缩 (+) / 回弹 (−)</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
       </c:tx>
       <c:overlay val="0"/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="1200">
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="Microsoft YaHei"/>
+              <a:cs typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -7159,22 +7817,31 @@
         </c:majorGridlines>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Damping force (N)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$20</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>阻尼力 (N)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -7187,7 +7854,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -7210,22 +7877,31 @@
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:r>
-                  <a:rPr lang="en-US" sz="900">
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="微软雅黑"/>
-                    <a:cs typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Shaft speed magnitude (m/s)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
+            <c:strRef>
+              <c:f>Locale!$D$58</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>轴速大小 (m/s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:tx>
           <c:overlay val="0"/>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr lang="en-US" sz="900">
+                  <a:latin typeface="Arial"/>
+                  <a:ea typeface="Microsoft YaHei"/>
+                  <a:cs typeface="Arial"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
@@ -7245,7 +7921,7 @@
             <a:pPr>
               <a:defRPr sz="900">
                 <a:latin typeface="Arial"/>
-                <a:ea typeface="微软雅黑"/>
+                <a:ea typeface="Microsoft YaHei"/>
                 <a:cs typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
@@ -7268,7 +7944,7 @@
           <a:pPr>
             <a:defRPr sz="900">
               <a:latin typeface="Arial"/>
-              <a:ea typeface="微软雅黑"/>
+              <a:ea typeface="Microsoft YaHei"/>
               <a:cs typeface="Arial"/>
             </a:defRPr>
           </a:pPr>
@@ -7291,7 +7967,7 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
@@ -7649,26 +8325,39 @@
     <col min="8" max="8" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="12" customHeight="1">
+    <row r="1" spans="1:8" ht="22" customHeight="1">
       <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="86" t="s">
+        <v>271</v>
+      </c>
+      <c r="F1" s="86" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="86" t="s">
+        <v>84</v>
+      </c>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="35" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
+      <c r="B2" s="82" t="str">
+        <f>VLOOKUP("title.raDamperCatalog",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RA · 避震器目录</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
@@ -7685,17 +8374,18 @@
       <c r="A4" s="6"/>
       <c r="B4" s="19"/>
       <c r="C4" s="6"/>
-      <c r="D4" s="9" t="s">
-        <v>62</v>
+      <c r="D4" s="9" t="str">
+        <f>VLOOKUP("label.specification",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>规格</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H4" s="6"/>
     </row>
@@ -7703,8 +8393,9 @@
       <c r="A5" s="6"/>
       <c r="B5" s="19"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="20" t="s">
-        <v>82</v>
+      <c r="D5" s="20" t="str">
+        <f>VLOOKUP("label.pistonTravel",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>活塞行程</v>
       </c>
       <c r="E5" s="15">
         <v>305</v>
@@ -7719,30 +8410,35 @@
     </row>
     <row r="6" spans="1:8" ht="31" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="82" t="s">
-        <v>77</v>
+      <c r="B6" s="84" t="s">
+        <v>68</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="14" t="s">
-        <v>68</v>
+      <c r="D6" s="13" t="str">
+        <f>VLOOKUP("label.dampingAdjustment",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阻尼调节</v>
+      </c>
+      <c r="E6" s="14" t="str">
+        <f>VLOOKUP("label.threeWay",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>3 向调节</v>
+      </c>
+      <c r="F6" s="14" t="str">
+        <f>VLOOKUP("label.threePlusOneWay",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>3+1 向调节</v>
+      </c>
+      <c r="G6" s="14" t="str">
+        <f>VLOOKUP("label.threePlusOneWay",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>3+1 向调节</v>
       </c>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" ht="31" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="82"/>
+      <c r="B7" s="84"/>
       <c r="C7" s="6"/>
-      <c r="D7" s="12" t="s">
-        <v>79</v>
+      <c r="D7" s="12" t="str">
+        <f>VLOOKUP("label.lowSpeedCompressionC",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>低速压缩 · c</v>
       </c>
       <c r="E7" s="16">
         <v>24</v>
@@ -7757,12 +8453,14 @@
     </row>
     <row r="8" spans="1:8" ht="31" customHeight="1">
       <c r="A8" s="6"/>
-      <c r="B8" s="8" t="s">
-        <v>65</v>
+      <c r="B8" s="8" t="str">
+        <f>VLOOKUP("label.rally",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>拉力</v>
       </c>
       <c r="C8" s="6"/>
-      <c r="D8" s="13" t="s">
-        <v>80</v>
+      <c r="D8" s="13" t="str">
+        <f>VLOOKUP("label.highSpeedCompressionC",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>高速压缩 · C</v>
       </c>
       <c r="E8" s="17">
         <v>10</v>
@@ -7777,12 +8475,14 @@
     </row>
     <row r="9" spans="1:8" ht="31" customHeight="1">
       <c r="A9" s="6"/>
-      <c r="B9" s="18" t="s">
-        <v>78</v>
+      <c r="B9" s="18" t="str">
+        <f>VLOOKUP("label.rallycross",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>跨界拉力</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="12" t="s">
-        <v>81</v>
+      <c r="D9" s="12" t="str">
+        <f>VLOOKUP("label.reboundR",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹 · R</v>
       </c>
       <c r="E9" s="16">
         <v>40</v>
@@ -7800,16 +8500,19 @@
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
       <c r="D10" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>72</v>
+        <v>62</v>
+      </c>
+      <c r="E10" s="14" t="str">
+        <f>VLOOKUP("label.fixed",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>固定</v>
+      </c>
+      <c r="F10" s="14" t="str">
+        <f>VLOOKUP("label.adjustableSixteenClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>可调 · 16 格</v>
+      </c>
+      <c r="G10" s="14" t="str">
+        <f>VLOOKUP("label.adjustableEightClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>可调 · 8 格</v>
       </c>
       <c r="H10" s="6"/>
     </row>
@@ -7818,14 +8521,16 @@
       <c r="B11" s="7"/>
       <c r="C11" s="6"/>
       <c r="D11" s="12" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E11" s="21"/>
-      <c r="F11" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>75</v>
+      <c r="F11" s="16" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
+      </c>
+      <c r="G11" s="16" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="H11" s="6"/>
     </row>
@@ -7834,16 +8539,19 @@
       <c r="B12" s="7"/>
       <c r="C12" s="6"/>
       <c r="D12" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="14" t="s">
-        <v>75</v>
+        <v>65</v>
+      </c>
+      <c r="E12" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
+      </c>
+      <c r="F12" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
+      </c>
+      <c r="G12" s="14" t="str">
+        <f>VLOOKUP("label.available",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>有</v>
       </c>
       <c r="H12" s="6"/>
     </row>
@@ -7852,7 +8560,7 @@
       <c r="B13" s="7"/>
       <c r="C13" s="6"/>
       <c r="D13" s="12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
@@ -7873,20 +8581,20 @@
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1">
@@ -7894,9 +8602,9 @@
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1">
@@ -7940,7 +8648,9 @@
       <c r="H21" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B6:B7"/>
@@ -7948,8 +8658,13 @@
     <mergeCell ref="D16:G16"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="E1:G1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"English,简体中文"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7987,8 +8702,9 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>46</v>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax5DampingCalculator",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx5 · 阻尼计算器</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -8023,22 +8739,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="23" t="s">
-        <v>0</v>
+      <c r="B4" s="23" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8061,21 +8778,23 @@
     </row>
     <row r="6" spans="1:15" ht="32" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="25" t="s">
-        <v>57</v>
+      <c r="B6" s="25" t="str">
+        <f>VLOOKUP("label.damperModel",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>避震器型号</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
+      <c r="F6" s="71" t="str">
+        <f>VLOOKUP("title.currentDampingForce",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>当前输入 · 阻尼力大小</v>
+      </c>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -8085,7 +8804,7 @@
     <row r="7" spans="1:15" ht="28" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="27">
         <v>-12</v>
@@ -8106,23 +8825,24 @@
     <row r="8" spans="1:15" ht="28" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="27">
         <v>-4</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="87">
-        <f>IF(C18="OK",Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),"检查输入")</f>
+      <c r="F8" s="1" t="str">
+        <f>VLOOKUP("label.compressionForceN",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>压缩力 (N)</v>
+      </c>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="88">
+        <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$81,4,FALSE),Samples!F165*MIN(C10,Samples!G165)+Samples!I165*MAX(0,C10-Samples!G165)+Samples!J165*MAX(0,C10-Samples!K165),VLOOKUP("status.checkInput",Locale!$A$2:$D$81,4,FALSE))</f>
         <v>3252.7200000000003</v>
       </c>
-      <c r="J8" s="88"/>
+      <c r="J8" s="89"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -8132,7 +8852,7 @@
     <row r="9" spans="1:15" ht="28" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="27">
         <v>-20</v>
@@ -8152,24 +8872,26 @@
     </row>
     <row r="10" spans="1:15" ht="28" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="25" t="s">
-        <v>21</v>
+      <c r="B10" s="25" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C10" s="28">
         <v>1</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="87">
-        <f>IF(C18="OK",Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),"检查输入")</f>
+      <c r="F10" s="1" t="str">
+        <f>VLOOKUP("label.reboundForceN",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹力 (N)</v>
+      </c>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="88">
+        <f>IF(C18=VLOOKUP("status.ok",Locale!$A$2:$D$81,4,FALSE),Samples!M165*MIN(C10,Samples!N165)+Samples!P165*MAX(0,C10-Samples!N165),VLOOKUP("status.checkInput",Locale!$A$2:$D$81,4,FALSE))</f>
         <v>1832</v>
       </c>
-      <c r="J10" s="88"/>
+      <c r="J10" s="89"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -8212,8 +8934,9 @@
     </row>
     <row r="13" spans="1:15" ht="32" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="25" t="s">
-        <v>23</v>
+      <c r="B13" s="25" t="str">
+        <f>VLOOKUP("label.cTotalClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>c 总格数</v>
       </c>
       <c r="C13" s="29">
         <f>Parameters!D23</f>
@@ -8221,13 +8944,14 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
+      <c r="F13" s="71" t="str">
+        <f>VLOOKUP("title.currentCurveParameters",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>当前曲线参数</v>
+      </c>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -8236,8 +8960,9 @@
     </row>
     <row r="14" spans="1:15" ht="28" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="30" t="s">
-        <v>24</v>
+      <c r="B14" s="30" t="str">
+        <f>VLOOKUP("label.hscTotalClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>C 总格数</v>
       </c>
       <c r="C14" s="31">
         <f>IF(C6="RA65",Parameters!D27,Parameters!D24)</f>
@@ -8245,17 +8970,17 @@
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
+      <c r="F14" s="90" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
       <c r="I14" s="32">
         <f>Samples!F165</f>
         <v>2400</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -8265,8 +8990,9 @@
     </row>
     <row r="15" spans="1:15" ht="28" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="25" t="s">
-        <v>25</v>
+      <c r="B15" s="25" t="str">
+        <f>VLOOKUP("label.lsrTotalClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>R 总格数</v>
       </c>
       <c r="C15" s="29">
         <f>IF(C6="RA85",Parameters!D26,Parameters!D25)</f>
@@ -8274,17 +9000,17 @@
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
+      <c r="F15" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="33">
         <f>Samples!I165</f>
         <v>2280</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -8298,17 +9024,18 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
+      <c r="F16" s="72" t="str">
+        <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSbump · 高速增量</v>
+      </c>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
       <c r="I16" s="32">
         <f>Samples!J165</f>
         <v>2420</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -8322,17 +9049,18 @@
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
+      <c r="F17" s="1" t="str">
+        <f>VLOOKUP("label.totalHighSpeedCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总高速系数</v>
+      </c>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
       <c r="I17" s="33">
         <f>Samples!L165</f>
         <v>4700</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -8342,12 +9070,13 @@
     </row>
     <row r="18" spans="1:15" ht="28" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="25" t="s">
-        <v>28</v>
+      <c r="B18" s="25" t="str">
+        <f>VLOOKUP("label.inputCheck",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>输入检查</v>
       </c>
       <c r="C18" s="34" t="str">
-        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="RA65",C6="RA85",C6="RA85/2"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),"OK","检查输入")</f>
-        <v>OK</v>
+        <f>IF(AND(OR(C4="Type-A",C4="Type-B"),OR(C6="RA65",C6="RA85",C6="RA85/2"),COUNT(C7:C10)=4,C7&gt;=-C13,C7&lt;=0,C8&gt;=-C14,C8&lt;=0,C9&gt;=-C15,C9&lt;=0,C10&gt;=0,INT(C7)=C7,INT(C8)=C8,INT(C9)=C9),VLOOKUP("status.ok",Locale!$A$2:$D$81,4,FALSE),VLOOKUP("status.checkInput",Locale!$A$2:$D$81,4,FALSE))</f>
+        <v>正常</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -8368,17 +9097,18 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="85" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
+      <c r="F19" s="90" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
       <c r="I19" s="32">
         <f>Samples!M165</f>
         <v>2000</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -8392,17 +9122,17 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="75" t="s">
-        <v>29</v>
-      </c>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
+      <c r="F20" s="74" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="33">
         <f>Samples!P165</f>
         <v>1760</v>
       </c>
       <c r="J20" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -8433,17 +9163,18 @@
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="73" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
+      <c r="F22" s="72" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
       <c r="I22" s="35">
         <f>Samples!G165</f>
         <v>0.12</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -8457,17 +9188,18 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
+      <c r="F23" s="1" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
       <c r="I23" s="36">
         <f>Samples!K165</f>
         <v>0.60399999999999998</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -8481,17 +9213,18 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="85" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
+      <c r="F24" s="90" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
       <c r="I24" s="35">
         <f>Samples!N165</f>
         <v>0.3</v>
       </c>
       <c r="J24" s="23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -8535,20 +9268,21 @@
     </row>
     <row r="27" spans="1:15" ht="23.15" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="84"/>
-      <c r="D27" s="84"/>
-      <c r="E27" s="84"/>
-      <c r="F27" s="84"/>
-      <c r="G27" s="84"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
-      <c r="L27" s="84"/>
-      <c r="M27" s="84"/>
+      <c r="B27" s="91" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C27" s="92"/>
+      <c r="D27" s="92"/>
+      <c r="E27" s="92"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="92"/>
+      <c r="H27" s="92"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
@@ -8809,6 +9543,17 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="E4:M4"/>
     <mergeCell ref="F6:J6"/>
@@ -8816,17 +9561,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B27:M27"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="5">
@@ -8849,6 +9583,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8883,8 +9618,9 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax5LSCSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx5 · LSC 扫描</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -8919,22 +9655,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="23" t="s">
-        <v>0</v>
+      <c r="B4" s="23" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -8957,8 +9694,9 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="25" t="s">
-        <v>2</v>
+      <c r="B6" s="25" t="str">
+        <f>VLOOKUP("label.fixedHsc",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>固定高速压缩</v>
       </c>
       <c r="C6" s="27">
         <v>-10</v>
@@ -9556,18 +10294,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="89"/>
-      <c r="M41" s="89"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -9606,7 +10344,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -9641,8 +10380,9 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>54</v>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax5HSCSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx5 · HSC 扫描</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -9677,22 +10417,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="23" t="s">
-        <v>0</v>
+      <c r="B4" s="23" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -9715,8 +10456,9 @@
     </row>
     <row r="6" spans="1:15" ht="28" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="25" t="s">
-        <v>3</v>
+      <c r="B6" s="25" t="str">
+        <f>VLOOKUP("label.fixedLsc",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>固定低速压缩</v>
       </c>
       <c r="C6" s="27">
         <v>-12</v>
@@ -10314,18 +11056,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="89"/>
-      <c r="M41" s="89"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -10364,7 +11106,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10399,8 +11142,9 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>55</v>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax5LSRSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx5 · LSR 扫描</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -10435,22 +11179,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="23" t="s">
-        <v>0</v>
+      <c r="B4" s="23" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11068,18 +11813,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="89"/>
-      <c r="M41" s="89"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11114,7 +11859,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11149,8 +11895,9 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>56</v>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax5FullSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx5 · 全范围扫描</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -11185,22 +11932,23 @@
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="23" t="s">
-        <v>0</v>
+      <c r="B4" s="23" t="str">
+        <f>VLOOKUP("label.valving",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>阀系</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
+      <c r="I4" s="87"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
+      <c r="M4" s="87"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
     </row>
@@ -11818,18 +12566,18 @@
     </row>
     <row r="41" spans="1:15" ht="23.15" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="89"/>
-      <c r="C41" s="89"/>
-      <c r="D41" s="89"/>
-      <c r="E41" s="89"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="89"/>
-      <c r="K41" s="89"/>
-      <c r="L41" s="89"/>
-      <c r="M41" s="89"/>
+      <c r="B41" s="93"/>
+      <c r="C41" s="93"/>
+      <c r="D41" s="93"/>
+      <c r="E41" s="93"/>
+      <c r="F41" s="93"/>
+      <c r="G41" s="93"/>
+      <c r="H41" s="93"/>
+      <c r="I41" s="93"/>
+      <c r="J41" s="93"/>
+      <c r="K41" s="93"/>
+      <c r="L41" s="93"/>
+      <c r="M41" s="93"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
@@ -11864,7 +12612,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11903,8 +12652,9 @@
     </row>
     <row r="2" spans="1:15" ht="35" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
-        <v>49</v>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP("title.rax5ValvingParameters",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>CTM Racing · RAx5 · 阀系参数</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -11922,21 +12672,22 @@
     </row>
     <row r="3" spans="1:15" ht="24" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
+      <c r="B3" s="68" t="str">
+        <f>VLOOKUP("note.yellowInputs",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
       <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" ht="28" customHeight="1">
@@ -11960,30 +12711,32 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
+      <c r="J5" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="K5" s="70"/>
+      <c r="L5" s="70"/>
+      <c r="M5" s="70"/>
+      <c r="N5" s="70"/>
       <c r="O5" s="1"/>
     </row>
     <row r="6" spans="1:15" ht="30" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>6</v>
+      <c r="B6" s="37" t="str">
+        <f>VLOOKUP("label.adjusterPosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>调节位置</v>
+      </c>
+      <c r="C6" s="37" t="str">
+        <f>VLOOKUP("label.ratio",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>比例</v>
       </c>
       <c r="D6" s="38">
         <v>0</v>
@@ -12026,10 +12779,11 @@
     <row r="7" spans="1:15" ht="29" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>8</v>
+        <v>5</v>
+      </c>
+      <c r="C7" s="25" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D7" s="29">
         <f>(D$6-1)*$D$23</f>
@@ -12077,10 +12831,11 @@
     <row r="8" spans="1:15" ht="29" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="C8" s="30" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D8" s="31">
         <f>(D$6-1)*$D$24</f>
@@ -12145,10 +12900,10 @@
     <row r="10" spans="1:15" ht="29" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" s="27">
         <v>1200</v>
@@ -12189,11 +12944,12 @@
     </row>
     <row r="11" spans="1:15" ht="29" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="30" t="s">
-        <v>44</v>
+      <c r="B11" s="30" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D11" s="40">
         <v>0.12</v>
@@ -12235,10 +12991,11 @@
     <row r="12" spans="1:15" ht="29" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="C12" s="25" t="str">
+        <f>VLOOKUP("label.multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>倍率</v>
       </c>
       <c r="D12" s="40">
         <v>1</v>
@@ -12279,11 +13036,12 @@
     </row>
     <row r="13" spans="1:15" ht="29" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="30" t="s">
-        <v>50</v>
+      <c r="B13" s="30" t="str">
+        <f>VLOOKUP("label.highSpeedBumpIncrement",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSbump · 高速增量</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D13" s="27">
         <v>500</v>
@@ -12324,11 +13082,12 @@
     </row>
     <row r="14" spans="1:15" ht="29" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="25" t="s">
-        <v>45</v>
+      <c r="B14" s="25" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="40">
         <v>0.57999999999999996</v>
@@ -12387,10 +13146,11 @@
     <row r="16" spans="1:15" ht="30" customHeight="1">
       <c r="A16" s="1"/>
       <c r="B16" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>8</v>
+        <v>45</v>
+      </c>
+      <c r="C16" s="37" t="str">
+        <f>VLOOKUP("label.clicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>格</v>
       </c>
       <c r="D16" s="43">
         <f>(D$6-1)*$D$25</f>
@@ -12437,11 +13197,12 @@
     </row>
     <row r="17" spans="1:15" ht="29" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="23" t="s">
-        <v>15</v>
+      <c r="B17" s="23" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D17" s="27">
         <v>1100</v>
@@ -12482,11 +13243,12 @@
     </row>
     <row r="18" spans="1:15" ht="29" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="26" t="s">
-        <v>16</v>
+      <c r="B18" s="26" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" s="40">
         <v>0.25</v>
@@ -12528,10 +13290,11 @@
     <row r="19" spans="1:15" ht="29" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="25" t="s">
         <v>14</v>
+      </c>
+      <c r="C19" s="25" t="str">
+        <f>VLOOKUP("label.multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>倍率</v>
       </c>
       <c r="D19" s="40">
         <v>0.96</v>
@@ -12606,73 +13369,78 @@
     </row>
     <row r="22" spans="1:15" ht="32" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="72" t="s">
-        <v>52</v>
-      </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
+      <c r="B22" s="71" t="str">
+        <f>VLOOKUP("label.adjusterClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>调节格数</v>
+      </c>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
       <c r="O22" s="1"/>
     </row>
     <row r="23" spans="1:15" ht="29" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="73" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="74"/>
+      <c r="B23" s="72" t="str">
+        <f>VLOOKUP("label.lscAllSeries",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC · 全系列</v>
+      </c>
+      <c r="C23" s="73"/>
       <c r="D23" s="29">
         <v>24</v>
       </c>
       <c r="E23" s="1"/>
-      <c r="F23" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="77"/>
+      <c r="F23" s="75" t="str">
+        <f>VLOOKUP("note.sweepEightSeriesClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>调节曲线使用 8 系 C、40 格 R。</v>
+      </c>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="76"/>
       <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" ht="29" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="68"/>
+      <c r="B24" s="1" t="str">
+        <f>VLOOKUP("label.hscEightSeries",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC · 8 系</v>
+      </c>
+      <c r="C24" s="67"/>
       <c r="D24" s="31">
         <v>20</v>
       </c>
       <c r="E24" s="1"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="77"/>
-      <c r="N24" s="77"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="76"/>
+      <c r="H24" s="76"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="76"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="76"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="76"/>
       <c r="O24" s="1"/>
     </row>
     <row r="25" spans="1:15" ht="29" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="74"/>
+      <c r="B25" s="72" t="str">
+        <f>VLOOKUP("label.lsrRa65EightVariant",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR · RA65 / 8系改型</v>
+      </c>
+      <c r="C25" s="73"/>
       <c r="D25" s="29">
         <v>40</v>
       </c>
@@ -12690,33 +13458,35 @@
     </row>
     <row r="26" spans="1:15" ht="29" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="75" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="68"/>
+      <c r="B26" s="74" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="67"/>
       <c r="D26" s="31">
         <v>60</v>
       </c>
       <c r="E26" s="1"/>
-      <c r="F26" s="78" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70"/>
+      <c r="F26" s="77" t="str">
+        <f>VLOOKUP("note.adjusterClicks",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>0 为最硬，负数为退出格数。</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="69"/>
+      <c r="L26" s="69"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="69"/>
       <c r="O26" s="1"/>
     </row>
     <row r="27" spans="1:15" ht="29" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="68"/>
+      <c r="B27" s="1" t="str">
+        <f>VLOOKUP("label.hscSixSeries",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC · 6 系</v>
+      </c>
+      <c r="C27" s="67"/>
       <c r="D27" s="31">
         <v>10</v>
       </c>
@@ -12734,21 +13504,22 @@
     </row>
     <row r="28" spans="1:15" ht="24" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
+      <c r="B28" s="78" t="str">
+        <f>VLOOKUP("note.baseDampingCurve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>连续分段理论曲线，仅基础阻尼。</v>
+      </c>
+      <c r="C28" s="79"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
       <c r="O28" s="1"/>
     </row>
     <row r="29" spans="1:15" ht="23.15" customHeight="1">
@@ -12770,19 +13541,19 @@
     </row>
     <row r="30" spans="1:15" ht="31" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="67"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="N30" s="67"/>
+      <c r="B30" s="80"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="80"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="80"/>
+      <c r="N30" s="80"/>
       <c r="O30" s="1"/>
     </row>
     <row r="31" spans="1:15" ht="23.15" customHeight="1">
@@ -12974,6 +13745,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B33:N33"/>
+    <mergeCell ref="B34:N34"/>
+    <mergeCell ref="B35:N35"/>
+    <mergeCell ref="B28:N28"/>
+    <mergeCell ref="B29:N29"/>
+    <mergeCell ref="B30:N30"/>
+    <mergeCell ref="B31:N31"/>
+    <mergeCell ref="B32:N32"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="B3:N3"/>
@@ -12986,21 +13765,1239 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="F23:N24"/>
     <mergeCell ref="F26:N26"/>
-    <mergeCell ref="B33:N33"/>
-    <mergeCell ref="B34:N34"/>
-    <mergeCell ref="B35:N35"/>
-    <mergeCell ref="B28:N28"/>
-    <mergeCell ref="B29:N29"/>
-    <mergeCell ref="B30:N30"/>
-    <mergeCell ref="B31:N31"/>
-    <mergeCell ref="B32:N32"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="66" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="66" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B2,C2)</f>
+        <v>RAx5 · 压缩 (+) / 回弹 (−)</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B3,C3)</f>
+        <v>RAx5 · 高速压缩调节曲线</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B4,C4)</f>
+        <v>RAx5 · 低速压缩调节曲线</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B5,C5)</f>
+        <v>RAx5 · 低速回弹调节曲线</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B6,C6)</f>
+        <v>可调 · 8 格</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B7,C7)</f>
+        <v>可调 · 16 格</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="65" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B8,C8)</f>
+        <v>调节格数</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B9,C9)</f>
+        <v>调节位置</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="65" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>113</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B10,C10)</f>
+        <v>有</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B11,C11)</f>
+        <v>bump2 倍率</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B12,C12)</f>
+        <v>压缩阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B13,C13)</f>
+        <v>c 总格数</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B14,C14)</f>
+        <v>计算器</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B15,C15)</f>
+        <v>格</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B16,C16)</f>
+        <v>压缩力 (N)</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B17,C17)</f>
+        <v>曲线</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B18,C18)</f>
+        <v>避震器型号</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B19,C19)</f>
+        <v>阻尼调节</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B20,C20)</f>
+        <v>阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="65" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B21,C21)</f>
+        <v>伸展速度 (m/s)</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B22,C22)</f>
+        <v>第一拐点</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="65" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B23,C23)</f>
+        <v>固定</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B24,C24)</f>
+        <v>固定高速压缩</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B25,C25)</f>
+        <v>固定低速压缩</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="D26" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B26,C26)</f>
+        <v>全范围扫描</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B27,C27)</f>
+        <v>HSbump · 高速增量</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="B28" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B28,C28)</f>
+        <v>高速压缩 · C</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B29,C29)</f>
+        <v>HSC · 8 系</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B30,C30)</f>
+        <v>HSC 区间</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="B31" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="C31" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B31,C31)</f>
+        <v>HSC 区间位置</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="65" t="s">
+        <v>75</v>
+      </c>
+      <c r="D32" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B32,C32)</f>
+        <v>HSC · 6 系</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="B33" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B33,C33)</f>
+        <v>HSC 扫描</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B34,C34)</f>
+        <v>C 总格数</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B35,C35)</f>
+        <v>HSR 倍率</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B36,C36)</f>
+        <v>输入检查</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="B37" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B37,C37)</f>
+        <v>低速压缩 · c</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B38,C38)</f>
+        <v>LSC · 全系列</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="C39" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B39,C39)</f>
+        <v>LSC 区间</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="B40" s="65" t="s">
+        <v>179</v>
+      </c>
+      <c r="C40" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B40,C40)</f>
+        <v>LSC 区间位置</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="65" t="s">
+        <v>180</v>
+      </c>
+      <c r="B41" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="65" t="s">
+        <v>181</v>
+      </c>
+      <c r="D41" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B41,C41)</f>
+        <v>LSC 扫描</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="65" t="s">
+        <v>182</v>
+      </c>
+      <c r="B42" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C42" s="65" t="s">
+        <v>53</v>
+      </c>
+      <c r="D42" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B42,C42)</f>
+        <v>LSR · RA65 / 8系改型</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="B43" s="65" t="s">
+        <v>185</v>
+      </c>
+      <c r="C43" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B43,C43)</f>
+        <v>LSR 区间</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B44" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="65" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B44,C44)</f>
+        <v>LSR 区间位置</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" s="65" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B45,C45)</f>
+        <v>LSR 扫描</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="C46" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="D46" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B46,C46)</f>
+        <v>R 总格数</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="C47" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B47,C47)</f>
+        <v>倍率</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="65" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B48,C48)</f>
+        <v>活塞行程</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B49,C49)</f>
+        <v>拉力</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="C50" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="D50" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B50,C50)</f>
+        <v>跨界拉力</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="65" t="s">
+        <v>202</v>
+      </c>
+      <c r="B51" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="C51" s="65" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B51,C51)</f>
+        <v>比例</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="65" t="s">
+        <v>204</v>
+      </c>
+      <c r="B52" s="65" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="D52" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B52,C52)</f>
+        <v>回弹</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="B53" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="C53" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="D53" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B53,C53)</f>
+        <v>回弹阻尼力 (N)</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="65" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B54,C54)</f>
+        <v>回弹力 (N)</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="B55" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="D55" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B55,C55)</f>
+        <v>回弹拐点</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="B56" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="C56" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B56,C56)</f>
+        <v>回弹 · R</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B57" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="C57" s="65" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B57,C57)</f>
+        <v>第二拐点</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="C58" s="65" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B58,C58)</f>
+        <v>轴速大小 (m/s)</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="65" t="s">
+        <v>222</v>
+      </c>
+      <c r="B59" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C59" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B59,C59)</f>
+        <v>轴速 (m/s)</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="65" t="s">
+        <v>224</v>
+      </c>
+      <c r="B60" s="65" t="s">
+        <v>223</v>
+      </c>
+      <c r="C60" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B60,C60)</f>
+        <v>轴速 (m/s)</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="C61" s="65" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B61,C61)</f>
+        <v>规格</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" s="65" t="s">
+        <v>61</v>
+      </c>
+      <c r="C62" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="D62" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B62,C62)</f>
+        <v>3+1 向调节</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" s="65" t="s">
+        <v>60</v>
+      </c>
+      <c r="C63" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="D63" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B63,C63)</f>
+        <v>3 向调节</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B64,C64)</f>
+        <v>总高速系数</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B65,C65)</f>
+        <v>总 HS 系数</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="D66" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B66,C66)</f>
+        <v>阀系</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B67,C67)</f>
+        <v>0 为最硬，负数为退出格数。</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="C68" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B68,C68)</f>
+        <v>连续分段理论曲线，仅基础阻尼。</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" s="65" t="s">
+        <v>242</v>
+      </c>
+      <c r="C69" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="D69" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B69,C69)</f>
+        <v>调节曲线使用 8 系 C、40 格 R。</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="65" t="s">
+        <v>244</v>
+      </c>
+      <c r="B70" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="C70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B70,C70)</f>
+        <v>黄色单元格为手动输入。</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" s="65" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="D71" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B71,C71)</f>
+        <v>检查输入</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="B72" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="C72" s="65" t="s">
+        <v>251</v>
+      </c>
+      <c r="D72" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B72,C72)</f>
+        <v>正常</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="B73" s="65" t="s">
+        <v>253</v>
+      </c>
+      <c r="C73" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B73,C73)</f>
+        <v>当前曲线参数</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="65" t="s">
+        <v>254</v>
+      </c>
+      <c r="B74" s="65" t="s">
+        <v>255</v>
+      </c>
+      <c r="C74" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B74,C74)</f>
+        <v>当前输入 · 阻尼力大小</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="65" t="s">
+        <v>256</v>
+      </c>
+      <c r="B75" s="65" t="s">
+        <v>257</v>
+      </c>
+      <c r="C75" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="D75" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B75,C75)</f>
+        <v>CTM Racing · RA · 避震器目录</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="B76" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="D76" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B76,C76)</f>
+        <v>CTM Racing · RAx5 · 阻尼计算器</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="B77" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="D77" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B77,C77)</f>
+        <v>CTM Racing · RAx5 · 全范围扫描</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="65" t="s">
+        <v>263</v>
+      </c>
+      <c r="B78" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="D78" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B78,C78)</f>
+        <v>CTM Racing · RAx5 · HSC 扫描</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="65" t="s">
+        <v>265</v>
+      </c>
+      <c r="B79" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="D79" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B79,C79)</f>
+        <v>CTM Racing · RAx5 · LSC 扫描</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80" s="65" t="s">
+        <v>268</v>
+      </c>
+      <c r="D80" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B80,C80)</f>
+        <v>CTM Racing · RAx5 · LSR 扫描</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="B81" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="D81" s="65" t="str">
+        <f>IF(Catalog!$E$1="English",B81,C81)</f>
+        <v>CTM Racing · RAx5 · 阀系参数</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04BB332A-2C6E-481C-890D-8B5D85D2F769}">
   <sheetPr>
     <tabColor rgb="FF93A0AC"/>
@@ -13015,29 +15012,30 @@
   <sheetData>
     <row r="1" spans="1:22" ht="32" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="90" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="90"/>
-      <c r="G1" s="90"/>
-      <c r="H1" s="90"/>
-      <c r="I1" s="90"/>
-      <c r="J1" s="90"/>
-      <c r="K1" s="90"/>
-      <c r="L1" s="90"/>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
+      <c r="B1" s="94" t="str">
+        <f>VLOOKUP("label.lscSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 扫描</v>
+      </c>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
     </row>
     <row r="2" spans="1:22" ht="22" customHeight="1">
       <c r="A2" s="1"/>
@@ -13089,68 +15087,82 @@
     </row>
     <row r="4" spans="1:22" ht="44" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="45" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="46" t="s">
+      <c r="F4" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="45" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H4" s="45" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="46" t="s">
+      <c r="K4" s="45" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L4" s="45" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M4" s="46" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N4" s="46" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O4" s="45" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P4" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="46" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="P4" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="48" t="s">
-        <v>43</v>
+      <c r="Q4" s="48" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R4" s="48" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S4" s="48" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T4" s="48" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U4" s="48" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V4" s="48" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="25" customHeight="1">
@@ -13662,8 +15674,9 @@
     </row>
     <row r="13" spans="1:22" ht="30" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="53" t="s">
-        <v>21</v>
+      <c r="B13" s="53" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C13" s="54" t="str">
         <f>B5</f>
@@ -14708,29 +16721,30 @@
     </row>
     <row r="41" spans="1:22" ht="32" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="90" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="90"/>
-      <c r="D41" s="90"/>
-      <c r="E41" s="90"/>
-      <c r="F41" s="90"/>
-      <c r="G41" s="90"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="90"/>
-      <c r="L41" s="90"/>
-      <c r="M41" s="90"/>
-      <c r="N41" s="90"/>
-      <c r="O41" s="90"/>
-      <c r="P41" s="91"/>
-      <c r="Q41" s="91"/>
-      <c r="R41" s="91"/>
-      <c r="S41" s="91"/>
-      <c r="T41" s="91"/>
-      <c r="U41" s="91"/>
-      <c r="V41" s="91"/>
+      <c r="B41" s="94" t="str">
+        <f>VLOOKUP("label.hscSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 扫描</v>
+      </c>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="94"/>
+      <c r="J41" s="94"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="94"/>
+      <c r="M41" s="94"/>
+      <c r="N41" s="94"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="95"/>
+      <c r="Q41" s="95"/>
+      <c r="R41" s="95"/>
+      <c r="S41" s="95"/>
+      <c r="T41" s="95"/>
+      <c r="U41" s="95"/>
+      <c r="V41" s="95"/>
     </row>
     <row r="42" spans="1:22" ht="22" customHeight="1">
       <c r="A42" s="1"/>
@@ -14780,68 +16794,82 @@
       <c r="V43" s="4"/>
     </row>
     <row r="44" spans="1:22" ht="44" customHeight="1">
-      <c r="B44" s="48" t="s">
+      <c r="B44" s="48" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C44" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C44" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="D44" s="47" t="s">
+      <c r="F44" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="48" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H44" s="48" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E44" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="H44" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="47" t="s">
+      <c r="K44" s="48" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L44" s="48" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M44" s="47" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N44" s="47" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O44" s="48" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P44" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="K44" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="L44" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="M44" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="N44" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="O44" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="P44" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q44" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="R44" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="S44" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="T44" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="U44" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="V44" s="48" t="s">
-        <v>43</v>
+      <c r="Q44" s="48" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R44" s="48" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S44" s="48" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T44" s="48" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U44" s="48" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V44" s="48" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="25" customHeight="1">
@@ -15344,8 +17372,9 @@
       <c r="V52" s="4"/>
     </row>
     <row r="53" spans="2:22" ht="30" customHeight="1">
-      <c r="B53" s="57" t="s">
-        <v>21</v>
+      <c r="B53" s="57" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C53" s="58" t="str">
         <f>B45</f>
@@ -16362,29 +18391,30 @@
       <c r="V80" s="4"/>
     </row>
     <row r="81" spans="2:22" ht="32" customHeight="1">
-      <c r="B81" s="91" t="s">
-        <v>92</v>
-      </c>
-      <c r="C81" s="91"/>
-      <c r="D81" s="91"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="91"/>
-      <c r="H81" s="91"/>
-      <c r="I81" s="91"/>
-      <c r="J81" s="91"/>
-      <c r="K81" s="91"/>
-      <c r="L81" s="91"/>
-      <c r="M81" s="91"/>
-      <c r="N81" s="91"/>
-      <c r="O81" s="91"/>
-      <c r="P81" s="91"/>
-      <c r="Q81" s="91"/>
-      <c r="R81" s="91"/>
-      <c r="S81" s="91"/>
-      <c r="T81" s="91"/>
-      <c r="U81" s="91"/>
-      <c r="V81" s="91"/>
+      <c r="B81" s="95" t="str">
+        <f>VLOOKUP("label.lsrSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 扫描</v>
+      </c>
+      <c r="C81" s="95"/>
+      <c r="D81" s="95"/>
+      <c r="E81" s="95"/>
+      <c r="F81" s="95"/>
+      <c r="G81" s="95"/>
+      <c r="H81" s="95"/>
+      <c r="I81" s="95"/>
+      <c r="J81" s="95"/>
+      <c r="K81" s="95"/>
+      <c r="L81" s="95"/>
+      <c r="M81" s="95"/>
+      <c r="N81" s="95"/>
+      <c r="O81" s="95"/>
+      <c r="P81" s="95"/>
+      <c r="Q81" s="95"/>
+      <c r="R81" s="95"/>
+      <c r="S81" s="95"/>
+      <c r="T81" s="95"/>
+      <c r="U81" s="95"/>
+      <c r="V81" s="95"/>
     </row>
     <row r="82" spans="2:22" ht="22" customHeight="1">
       <c r="B82" s="4"/>
@@ -16433,68 +18463,82 @@
       <c r="V83" s="4"/>
     </row>
     <row r="84" spans="2:22" ht="44" customHeight="1">
-      <c r="B84" s="48" t="s">
+      <c r="B84" s="48" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C84" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E84" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C84" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="D84" s="47" t="s">
+      <c r="F84" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84" s="48" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H84" s="48" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I84" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E84" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="F84" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G84" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="H84" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="I84" s="47" t="s">
+      <c r="K84" s="48" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L84" s="48" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M84" s="47" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N84" s="47" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O84" s="48" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P84" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J84" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="K84" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="L84" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="M84" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="N84" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="O84" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="P84" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q84" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="R84" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="S84" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="T84" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="U84" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="V84" s="48" t="s">
-        <v>43</v>
+      <c r="Q84" s="48" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R84" s="48" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S84" s="48" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T84" s="48" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U84" s="48" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V84" s="48" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="85" spans="2:22" ht="25" customHeight="1">
@@ -16997,8 +19041,9 @@
       <c r="V92" s="4"/>
     </row>
     <row r="93" spans="2:22" ht="30" customHeight="1">
-      <c r="B93" s="57" t="s">
-        <v>21</v>
+      <c r="B93" s="57" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C93" s="58" t="str">
         <f>B85</f>
@@ -18015,29 +20060,30 @@
       <c r="V120" s="4"/>
     </row>
     <row r="121" spans="2:22" ht="32" customHeight="1">
-      <c r="B121" s="91" t="s">
-        <v>93</v>
-      </c>
-      <c r="C121" s="91"/>
-      <c r="D121" s="91"/>
-      <c r="E121" s="91"/>
-      <c r="F121" s="91"/>
-      <c r="G121" s="91"/>
-      <c r="H121" s="91"/>
-      <c r="I121" s="91"/>
-      <c r="J121" s="91"/>
-      <c r="K121" s="91"/>
-      <c r="L121" s="91"/>
-      <c r="M121" s="91"/>
-      <c r="N121" s="91"/>
-      <c r="O121" s="91"/>
-      <c r="P121" s="91"/>
-      <c r="Q121" s="91"/>
-      <c r="R121" s="91"/>
-      <c r="S121" s="91"/>
-      <c r="T121" s="91"/>
-      <c r="U121" s="91"/>
-      <c r="V121" s="91"/>
+      <c r="B121" s="95" t="str">
+        <f>VLOOKUP("label.fullSweep",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>全范围扫描</v>
+      </c>
+      <c r="C121" s="95"/>
+      <c r="D121" s="95"/>
+      <c r="E121" s="95"/>
+      <c r="F121" s="95"/>
+      <c r="G121" s="95"/>
+      <c r="H121" s="95"/>
+      <c r="I121" s="95"/>
+      <c r="J121" s="95"/>
+      <c r="K121" s="95"/>
+      <c r="L121" s="95"/>
+      <c r="M121" s="95"/>
+      <c r="N121" s="95"/>
+      <c r="O121" s="95"/>
+      <c r="P121" s="95"/>
+      <c r="Q121" s="95"/>
+      <c r="R121" s="95"/>
+      <c r="S121" s="95"/>
+      <c r="T121" s="95"/>
+      <c r="U121" s="95"/>
+      <c r="V121" s="95"/>
     </row>
     <row r="122" spans="2:22" ht="22" customHeight="1">
       <c r="B122" s="4"/>
@@ -18086,68 +20132,82 @@
       <c r="V123" s="4"/>
     </row>
     <row r="124" spans="2:22" ht="44" customHeight="1">
-      <c r="B124" s="48" t="s">
+      <c r="B124" s="48" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C124" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="D124" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="E124" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="C124" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="D124" s="47" t="s">
+      <c r="F124" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="G124" s="48" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H124" s="48" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I124" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="J124" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="E124" s="47" t="s">
-        <v>33</v>
-      </c>
-      <c r="F124" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="G124" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="H124" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="I124" s="47" t="s">
+      <c r="K124" s="48" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L124" s="48" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M124" s="47" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N124" s="47" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O124" s="48" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P124" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J124" s="47" t="s">
-        <v>35</v>
-      </c>
-      <c r="K124" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="L124" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="M124" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="N124" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="O124" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="P124" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q124" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="R124" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="S124" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="T124" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="U124" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="V124" s="48" t="s">
-        <v>43</v>
+      <c r="Q124" s="48" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R124" s="48" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S124" s="48" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T124" s="48" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U124" s="48" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V124" s="48" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="125" spans="2:22" ht="25" customHeight="1">
@@ -18650,8 +20710,9 @@
       <c r="V132" s="4"/>
     </row>
     <row r="133" spans="2:22" ht="30" customHeight="1">
-      <c r="B133" s="57" t="s">
-        <v>21</v>
+      <c r="B133" s="57" t="str">
+        <f>VLOOKUP("label.shaftVelocityMps",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>轴速 (m/s)</v>
       </c>
       <c r="C133" s="58" t="str">
         <f>B125</f>
@@ -19929,93 +21990,108 @@
       <c r="V157" s="4"/>
     </row>
     <row r="161" spans="2:22" ht="32" customHeight="1">
-      <c r="B161" s="92" t="s">
-        <v>94</v>
-      </c>
-      <c r="C161" s="92"/>
-      <c r="D161" s="92"/>
-      <c r="E161" s="92"/>
-      <c r="F161" s="92"/>
-      <c r="G161" s="92"/>
-      <c r="H161" s="92"/>
-      <c r="I161" s="92"/>
-      <c r="J161" s="92"/>
-      <c r="K161" s="92"/>
-      <c r="L161" s="92"/>
-      <c r="M161" s="92"/>
-      <c r="N161" s="92"/>
-      <c r="O161" s="92"/>
-      <c r="P161" s="92"/>
-      <c r="Q161" s="92"/>
-      <c r="R161" s="92"/>
-      <c r="S161" s="92"/>
-      <c r="T161" s="92"/>
-      <c r="U161" s="92"/>
-      <c r="V161" s="92"/>
+      <c r="B161" s="96" t="str">
+        <f>VLOOKUP("label.calculator",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>计算器</v>
+      </c>
+      <c r="C161" s="96"/>
+      <c r="D161" s="96"/>
+      <c r="E161" s="96"/>
+      <c r="F161" s="96"/>
+      <c r="G161" s="96"/>
+      <c r="H161" s="96"/>
+      <c r="I161" s="96"/>
+      <c r="J161" s="96"/>
+      <c r="K161" s="96"/>
+      <c r="L161" s="96"/>
+      <c r="M161" s="96"/>
+      <c r="N161" s="96"/>
+      <c r="O161" s="96"/>
+      <c r="P161" s="96"/>
+      <c r="Q161" s="96"/>
+      <c r="R161" s="96"/>
+      <c r="S161" s="96"/>
+      <c r="T161" s="96"/>
+      <c r="U161" s="96"/>
+      <c r="V161" s="96"/>
     </row>
     <row r="164" spans="2:22" ht="44" customHeight="1">
-      <c r="B164" s="61" t="s">
+      <c r="B164" s="61" t="str">
+        <f>VLOOKUP("label.curve",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>曲线</v>
+      </c>
+      <c r="C164" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D164" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E164" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="C164" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="D164" s="62" t="s">
+      <c r="F164" s="62" t="s">
+        <v>8</v>
+      </c>
+      <c r="G164" s="61" t="str">
+        <f>VLOOKUP("label.firstKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第一拐点</v>
+      </c>
+      <c r="H164" s="61" t="str">
+        <f>VLOOKUP("label.bump2Multiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>bump2 倍率</v>
+      </c>
+      <c r="I164" s="62" t="s">
+        <v>23</v>
+      </c>
+      <c r="J164" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="E164" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="F164" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="G164" s="61" t="s">
-        <v>44</v>
-      </c>
-      <c r="H164" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="I164" s="62" t="s">
+      <c r="K164" s="61" t="str">
+        <f>VLOOKUP("label.secondKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>第二拐点</v>
+      </c>
+      <c r="L164" s="61" t="str">
+        <f>VLOOKUP("label.totalHsCoefficient",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>总 HS 系数</v>
+      </c>
+      <c r="M164" s="62" t="str">
+        <f>VLOOKUP("label.rebound",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹</v>
+      </c>
+      <c r="N164" s="62" t="str">
+        <f>VLOOKUP("label.reboundKnee",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>回弹拐点</v>
+      </c>
+      <c r="O164" s="61" t="str">
+        <f>VLOOKUP("label.hsrMultiplier",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSR 倍率</v>
+      </c>
+      <c r="P164" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="J164" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="K164" s="61" t="s">
-        <v>45</v>
-      </c>
-      <c r="L164" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="M164" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="N164" s="62" t="s">
-        <v>16</v>
-      </c>
-      <c r="O164" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="P164" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q164" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="R164" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="S164" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="T164" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="U164" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="V164" s="61" t="s">
-        <v>43</v>
+      <c r="Q164" s="61" t="str">
+        <f>VLOOKUP("label.lscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间</v>
+      </c>
+      <c r="R164" s="61" t="str">
+        <f>VLOOKUP("label.hscRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间</v>
+      </c>
+      <c r="S164" s="61" t="str">
+        <f>VLOOKUP("label.lsrRange",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间</v>
+      </c>
+      <c r="T164" s="61" t="str">
+        <f>VLOOKUP("label.lscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSC 区间位置</v>
+      </c>
+      <c r="U164" s="61" t="str">
+        <f>VLOOKUP("label.hscRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>HSC 区间位置</v>
+      </c>
+      <c r="V164" s="61" t="str">
+        <f>VLOOKUP("label.lsrRangePosition",Locale!$A$2:$D$81,4,FALSE)</f>
+        <v>LSR 区间位置</v>
       </c>
     </row>
     <row r="165" spans="2:22" ht="25" customHeight="1">
@@ -20111,5 +22187,6 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>